--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="F14" t="n">
-        <v>9.56</v>
+        <v>8.4</v>
       </c>
       <c r="G14" t="n">
-        <v>166.1</v>
+        <v>160.6</v>
       </c>
       <c r="H14" t="n">
-        <v>79.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-31.97</v>
+        <v>154.02</v>
       </c>
       <c r="K14" t="n">
-        <v>-114.89</v>
+        <v>-46.16</v>
       </c>
       <c r="L14" t="n">
-        <v>119.25</v>
+        <v>160.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:07:18</t>
+          <t>07:07:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.43</v>
+        <v>3.11</v>
       </c>
       <c r="F15" t="n">
-        <v>8.960000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="G15" t="n">
-        <v>161.3</v>
+        <v>179.3</v>
       </c>
       <c r="H15" t="n">
-        <v>71.5</v>
+        <v>70.7</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>66.23</v>
+        <v>-113.11</v>
       </c>
       <c r="K15" t="n">
-        <v>39.27</v>
+        <v>-17.8</v>
       </c>
       <c r="L15" t="n">
-        <v>77</v>
+        <v>114.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:07:48</t>
+          <t>07:09:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="F16" t="n">
-        <v>8.91</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>178.5</v>
+        <v>178</v>
       </c>
       <c r="H16" t="n">
-        <v>74.09999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>22.88</v>
+        <v>289.92</v>
       </c>
       <c r="K16" t="n">
-        <v>-22.17</v>
+        <v>-28.37</v>
       </c>
       <c r="L16" t="n">
-        <v>31.86</v>
+        <v>291.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:14:02</t>
+          <t>07:14:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.78</v>
+        <v>3.21</v>
       </c>
       <c r="F17" t="n">
-        <v>8.039999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="G17" t="n">
-        <v>161.5</v>
+        <v>169</v>
       </c>
       <c r="H17" t="n">
-        <v>76.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>83.58</v>
+        <v>69.39</v>
       </c>
       <c r="K17" t="n">
-        <v>91.69</v>
+        <v>-116.53</v>
       </c>
       <c r="L17" t="n">
-        <v>124.07</v>
+        <v>135.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:16:05</t>
+          <t>07:16:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>8.73</v>
       </c>
       <c r="G18" t="n">
-        <v>167.1</v>
+        <v>172.2</v>
       </c>
       <c r="H18" t="n">
-        <v>77.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-35.91</v>
+        <v>167.49</v>
       </c>
       <c r="K18" t="n">
-        <v>250.09</v>
+        <v>12.45</v>
       </c>
       <c r="L18" t="n">
-        <v>252.66</v>
+        <v>167.95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:18:29</t>
+          <t>07:19:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.55</v>
+        <v>3.08</v>
       </c>
       <c r="F19" t="n">
-        <v>8.85</v>
+        <v>8.76</v>
       </c>
       <c r="G19" t="n">
-        <v>162.9</v>
+        <v>161.5</v>
       </c>
       <c r="H19" t="n">
-        <v>77.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-33</v>
+        <v>68.59</v>
       </c>
       <c r="K19" t="n">
-        <v>24.08</v>
+        <v>114.88</v>
       </c>
       <c r="L19" t="n">
-        <v>40.85</v>
+        <v>133.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:24:12</t>
+          <t>07:23:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="F20" t="n">
-        <v>8.82</v>
+        <v>8.56</v>
       </c>
       <c r="G20" t="n">
-        <v>172.4</v>
+        <v>154.2</v>
       </c>
       <c r="H20" t="n">
-        <v>77.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>183.93</v>
+        <v>-414.63</v>
       </c>
       <c r="K20" t="n">
-        <v>187.49</v>
+        <v>-152.06</v>
       </c>
       <c r="L20" t="n">
-        <v>262.65</v>
+        <v>441.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:25:22</t>
+          <t>07:24:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="F21" t="n">
-        <v>8.210000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="G21" t="n">
-        <v>169.1</v>
+        <v>168.3</v>
       </c>
       <c r="H21" t="n">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-440.76</v>
+        <v>31.38</v>
       </c>
       <c r="K21" t="n">
-        <v>380.21</v>
+        <v>209.95</v>
       </c>
       <c r="L21" t="n">
-        <v>582.09</v>
+        <v>212.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:27:12</t>
+          <t>07:25:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.7</v>
+        <v>3.48</v>
       </c>
       <c r="F22" t="n">
-        <v>8.76</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>172.2</v>
+        <v>165</v>
       </c>
       <c r="H22" t="n">
-        <v>66.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-97.76000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="K22" t="n">
-        <v>-387.88</v>
+        <v>340.76</v>
       </c>
       <c r="L22" t="n">
-        <v>400.01</v>
+        <v>344.64</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:32:18</t>
+          <t>07:30:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.6</v>
+        <v>3.27</v>
       </c>
       <c r="F23" t="n">
-        <v>8.15</v>
+        <v>9.33</v>
       </c>
       <c r="G23" t="n">
-        <v>177</v>
+        <v>159.5</v>
       </c>
       <c r="H23" t="n">
-        <v>78.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>371.06</v>
+        <v>-205.31</v>
       </c>
       <c r="K23" t="n">
-        <v>506.07</v>
+        <v>-282.98</v>
       </c>
       <c r="L23" t="n">
-        <v>627.52</v>
+        <v>349.61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:34:54</t>
+          <t>07:32:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="F24" t="n">
-        <v>9.050000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="G24" t="n">
-        <v>158.9</v>
+        <v>169.5</v>
       </c>
       <c r="H24" t="n">
-        <v>72</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-480.11</v>
+        <v>-447.33</v>
       </c>
       <c r="K24" t="n">
-        <v>65.65000000000001</v>
+        <v>-285.31</v>
       </c>
       <c r="L24" t="n">
-        <v>484.58</v>
+        <v>530.5700000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:37:19</t>
+          <t>07:34:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.33</v>
+        <v>2.77</v>
       </c>
       <c r="F25" t="n">
-        <v>9.31</v>
+        <v>8.52</v>
       </c>
       <c r="G25" t="n">
-        <v>166</v>
+        <v>169.3</v>
       </c>
       <c r="H25" t="n">
-        <v>76.09999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="I25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-350.68</v>
+        <v>-96.23999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>15.38</v>
+        <v>-177.65</v>
       </c>
       <c r="L25" t="n">
-        <v>351.02</v>
+        <v>202.05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:41:33</t>
+          <t>07:39:07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="F26" t="n">
-        <v>8.99</v>
+        <v>8.51</v>
       </c>
       <c r="G26" t="n">
-        <v>177.5</v>
+        <v>159.6</v>
       </c>
       <c r="H26" t="n">
-        <v>79</v>
+        <v>77.3</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>841.65</v>
+        <v>-159.9</v>
       </c>
       <c r="K26" t="n">
-        <v>689.15</v>
+        <v>271.05</v>
       </c>
       <c r="L26" t="n">
-        <v>1087.8</v>
+        <v>314.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:43:05</t>
+          <t>07:41:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="F27" t="n">
-        <v>9.539999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="G27" t="n">
-        <v>175.5</v>
+        <v>177.5</v>
       </c>
       <c r="H27" t="n">
-        <v>76.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>12.78</v>
+        <v>-324.14</v>
       </c>
       <c r="K27" t="n">
-        <v>-605.71</v>
+        <v>-229.54</v>
       </c>
       <c r="L27" t="n">
-        <v>605.85</v>
+        <v>397.18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:44:32</t>
+          <t>07:43:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="F28" t="n">
-        <v>9.58</v>
+        <v>9.1</v>
       </c>
       <c r="G28" t="n">
-        <v>157.4</v>
+        <v>152.4</v>
       </c>
       <c r="H28" t="n">
-        <v>76</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>237.66</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>244.24</v>
+        <v>589.79</v>
       </c>
       <c r="L28" t="n">
-        <v>340.79</v>
+        <v>595.17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:55:57</t>
+          <t>07:54:49</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.93</v>
+        <v>2.68</v>
       </c>
       <c r="F29" t="n">
-        <v>9.18</v>
+        <v>9.52</v>
       </c>
       <c r="G29" t="n">
-        <v>159.7</v>
+        <v>170.2</v>
       </c>
       <c r="H29" t="n">
-        <v>75</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-133.67</v>
+        <v>-41.63</v>
       </c>
       <c r="K29" t="n">
-        <v>3.41</v>
+        <v>-53.05</v>
       </c>
       <c r="L29" t="n">
-        <v>133.71</v>
+        <v>67.43000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:57:04</t>
+          <t>07:55:23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.33</v>
+        <v>2.99</v>
       </c>
       <c r="F30" t="n">
-        <v>8.48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>161.7</v>
+        <v>175.5</v>
       </c>
       <c r="H30" t="n">
-        <v>76.7</v>
+        <v>79.8</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-66.23999999999999</v>
+        <v>7.25</v>
       </c>
       <c r="K30" t="n">
-        <v>-47.33</v>
+        <v>-90.70999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>81.41</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:59:02</t>
+          <t>07:56:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.65</v>
+        <v>3.19</v>
       </c>
       <c r="F31" t="n">
-        <v>8.630000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="G31" t="n">
-        <v>156.3</v>
+        <v>159.6</v>
       </c>
       <c r="H31" t="n">
-        <v>80.3</v>
+        <v>79.8</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>11.74</v>
+        <v>32.6</v>
       </c>
       <c r="K31" t="n">
-        <v>73.11</v>
+        <v>40.46</v>
       </c>
       <c r="L31" t="n">
-        <v>74.05</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:04:22</t>
+          <t>08:02:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.98</v>
+        <v>3.36</v>
       </c>
       <c r="F32" t="n">
-        <v>8.99</v>
+        <v>8.26</v>
       </c>
       <c r="G32" t="n">
-        <v>154.2</v>
+        <v>158.4</v>
       </c>
       <c r="H32" t="n">
-        <v>74.7</v>
+        <v>77.2</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-51.32</v>
+        <v>176.41</v>
       </c>
       <c r="K32" t="n">
-        <v>-31.68</v>
+        <v>-7.36</v>
       </c>
       <c r="L32" t="n">
-        <v>60.31</v>
+        <v>176.57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:06:26</t>
+          <t>08:03:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="F33" t="n">
-        <v>8.710000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="G33" t="n">
-        <v>172.9</v>
+        <v>156</v>
       </c>
       <c r="H33" t="n">
-        <v>76.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>29.53</v>
+        <v>63.27</v>
       </c>
       <c r="K33" t="n">
-        <v>256.84</v>
+        <v>-86.97</v>
       </c>
       <c r="L33" t="n">
-        <v>258.53</v>
+        <v>107.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:07:15</t>
+          <t>08:06:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="F34" t="n">
-        <v>9.279999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="G34" t="n">
-        <v>173.7</v>
+        <v>172.5</v>
       </c>
       <c r="H34" t="n">
-        <v>72.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>173.06</v>
+        <v>37.37</v>
       </c>
       <c r="K34" t="n">
-        <v>-53.61</v>
+        <v>-70.09</v>
       </c>
       <c r="L34" t="n">
-        <v>181.17</v>
+        <v>79.43000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:12:01</t>
+          <t>08:10:29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>8.880000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>170.1</v>
+        <v>163.2</v>
       </c>
       <c r="H35" t="n">
-        <v>78.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>201.73</v>
+        <v>-189.92</v>
       </c>
       <c r="K35" t="n">
-        <v>-178.34</v>
+        <v>-269.89</v>
       </c>
       <c r="L35" t="n">
-        <v>269.26</v>
+        <v>330.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:14:02</t>
+          <t>08:12:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.93</v>
+        <v>3.23</v>
       </c>
       <c r="F36" t="n">
-        <v>9.02</v>
+        <v>8.01</v>
       </c>
       <c r="G36" t="n">
-        <v>176.5</v>
+        <v>167.6</v>
       </c>
       <c r="H36" t="n">
-        <v>75</v>
+        <v>79.7</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>94.61</v>
+        <v>-125.33</v>
       </c>
       <c r="K36" t="n">
-        <v>-30.54</v>
+        <v>69.38</v>
       </c>
       <c r="L36" t="n">
-        <v>99.42</v>
+        <v>143.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:15:42</t>
+          <t>08:13:29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="F37" t="n">
-        <v>8.35</v>
+        <v>8.9</v>
       </c>
       <c r="G37" t="n">
-        <v>158.2</v>
+        <v>177</v>
       </c>
       <c r="H37" t="n">
-        <v>75.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I37" t="n">
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-102.24</v>
+        <v>282.95</v>
       </c>
       <c r="K37" t="n">
-        <v>-123.32</v>
+        <v>-49.44</v>
       </c>
       <c r="L37" t="n">
-        <v>160.18</v>
+        <v>287.24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:20:30</t>
+          <t>08:18:03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.96</v>
+        <v>3.36</v>
       </c>
       <c r="F38" t="n">
-        <v>9.050000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="G38" t="n">
-        <v>172.4</v>
+        <v>158.9</v>
       </c>
       <c r="H38" t="n">
-        <v>71.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="I38" t="n">
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-393.92</v>
+        <v>-128.59</v>
       </c>
       <c r="K38" t="n">
-        <v>176.51</v>
+        <v>-190.46</v>
       </c>
       <c r="L38" t="n">
-        <v>431.66</v>
+        <v>229.81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:22:08</t>
+          <t>08:19:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="F39" t="n">
-        <v>9.25</v>
+        <v>8.75</v>
       </c>
       <c r="G39" t="n">
-        <v>161.1</v>
+        <v>164.4</v>
       </c>
       <c r="H39" t="n">
-        <v>73.8</v>
+        <v>75.8</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-262.98</v>
+        <v>177.29</v>
       </c>
       <c r="K39" t="n">
-        <v>-246.09</v>
+        <v>-70.76000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>360.17</v>
+        <v>190.89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:23:34</t>
+          <t>08:21:47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.34</v>
+        <v>2.84</v>
       </c>
       <c r="F40" t="n">
-        <v>8.550000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="G40" t="n">
-        <v>167.7</v>
+        <v>166.4</v>
       </c>
       <c r="H40" t="n">
-        <v>67</v>
+        <v>76.7</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>451.41</v>
+        <v>145.51</v>
       </c>
       <c r="K40" t="n">
-        <v>-19.49</v>
+        <v>-73.28</v>
       </c>
       <c r="L40" t="n">
-        <v>451.83</v>
+        <v>162.92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:29:11</t>
+          <t>08:26:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="F41" t="n">
-        <v>8.710000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="G41" t="n">
-        <v>158.8</v>
+        <v>166.4</v>
       </c>
       <c r="H41" t="n">
-        <v>70.7</v>
+        <v>78.2</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>94.76000000000001</v>
+        <v>-316.23</v>
       </c>
       <c r="K41" t="n">
-        <v>-517.49</v>
+        <v>-366.21</v>
       </c>
       <c r="L41" t="n">
-        <v>526.09</v>
+        <v>483.85</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:30:33</t>
+          <t>08:28:06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.39</v>
+        <v>3.09</v>
       </c>
       <c r="F42" t="n">
-        <v>8.82</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>180.5</v>
+        <v>167.6</v>
       </c>
       <c r="H42" t="n">
-        <v>80.3</v>
+        <v>75</v>
       </c>
       <c r="I42" t="n">
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-633.99</v>
+        <v>618.61</v>
       </c>
       <c r="K42" t="n">
-        <v>296.92</v>
+        <v>-168.56</v>
       </c>
       <c r="L42" t="n">
-        <v>700.0700000000001</v>
+        <v>641.16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:31:37</t>
+          <t>08:29:42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>8.81</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>165.4</v>
+        <v>151.5</v>
       </c>
       <c r="H43" t="n">
-        <v>73.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-359.33</v>
+        <v>382.37</v>
       </c>
       <c r="K43" t="n">
-        <v>474.77</v>
+        <v>415.69</v>
       </c>
       <c r="L43" t="n">
-        <v>595.42</v>
+        <v>564.8099999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:45:19</t>
+          <t>08:42:06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.08</v>
+        <v>3.29</v>
       </c>
       <c r="F44" t="n">
-        <v>9.390000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="G44" t="n">
-        <v>175.9</v>
+        <v>153.4</v>
       </c>
       <c r="H44" t="n">
-        <v>78.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I44" t="n">
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.12</v>
+        <v>62.25</v>
       </c>
       <c r="K44" t="n">
-        <v>6.12</v>
+        <v>219.23</v>
       </c>
       <c r="L44" t="n">
-        <v>6.48</v>
+        <v>227.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:46:57</t>
+          <t>08:44:25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.61</v>
+        <v>3.21</v>
       </c>
       <c r="F45" t="n">
-        <v>8.640000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="G45" t="n">
-        <v>183.5</v>
+        <v>161.4</v>
       </c>
       <c r="H45" t="n">
-        <v>75.2</v>
+        <v>73.3</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>145.23</v>
+        <v>15.73</v>
       </c>
       <c r="K45" t="n">
-        <v>-57.43</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>156.17</v>
+        <v>73.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:49:00</t>
+          <t>08:45:31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.39</v>
+        <v>3.64</v>
       </c>
       <c r="F46" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="G46" t="n">
-        <v>165.8</v>
+        <v>161.7</v>
       </c>
       <c r="H46" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.64</v>
+        <v>-157.39</v>
       </c>
       <c r="K46" t="n">
-        <v>225.06</v>
+        <v>-49.49</v>
       </c>
       <c r="L46" t="n">
-        <v>225.11</v>
+        <v>164.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:52:38</t>
+          <t>08:51:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="F47" t="n">
-        <v>9.33</v>
+        <v>9.23</v>
       </c>
       <c r="G47" t="n">
-        <v>160.2</v>
+        <v>166.2</v>
       </c>
       <c r="H47" t="n">
-        <v>79.7</v>
+        <v>73.3</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-50.33</v>
+        <v>2.99</v>
       </c>
       <c r="K47" t="n">
-        <v>87.53</v>
+        <v>142.74</v>
       </c>
       <c r="L47" t="n">
-        <v>100.97</v>
+        <v>142.78</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:54:15</t>
+          <t>08:53:20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.9</v>
+        <v>3.36</v>
       </c>
       <c r="F48" t="n">
-        <v>9.050000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>156.6</v>
+        <v>172.2</v>
       </c>
       <c r="H48" t="n">
-        <v>70.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-117.88</v>
+        <v>25.71</v>
       </c>
       <c r="K48" t="n">
-        <v>-136.49</v>
+        <v>-317.59</v>
       </c>
       <c r="L48" t="n">
-        <v>180.35</v>
+        <v>318.63</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:55:20</t>
+          <t>08:55:42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.36</v>
+        <v>3.74</v>
       </c>
       <c r="F49" t="n">
-        <v>8.640000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="G49" t="n">
-        <v>171.9</v>
+        <v>168.8</v>
       </c>
       <c r="H49" t="n">
-        <v>75.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>30.97</v>
+        <v>-81.78</v>
       </c>
       <c r="K49" t="n">
-        <v>-85.06</v>
+        <v>-50.73</v>
       </c>
       <c r="L49" t="n">
-        <v>90.52</v>
+        <v>96.23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:59:53</t>
+          <t>09:00:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.47</v>
+        <v>3.14</v>
       </c>
       <c r="F50" t="n">
-        <v>8.35</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>174.3</v>
+        <v>168.4</v>
       </c>
       <c r="H50" t="n">
-        <v>72.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-326.52</v>
+        <v>-187.85</v>
       </c>
       <c r="K50" t="n">
-        <v>7.15</v>
+        <v>323.33</v>
       </c>
       <c r="L50" t="n">
-        <v>326.6</v>
+        <v>373.94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:02:20</t>
+          <t>09:01:57</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="F51" t="n">
-        <v>8.460000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="G51" t="n">
-        <v>158.6</v>
+        <v>146.5</v>
       </c>
       <c r="H51" t="n">
-        <v>77.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>295.13</v>
+        <v>-13.79</v>
       </c>
       <c r="K51" t="n">
-        <v>-426.61</v>
+        <v>-127.38</v>
       </c>
       <c r="L51" t="n">
-        <v>518.75</v>
+        <v>128.13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:04:35</t>
+          <t>09:04:17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.41</v>
+        <v>2.6</v>
       </c>
       <c r="F52" t="n">
-        <v>8.460000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>165.6</v>
+        <v>159.5</v>
       </c>
       <c r="H52" t="n">
-        <v>73.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>308.36</v>
+        <v>-150.59</v>
       </c>
       <c r="K52" t="n">
-        <v>32.93</v>
+        <v>20.76</v>
       </c>
       <c r="L52" t="n">
-        <v>310.11</v>
+        <v>152.01</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:10:10</t>
+          <t>09:07:41</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.09</v>
+        <v>3.56</v>
       </c>
       <c r="F53" t="n">
-        <v>8.82</v>
+        <v>8.18</v>
       </c>
       <c r="G53" t="n">
-        <v>172.4</v>
+        <v>153.7</v>
       </c>
       <c r="H53" t="n">
-        <v>80.7</v>
+        <v>69.3</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>29.71</v>
+        <v>109.28</v>
       </c>
       <c r="K53" t="n">
-        <v>-355</v>
+        <v>-303.27</v>
       </c>
       <c r="L53" t="n">
-        <v>356.24</v>
+        <v>322.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:11:50</t>
+          <t>09:09:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.29</v>
+        <v>2.92</v>
       </c>
       <c r="F54" t="n">
-        <v>7.72</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>166.4</v>
+        <v>171.9</v>
       </c>
       <c r="H54" t="n">
-        <v>78.7</v>
+        <v>65.5</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>11.65</v>
+        <v>-221.46</v>
       </c>
       <c r="K54" t="n">
-        <v>68.88</v>
+        <v>41.54</v>
       </c>
       <c r="L54" t="n">
-        <v>69.84999999999999</v>
+        <v>225.32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:13:03</t>
+          <t>09:11:20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.18</v>
+        <v>3.46</v>
       </c>
       <c r="F55" t="n">
-        <v>8.609999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>180.1</v>
+        <v>160.3</v>
       </c>
       <c r="H55" t="n">
-        <v>71.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>294.06</v>
+        <v>302.99</v>
       </c>
       <c r="K55" t="n">
-        <v>-215.97</v>
+        <v>137.12</v>
       </c>
       <c r="L55" t="n">
-        <v>364.85</v>
+        <v>332.57</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:17:55</t>
+          <t>09:16:11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="F56" t="n">
-        <v>8.539999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="G56" t="n">
-        <v>163.6</v>
+        <v>158.6</v>
       </c>
       <c r="H56" t="n">
-        <v>78.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>-231</v>
+        <v>329.97</v>
       </c>
       <c r="K56" t="n">
-        <v>1032.28</v>
+        <v>191.21</v>
       </c>
       <c r="L56" t="n">
-        <v>1057.81</v>
+        <v>381.37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:20:09</t>
+          <t>09:18:24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.84</v>
+        <v>3.68</v>
       </c>
       <c r="F57" t="n">
-        <v>8.84</v>
+        <v>9.06</v>
       </c>
       <c r="G57" t="n">
-        <v>156.4</v>
+        <v>159.5</v>
       </c>
       <c r="H57" t="n">
-        <v>81.7</v>
+        <v>74.2</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-10.17</v>
+        <v>-15.55</v>
       </c>
       <c r="K57" t="n">
-        <v>-119.6</v>
+        <v>232.23</v>
       </c>
       <c r="L57" t="n">
-        <v>120.04</v>
+        <v>232.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:21:21</t>
+          <t>09:20:07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.27</v>
+        <v>3.14</v>
       </c>
       <c r="F58" t="n">
-        <v>8.960000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="G58" t="n">
-        <v>172.7</v>
+        <v>167.8</v>
       </c>
       <c r="H58" t="n">
-        <v>77.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>503.78</v>
+        <v>-462.55</v>
       </c>
       <c r="K58" t="n">
-        <v>-92.31999999999999</v>
+        <v>-579.8200000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>512.17</v>
+        <v>741.72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:31:47</t>
+          <t>09:28:45</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="F59" t="n">
-        <v>8.9</v>
+        <v>8.92</v>
       </c>
       <c r="G59" t="n">
-        <v>162.6</v>
+        <v>172.6</v>
       </c>
       <c r="H59" t="n">
-        <v>81.7</v>
+        <v>71.8</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>61.57</v>
+        <v>-77.68000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-58.84</v>
+        <v>28.4</v>
       </c>
       <c r="L59" t="n">
-        <v>85.16</v>
+        <v>82.70999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:33:22</t>
+          <t>09:30:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.29</v>
+        <v>3.05</v>
       </c>
       <c r="F60" t="n">
-        <v>8.609999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="G60" t="n">
-        <v>172.2</v>
+        <v>160</v>
       </c>
       <c r="H60" t="n">
-        <v>79.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.17</v>
+        <v>114.44</v>
       </c>
       <c r="K60" t="n">
-        <v>62.46</v>
+        <v>21.94</v>
       </c>
       <c r="L60" t="n">
-        <v>62.77</v>
+        <v>116.52</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:35:58</t>
+          <t>09:31:09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="F61" t="n">
-        <v>8.77</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>165.6</v>
+        <v>166.7</v>
       </c>
       <c r="H61" t="n">
-        <v>75.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>87.45999999999999</v>
+        <v>-206.98</v>
       </c>
       <c r="K61" t="n">
-        <v>-54.48</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>103.04</v>
+        <v>217.04</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:41:06</t>
+          <t>09:37:19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.42</v>
+        <v>3.09</v>
       </c>
       <c r="F62" t="n">
-        <v>8.890000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>165.8</v>
+        <v>178.7</v>
       </c>
       <c r="H62" t="n">
-        <v>75.59999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-68.08</v>
+        <v>42.96</v>
       </c>
       <c r="K62" t="n">
-        <v>-316.32</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>323.56</v>
+        <v>93.62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:43:14</t>
+          <t>09:38:05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="F63" t="n">
-        <v>9.07</v>
+        <v>8.58</v>
       </c>
       <c r="G63" t="n">
-        <v>164.9</v>
+        <v>162.9</v>
       </c>
       <c r="H63" t="n">
-        <v>72.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>219.51</v>
+        <v>-3.35</v>
       </c>
       <c r="K63" t="n">
-        <v>-59.63</v>
+        <v>-40.85</v>
       </c>
       <c r="L63" t="n">
-        <v>227.47</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:44:35</t>
+          <t>09:39:22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.86</v>
+        <v>3.71</v>
       </c>
       <c r="F64" t="n">
-        <v>9.02</v>
+        <v>8.92</v>
       </c>
       <c r="G64" t="n">
-        <v>171.3</v>
+        <v>174.9</v>
       </c>
       <c r="H64" t="n">
-        <v>60.9</v>
+        <v>71.8</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-31.54</v>
+        <v>77.87</v>
       </c>
       <c r="K64" t="n">
-        <v>-30.16</v>
+        <v>70.19</v>
       </c>
       <c r="L64" t="n">
-        <v>43.64</v>
+        <v>104.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:48:21</t>
+          <t>09:44:08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.3</v>
+        <v>3.93</v>
       </c>
       <c r="F65" t="n">
-        <v>7.9</v>
+        <v>8.76</v>
       </c>
       <c r="G65" t="n">
-        <v>164</v>
+        <v>160.8</v>
       </c>
       <c r="H65" t="n">
-        <v>69.5</v>
+        <v>77</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-70.65000000000001</v>
+        <v>-189.73</v>
       </c>
       <c r="K65" t="n">
-        <v>-512.73</v>
+        <v>-144.58</v>
       </c>
       <c r="L65" t="n">
-        <v>517.58</v>
+        <v>238.54</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:49:29</t>
+          <t>09:46:05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.87</v>
+        <v>3.56</v>
       </c>
       <c r="F66" t="n">
-        <v>9.32</v>
+        <v>8.4</v>
       </c>
       <c r="G66" t="n">
-        <v>155.2</v>
+        <v>157.4</v>
       </c>
       <c r="H66" t="n">
-        <v>71.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>33.34</v>
+        <v>-327.1</v>
       </c>
       <c r="K66" t="n">
-        <v>-270.36</v>
+        <v>-23.52</v>
       </c>
       <c r="L66" t="n">
-        <v>272.41</v>
+        <v>327.95</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:50:58</t>
+          <t>09:47:32</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.54</v>
+        <v>3.95</v>
       </c>
       <c r="F67" t="n">
-        <v>7.98</v>
+        <v>8.75</v>
       </c>
       <c r="G67" t="n">
-        <v>160.6</v>
+        <v>165.2</v>
       </c>
       <c r="H67" t="n">
-        <v>76.3</v>
+        <v>77</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-71.90000000000001</v>
+        <v>-92.37</v>
       </c>
       <c r="K67" t="n">
-        <v>-128.71</v>
+        <v>43.38</v>
       </c>
       <c r="L67" t="n">
-        <v>147.43</v>
+        <v>102.05</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:54:54</t>
+          <t>09:50:20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="F68" t="n">
-        <v>8.81</v>
+        <v>9.27</v>
       </c>
       <c r="G68" t="n">
-        <v>184.1</v>
+        <v>170.3</v>
       </c>
       <c r="H68" t="n">
-        <v>72.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>330.09</v>
+        <v>-25.14</v>
       </c>
       <c r="K68" t="n">
-        <v>337.27</v>
+        <v>-81.59</v>
       </c>
       <c r="L68" t="n">
-        <v>471.93</v>
+        <v>85.38</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:56:25</t>
+          <t>09:52:23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="F69" t="n">
-        <v>9.5</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>179</v>
+        <v>157.2</v>
       </c>
       <c r="H69" t="n">
-        <v>74.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I69" t="n">
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>192.93</v>
+        <v>-46.59</v>
       </c>
       <c r="K69" t="n">
-        <v>343.95</v>
+        <v>455.66</v>
       </c>
       <c r="L69" t="n">
-        <v>394.37</v>
+        <v>458.04</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:58:20</t>
+          <t>09:54:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.88</v>
+        <v>3.49</v>
       </c>
       <c r="F70" t="n">
-        <v>8.99</v>
+        <v>8.01</v>
       </c>
       <c r="G70" t="n">
-        <v>150.8</v>
+        <v>162.8</v>
       </c>
       <c r="H70" t="n">
-        <v>73.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>483.56</v>
+        <v>596.2</v>
       </c>
       <c r="K70" t="n">
-        <v>-206.47</v>
+        <v>95.5</v>
       </c>
       <c r="L70" t="n">
-        <v>525.8</v>
+        <v>603.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:03:26</t>
+          <t>09:58:19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.79</v>
+        <v>3.61</v>
       </c>
       <c r="F71" t="n">
-        <v>9.4</v>
+        <v>8.17</v>
       </c>
       <c r="G71" t="n">
-        <v>172.3</v>
+        <v>167.4</v>
       </c>
       <c r="H71" t="n">
-        <v>76</v>
+        <v>74.2</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-524.96</v>
+        <v>173.07</v>
       </c>
       <c r="K71" t="n">
-        <v>-252.71</v>
+        <v>312.69</v>
       </c>
       <c r="L71" t="n">
-        <v>582.62</v>
+        <v>357.39</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:04:33</t>
+          <t>10:00:39</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.59</v>
+        <v>3.72</v>
       </c>
       <c r="F72" t="n">
-        <v>8.92</v>
+        <v>8.5</v>
       </c>
       <c r="G72" t="n">
-        <v>162.5</v>
+        <v>170</v>
       </c>
       <c r="H72" t="n">
-        <v>81.8</v>
+        <v>68.5</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>44.87</v>
+        <v>-577.51</v>
       </c>
       <c r="K72" t="n">
-        <v>-47.47</v>
+        <v>-100.72</v>
       </c>
       <c r="L72" t="n">
-        <v>65.33</v>
+        <v>586.23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:05:59</t>
+          <t>10:02:14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="F73" t="n">
-        <v>9.15</v>
+        <v>9.01</v>
       </c>
       <c r="G73" t="n">
-        <v>156.2</v>
+        <v>166.7</v>
       </c>
       <c r="H73" t="n">
-        <v>72.8</v>
+        <v>66.5</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-119.89</v>
+        <v>-134.45</v>
       </c>
       <c r="K73" t="n">
-        <v>-227.86</v>
+        <v>256.77</v>
       </c>
       <c r="L73" t="n">
-        <v>257.48</v>
+        <v>289.84</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:15:35</t>
+          <t>10:13:26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.45</v>
+        <v>3.63</v>
       </c>
       <c r="F74" t="n">
-        <v>8.81</v>
+        <v>8.77</v>
       </c>
       <c r="G74" t="n">
-        <v>159.4</v>
+        <v>151.5</v>
       </c>
       <c r="H74" t="n">
-        <v>68.5</v>
+        <v>74.2</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>14.62</v>
+        <v>60.08</v>
       </c>
       <c r="K74" t="n">
-        <v>-43.62</v>
+        <v>-176.1</v>
       </c>
       <c r="L74" t="n">
-        <v>46.01</v>
+        <v>186.06</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:17:50</t>
+          <t>10:14:38</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.34</v>
+        <v>3.41</v>
       </c>
       <c r="F75" t="n">
-        <v>8.35</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>174.9</v>
+        <v>180.6</v>
       </c>
       <c r="H75" t="n">
-        <v>78.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>51.65</v>
+        <v>115.18</v>
       </c>
       <c r="K75" t="n">
-        <v>166.61</v>
+        <v>-28.24</v>
       </c>
       <c r="L75" t="n">
-        <v>174.43</v>
+        <v>118.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:18:52</t>
+          <t>10:16:29</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>3.49</v>
       </c>
       <c r="F76" t="n">
-        <v>8.869999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>152.4</v>
+        <v>160.5</v>
       </c>
       <c r="H76" t="n">
-        <v>75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-106.97</v>
+        <v>-42.75</v>
       </c>
       <c r="K76" t="n">
-        <v>115.77</v>
+        <v>-45.52</v>
       </c>
       <c r="L76" t="n">
-        <v>157.62</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:22:07</t>
+          <t>10:20:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.57</v>
+        <v>2.88</v>
       </c>
       <c r="F77" t="n">
-        <v>8.49</v>
+        <v>8.65</v>
       </c>
       <c r="G77" t="n">
-        <v>176.2</v>
+        <v>162.5</v>
       </c>
       <c r="H77" t="n">
-        <v>76</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-250.27</v>
+        <v>-68.95</v>
       </c>
       <c r="K77" t="n">
-        <v>174.98</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>305.38</v>
+        <v>107.68</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:22:52</t>
+          <t>10:23:15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.41</v>
+        <v>3.9</v>
       </c>
       <c r="F78" t="n">
-        <v>8.51</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>167.2</v>
+        <v>179.1</v>
       </c>
       <c r="H78" t="n">
-        <v>73</v>
+        <v>74.2</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>81.73999999999999</v>
+        <v>-62.93</v>
       </c>
       <c r="K78" t="n">
-        <v>-46.19</v>
+        <v>98.94</v>
       </c>
       <c r="L78" t="n">
-        <v>93.89</v>
+        <v>117.26</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:24:35</t>
+          <t>10:24:17</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="F79" t="n">
-        <v>8.720000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="G79" t="n">
-        <v>169</v>
+        <v>166.2</v>
       </c>
       <c r="H79" t="n">
-        <v>78.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-69.17</v>
+        <v>7.11</v>
       </c>
       <c r="K79" t="n">
-        <v>-128.87</v>
+        <v>-166.63</v>
       </c>
       <c r="L79" t="n">
-        <v>146.26</v>
+        <v>166.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:29:28</t>
+          <t>10:28:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="F80" t="n">
-        <v>8.69</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>153.8</v>
+        <v>158.1</v>
       </c>
       <c r="H80" t="n">
-        <v>76.7</v>
+        <v>79</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-220.91</v>
+        <v>28.78</v>
       </c>
       <c r="K80" t="n">
-        <v>-17</v>
+        <v>19.32</v>
       </c>
       <c r="L80" t="n">
-        <v>221.57</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:31:42</t>
+          <t>10:30:04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.69</v>
+        <v>3.32</v>
       </c>
       <c r="F81" t="n">
-        <v>8.880000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="G81" t="n">
-        <v>164.5</v>
+        <v>173.8</v>
       </c>
       <c r="H81" t="n">
-        <v>81.40000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>80.56999999999999</v>
+        <v>-135.39</v>
       </c>
       <c r="K81" t="n">
-        <v>-244.67</v>
+        <v>-240.72</v>
       </c>
       <c r="L81" t="n">
-        <v>257.59</v>
+        <v>276.18</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:33:01</t>
+          <t>10:31:36</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.84</v>
+        <v>3.59</v>
       </c>
       <c r="F82" t="n">
-        <v>8.77</v>
+        <v>8.48</v>
       </c>
       <c r="G82" t="n">
-        <v>165.6</v>
+        <v>162.8</v>
       </c>
       <c r="H82" t="n">
-        <v>78.5</v>
+        <v>75</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-213.25</v>
+        <v>-232.72</v>
       </c>
       <c r="K82" t="n">
-        <v>-80.44</v>
+        <v>-233.97</v>
       </c>
       <c r="L82" t="n">
-        <v>227.92</v>
+        <v>330</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:37:14</t>
+          <t>10:35:44</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.39</v>
+        <v>3.79</v>
       </c>
       <c r="F83" t="n">
-        <v>9.31</v>
+        <v>9.09</v>
       </c>
       <c r="G83" t="n">
-        <v>166.8</v>
+        <v>163.9</v>
       </c>
       <c r="H83" t="n">
-        <v>72.2</v>
+        <v>73.2</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-38.18</v>
+        <v>-216.09</v>
       </c>
       <c r="K83" t="n">
-        <v>272.32</v>
+        <v>-258.2</v>
       </c>
       <c r="L83" t="n">
-        <v>274.98</v>
+        <v>336.69</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:39:17</t>
+          <t>10:37:27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.16</v>
+        <v>3.49</v>
       </c>
       <c r="F84" t="n">
-        <v>9.19</v>
+        <v>8.82</v>
       </c>
       <c r="G84" t="n">
-        <v>167</v>
+        <v>164.3</v>
       </c>
       <c r="H84" t="n">
-        <v>78.3</v>
+        <v>74.3</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>10.55</v>
+        <v>-210.69</v>
       </c>
       <c r="K84" t="n">
-        <v>74.27</v>
+        <v>277.81</v>
       </c>
       <c r="L84" t="n">
-        <v>75.02</v>
+        <v>348.67</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:40:48</t>
+          <t>10:38:21</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.64</v>
+        <v>3.41</v>
       </c>
       <c r="F85" t="n">
-        <v>8.210000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="G85" t="n">
-        <v>161.9</v>
+        <v>156.5</v>
       </c>
       <c r="H85" t="n">
-        <v>75.7</v>
+        <v>73.5</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>312.59</v>
+        <v>76.08</v>
       </c>
       <c r="K85" t="n">
-        <v>184.26</v>
+        <v>281.9</v>
       </c>
       <c r="L85" t="n">
-        <v>362.86</v>
+        <v>291.98</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:44:19</t>
+          <t>10:42:43</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="F86" t="n">
-        <v>9.26</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>148.3</v>
+        <v>178.2</v>
       </c>
       <c r="H86" t="n">
-        <v>74.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>952.64</v>
+        <v>164.38</v>
       </c>
       <c r="K86" t="n">
-        <v>149.79</v>
+        <v>-197.41</v>
       </c>
       <c r="L86" t="n">
-        <v>964.34</v>
+        <v>256.89</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:46:47</t>
+          <t>10:45:22</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.26</v>
+        <v>4.21</v>
       </c>
       <c r="F87" t="n">
-        <v>8.43</v>
+        <v>8.65</v>
       </c>
       <c r="G87" t="n">
-        <v>167.5</v>
+        <v>174.4</v>
       </c>
       <c r="H87" t="n">
-        <v>76.59999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>9.67</v>
+        <v>-169.16</v>
       </c>
       <c r="K87" t="n">
-        <v>-259.25</v>
+        <v>111.52</v>
       </c>
       <c r="L87" t="n">
-        <v>259.43</v>
+        <v>202.61</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:47:55</t>
+          <t>10:46:01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="F88" t="n">
-        <v>9.050000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="G88" t="n">
-        <v>171.1</v>
+        <v>157.8</v>
       </c>
       <c r="H88" t="n">
-        <v>72.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-647.88</v>
+        <v>-453.91</v>
       </c>
       <c r="K88" t="n">
-        <v>67.42</v>
+        <v>-130.25</v>
       </c>
       <c r="L88" t="n">
-        <v>651.38</v>
+        <v>472.23</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>154.02</v>
+        <v>165.66</v>
       </c>
       <c r="K14" t="n">
-        <v>-46.16</v>
+        <v>-49.64</v>
       </c>
       <c r="L14" t="n">
-        <v>160.78</v>
+        <v>172.93</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-113.11</v>
+        <v>-115.11</v>
       </c>
       <c r="K15" t="n">
-        <v>-17.8</v>
+        <v>-18.11</v>
       </c>
       <c r="L15" t="n">
-        <v>114.51</v>
+        <v>116.53</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>289.92</v>
+        <v>235.34</v>
       </c>
       <c r="K16" t="n">
-        <v>-28.37</v>
+        <v>-23.03</v>
       </c>
       <c r="L16" t="n">
-        <v>291.31</v>
+        <v>236.47</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>69.39</v>
+        <v>84.39</v>
       </c>
       <c r="K17" t="n">
-        <v>-116.53</v>
+        <v>-141.73</v>
       </c>
       <c r="L17" t="n">
-        <v>135.62</v>
+        <v>164.95</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>167.49</v>
+        <v>145.45</v>
       </c>
       <c r="K18" t="n">
-        <v>12.45</v>
+        <v>10.81</v>
       </c>
       <c r="L18" t="n">
-        <v>167.95</v>
+        <v>145.85</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>68.59</v>
+        <v>66.06</v>
       </c>
       <c r="K19" t="n">
-        <v>114.88</v>
+        <v>110.64</v>
       </c>
       <c r="L19" t="n">
-        <v>133.8</v>
+        <v>128.87</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-414.63</v>
+        <v>-383.68</v>
       </c>
       <c r="K20" t="n">
-        <v>-152.06</v>
+        <v>-140.71</v>
       </c>
       <c r="L20" t="n">
-        <v>441.64</v>
+        <v>408.67</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>31.38</v>
+        <v>32.87</v>
       </c>
       <c r="K21" t="n">
-        <v>209.95</v>
+        <v>219.91</v>
       </c>
       <c r="L21" t="n">
-        <v>212.28</v>
+        <v>222.36</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>51.6</v>
+        <v>50.89</v>
       </c>
       <c r="K22" t="n">
-        <v>340.76</v>
+        <v>336.07</v>
       </c>
       <c r="L22" t="n">
-        <v>344.64</v>
+        <v>339.9</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-205.31</v>
+        <v>-217.14</v>
       </c>
       <c r="K23" t="n">
-        <v>-282.98</v>
+        <v>-299.28</v>
       </c>
       <c r="L23" t="n">
-        <v>349.61</v>
+        <v>369.75</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-447.33</v>
+        <v>-473.74</v>
       </c>
       <c r="K24" t="n">
-        <v>-285.31</v>
+        <v>-302.15</v>
       </c>
       <c r="L24" t="n">
-        <v>530.5700000000001</v>
+        <v>561.89</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-96.23999999999999</v>
+        <v>-137.38</v>
       </c>
       <c r="K25" t="n">
-        <v>-177.65</v>
+        <v>-253.61</v>
       </c>
       <c r="L25" t="n">
-        <v>202.05</v>
+        <v>288.43</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-159.9</v>
+        <v>-206.85</v>
       </c>
       <c r="K26" t="n">
-        <v>271.05</v>
+        <v>350.65</v>
       </c>
       <c r="L26" t="n">
-        <v>314.7</v>
+        <v>407.11</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-324.14</v>
+        <v>-372.64</v>
       </c>
       <c r="K27" t="n">
-        <v>-229.54</v>
+        <v>-263.89</v>
       </c>
       <c r="L27" t="n">
-        <v>397.18</v>
+        <v>456.62</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>79.84999999999999</v>
+        <v>86.91</v>
       </c>
       <c r="K28" t="n">
-        <v>589.79</v>
+        <v>641.9299999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>595.17</v>
+        <v>647.79</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-41.63</v>
+        <v>-48.95</v>
       </c>
       <c r="K29" t="n">
-        <v>-53.05</v>
+        <v>-62.38</v>
       </c>
       <c r="L29" t="n">
-        <v>67.43000000000001</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>7.25</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-90.70999999999999</v>
+        <v>-107.65</v>
       </c>
       <c r="L30" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>32.6</v>
+        <v>49.26</v>
       </c>
       <c r="K31" t="n">
-        <v>40.46</v>
+        <v>61.14</v>
       </c>
       <c r="L31" t="n">
-        <v>51.95</v>
+        <v>78.52</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>176.41</v>
+        <v>163.61</v>
       </c>
       <c r="K32" t="n">
-        <v>-7.36</v>
+        <v>-6.83</v>
       </c>
       <c r="L32" t="n">
-        <v>176.57</v>
+        <v>163.75</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>63.27</v>
+        <v>73.5</v>
       </c>
       <c r="K33" t="n">
-        <v>-86.97</v>
+        <v>-101.04</v>
       </c>
       <c r="L33" t="n">
-        <v>107.55</v>
+        <v>124.94</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>37.37</v>
+        <v>48.56</v>
       </c>
       <c r="K34" t="n">
-        <v>-70.09</v>
+        <v>-91.09</v>
       </c>
       <c r="L34" t="n">
-        <v>79.43000000000001</v>
+        <v>103.23</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-189.92</v>
+        <v>-185.58</v>
       </c>
       <c r="K35" t="n">
-        <v>-269.89</v>
+        <v>-263.72</v>
       </c>
       <c r="L35" t="n">
-        <v>330.01</v>
+        <v>322.47</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-125.33</v>
+        <v>-161.64</v>
       </c>
       <c r="K36" t="n">
-        <v>69.38</v>
+        <v>89.48</v>
       </c>
       <c r="L36" t="n">
-        <v>143.25</v>
+        <v>184.75</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>282.95</v>
+        <v>318.3</v>
       </c>
       <c r="K37" t="n">
-        <v>-49.44</v>
+        <v>-55.62</v>
       </c>
       <c r="L37" t="n">
-        <v>287.24</v>
+        <v>323.12</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-128.59</v>
+        <v>-198.65</v>
       </c>
       <c r="K38" t="n">
-        <v>-190.46</v>
+        <v>-294.24</v>
       </c>
       <c r="L38" t="n">
-        <v>229.81</v>
+        <v>355.02</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>177.29</v>
+        <v>253.21</v>
       </c>
       <c r="K39" t="n">
-        <v>-70.76000000000001</v>
+        <v>-101.05</v>
       </c>
       <c r="L39" t="n">
-        <v>190.89</v>
+        <v>272.63</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>145.51</v>
+        <v>193.76</v>
       </c>
       <c r="K40" t="n">
-        <v>-73.28</v>
+        <v>-97.58</v>
       </c>
       <c r="L40" t="n">
-        <v>162.92</v>
+        <v>216.94</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-316.23</v>
+        <v>-396.58</v>
       </c>
       <c r="K41" t="n">
-        <v>-366.21</v>
+        <v>-459.24</v>
       </c>
       <c r="L41" t="n">
-        <v>483.85</v>
+        <v>606.78</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>618.61</v>
+        <v>746.39</v>
       </c>
       <c r="K42" t="n">
-        <v>-168.56</v>
+        <v>-203.38</v>
       </c>
       <c r="L42" t="n">
-        <v>641.16</v>
+        <v>773.6</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>382.37</v>
+        <v>388.26</v>
       </c>
       <c r="K43" t="n">
-        <v>415.69</v>
+        <v>422.09</v>
       </c>
       <c r="L43" t="n">
-        <v>564.8099999999999</v>
+        <v>573.5</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>62.25</v>
+        <v>58.41</v>
       </c>
       <c r="K44" t="n">
-        <v>219.23</v>
+        <v>205.71</v>
       </c>
       <c r="L44" t="n">
-        <v>227.9</v>
+        <v>213.84</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>15.73</v>
+        <v>18.42</v>
       </c>
       <c r="K45" t="n">
-        <v>71.56999999999999</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>73.28</v>
+        <v>85.79000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-157.39</v>
+        <v>-153.01</v>
       </c>
       <c r="K46" t="n">
-        <v>-49.49</v>
+        <v>-48.12</v>
       </c>
       <c r="L46" t="n">
-        <v>164.99</v>
+        <v>160.4</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="K47" t="n">
-        <v>142.74</v>
+        <v>156.68</v>
       </c>
       <c r="L47" t="n">
-        <v>142.78</v>
+        <v>156.72</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>25.71</v>
+        <v>20.5</v>
       </c>
       <c r="K48" t="n">
-        <v>-317.59</v>
+        <v>-253.17</v>
       </c>
       <c r="L48" t="n">
-        <v>318.63</v>
+        <v>254</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-81.78</v>
+        <v>-106.15</v>
       </c>
       <c r="K49" t="n">
-        <v>-50.73</v>
+        <v>-65.84999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>96.23</v>
+        <v>124.92</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-187.85</v>
+        <v>-194.24</v>
       </c>
       <c r="K50" t="n">
-        <v>323.33</v>
+        <v>334.34</v>
       </c>
       <c r="L50" t="n">
-        <v>373.94</v>
+        <v>386.67</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.79</v>
+        <v>-24.3</v>
       </c>
       <c r="K51" t="n">
-        <v>-127.38</v>
+        <v>-224.42</v>
       </c>
       <c r="L51" t="n">
-        <v>128.13</v>
+        <v>225.74</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-150.59</v>
+        <v>-167.11</v>
       </c>
       <c r="K52" t="n">
-        <v>20.76</v>
+        <v>23.04</v>
       </c>
       <c r="L52" t="n">
-        <v>152.01</v>
+        <v>168.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>109.28</v>
+        <v>144.68</v>
       </c>
       <c r="K53" t="n">
-        <v>-303.27</v>
+        <v>-401.52</v>
       </c>
       <c r="L53" t="n">
-        <v>322.36</v>
+        <v>426.79</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-221.46</v>
+        <v>-293.63</v>
       </c>
       <c r="K54" t="n">
-        <v>41.54</v>
+        <v>55.07</v>
       </c>
       <c r="L54" t="n">
-        <v>225.32</v>
+        <v>298.75</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>302.99</v>
+        <v>363.85</v>
       </c>
       <c r="K55" t="n">
-        <v>137.12</v>
+        <v>164.66</v>
       </c>
       <c r="L55" t="n">
-        <v>332.57</v>
+        <v>399.38</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>329.97</v>
+        <v>401.66</v>
       </c>
       <c r="K56" t="n">
-        <v>191.21</v>
+        <v>232.76</v>
       </c>
       <c r="L56" t="n">
-        <v>381.37</v>
+        <v>464.23</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-15.55</v>
+        <v>-28.88</v>
       </c>
       <c r="K57" t="n">
-        <v>232.23</v>
+        <v>431.31</v>
       </c>
       <c r="L57" t="n">
-        <v>232.75</v>
+        <v>432.27</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-462.55</v>
+        <v>-542.0700000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>-579.8200000000001</v>
+        <v>-679.5</v>
       </c>
       <c r="L58" t="n">
-        <v>741.72</v>
+        <v>869.23</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-77.68000000000001</v>
+        <v>-99.43000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>28.4</v>
+        <v>36.36</v>
       </c>
       <c r="L59" t="n">
-        <v>82.70999999999999</v>
+        <v>105.87</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>114.44</v>
+        <v>113.83</v>
       </c>
       <c r="K60" t="n">
-        <v>21.94</v>
+        <v>21.82</v>
       </c>
       <c r="L60" t="n">
-        <v>116.52</v>
+        <v>115.9</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-206.98</v>
+        <v>-201.17</v>
       </c>
       <c r="K61" t="n">
-        <v>65.31999999999999</v>
+        <v>63.49</v>
       </c>
       <c r="L61" t="n">
-        <v>217.04</v>
+        <v>210.95</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>42.96</v>
+        <v>56.35</v>
       </c>
       <c r="K62" t="n">
-        <v>83.18000000000001</v>
+        <v>109.1</v>
       </c>
       <c r="L62" t="n">
-        <v>93.62</v>
+        <v>122.79</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-3.35</v>
+        <v>-8.26</v>
       </c>
       <c r="K63" t="n">
-        <v>-40.85</v>
+        <v>-100.57</v>
       </c>
       <c r="L63" t="n">
-        <v>40.98</v>
+        <v>100.91</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>77.87</v>
+        <v>113.48</v>
       </c>
       <c r="K64" t="n">
-        <v>70.19</v>
+        <v>102.3</v>
       </c>
       <c r="L64" t="n">
-        <v>104.83</v>
+        <v>152.78</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-189.73</v>
+        <v>-259.34</v>
       </c>
       <c r="K65" t="n">
-        <v>-144.58</v>
+        <v>-197.63</v>
       </c>
       <c r="L65" t="n">
-        <v>238.54</v>
+        <v>326.06</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-327.1</v>
+        <v>-388.43</v>
       </c>
       <c r="K66" t="n">
-        <v>-23.52</v>
+        <v>-27.93</v>
       </c>
       <c r="L66" t="n">
-        <v>327.95</v>
+        <v>389.44</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-92.37</v>
+        <v>-194.47</v>
       </c>
       <c r="K67" t="n">
-        <v>43.38</v>
+        <v>91.34</v>
       </c>
       <c r="L67" t="n">
-        <v>102.05</v>
+        <v>214.85</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-25.14</v>
+        <v>-55.92</v>
       </c>
       <c r="K68" t="n">
-        <v>-81.59</v>
+        <v>-181.46</v>
       </c>
       <c r="L68" t="n">
-        <v>85.38</v>
+        <v>189.88</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-46.59</v>
+        <v>-54.57</v>
       </c>
       <c r="K69" t="n">
-        <v>455.66</v>
+        <v>533.62</v>
       </c>
       <c r="L69" t="n">
-        <v>458.04</v>
+        <v>536.4</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>596.2</v>
+        <v>665.9400000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>95.5</v>
+        <v>106.67</v>
       </c>
       <c r="L70" t="n">
-        <v>603.8</v>
+        <v>674.4299999999999</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>173.07</v>
+        <v>278.14</v>
       </c>
       <c r="K71" t="n">
-        <v>312.69</v>
+        <v>502.54</v>
       </c>
       <c r="L71" t="n">
-        <v>357.39</v>
+        <v>574.38</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-577.51</v>
+        <v>-690.3200000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>-100.72</v>
+        <v>-120.4</v>
       </c>
       <c r="L72" t="n">
-        <v>586.23</v>
+        <v>700.74</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-134.45</v>
+        <v>-225.13</v>
       </c>
       <c r="K73" t="n">
-        <v>256.77</v>
+        <v>429.95</v>
       </c>
       <c r="L73" t="n">
-        <v>289.84</v>
+        <v>485.32</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>60.08</v>
+        <v>56.13</v>
       </c>
       <c r="K74" t="n">
-        <v>-176.1</v>
+        <v>-164.51</v>
       </c>
       <c r="L74" t="n">
-        <v>186.06</v>
+        <v>173.82</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>115.18</v>
+        <v>119.93</v>
       </c>
       <c r="K75" t="n">
-        <v>-28.24</v>
+        <v>-29.41</v>
       </c>
       <c r="L75" t="n">
-        <v>118.6</v>
+        <v>123.48</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-42.75</v>
+        <v>-61.34</v>
       </c>
       <c r="K76" t="n">
-        <v>-45.52</v>
+        <v>-65.3</v>
       </c>
       <c r="L76" t="n">
-        <v>62.44</v>
+        <v>89.59</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-68.95</v>
+        <v>-82.70999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>82.70999999999999</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>107.68</v>
+        <v>129.17</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-62.93</v>
+        <v>-80.47</v>
       </c>
       <c r="K78" t="n">
-        <v>98.94</v>
+        <v>126.5</v>
       </c>
       <c r="L78" t="n">
-        <v>117.26</v>
+        <v>149.93</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>7.11</v>
+        <v>7.24</v>
       </c>
       <c r="K79" t="n">
-        <v>-166.63</v>
+        <v>-169.56</v>
       </c>
       <c r="L79" t="n">
-        <v>166.78</v>
+        <v>169.71</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>28.78</v>
+        <v>109.12</v>
       </c>
       <c r="K80" t="n">
-        <v>19.32</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>34.66</v>
+        <v>131.42</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-135.39</v>
+        <v>-158.45</v>
       </c>
       <c r="K81" t="n">
-        <v>-240.72</v>
+        <v>-281.7</v>
       </c>
       <c r="L81" t="n">
-        <v>276.18</v>
+        <v>323.21</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-232.72</v>
+        <v>-244.44</v>
       </c>
       <c r="K82" t="n">
-        <v>-233.97</v>
+        <v>-245.75</v>
       </c>
       <c r="L82" t="n">
-        <v>330</v>
+        <v>346.62</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-216.09</v>
+        <v>-311.65</v>
       </c>
       <c r="K83" t="n">
-        <v>-258.2</v>
+        <v>-372.4</v>
       </c>
       <c r="L83" t="n">
-        <v>336.69</v>
+        <v>485.6</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-210.69</v>
+        <v>-284.18</v>
       </c>
       <c r="K84" t="n">
-        <v>277.81</v>
+        <v>374.71</v>
       </c>
       <c r="L84" t="n">
-        <v>348.67</v>
+        <v>470.28</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>76.08</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>281.9</v>
+        <v>351.02</v>
       </c>
       <c r="L85" t="n">
-        <v>291.98</v>
+        <v>363.58</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>164.38</v>
+        <v>330.39</v>
       </c>
       <c r="K86" t="n">
-        <v>-197.41</v>
+        <v>-396.77</v>
       </c>
       <c r="L86" t="n">
-        <v>256.89</v>
+        <v>516.3200000000001</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-169.16</v>
+        <v>-380.88</v>
       </c>
       <c r="K87" t="n">
-        <v>111.52</v>
+        <v>251.08</v>
       </c>
       <c r="L87" t="n">
-        <v>202.61</v>
+        <v>456.2</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-453.91</v>
+        <v>-584.62</v>
       </c>
       <c r="K88" t="n">
-        <v>-130.25</v>
+        <v>-167.76</v>
       </c>
       <c r="L88" t="n">
-        <v>472.23</v>
+        <v>608.22</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>165.66</v>
+        <v>119.95</v>
       </c>
       <c r="K14" t="n">
-        <v>-49.64</v>
+        <v>-35.95</v>
       </c>
       <c r="L14" t="n">
-        <v>172.93</v>
+        <v>125.22</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-115.11</v>
+        <v>-96.7</v>
       </c>
       <c r="K15" t="n">
-        <v>-18.11</v>
+        <v>-15.22</v>
       </c>
       <c r="L15" t="n">
-        <v>116.53</v>
+        <v>97.89</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>235.34</v>
+        <v>194.44</v>
       </c>
       <c r="K16" t="n">
-        <v>-23.03</v>
+        <v>-19.03</v>
       </c>
       <c r="L16" t="n">
-        <v>236.47</v>
+        <v>195.37</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>84.39</v>
+        <v>58.71</v>
       </c>
       <c r="K17" t="n">
-        <v>-141.73</v>
+        <v>-98.59999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>164.95</v>
+        <v>114.76</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>145.45</v>
+        <v>127.43</v>
       </c>
       <c r="K18" t="n">
-        <v>10.81</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>145.85</v>
+        <v>127.78</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>66.06</v>
+        <v>57.35</v>
       </c>
       <c r="K19" t="n">
-        <v>110.64</v>
+        <v>96.05</v>
       </c>
       <c r="L19" t="n">
-        <v>128.87</v>
+        <v>111.86</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-383.68</v>
+        <v>-250.93</v>
       </c>
       <c r="K20" t="n">
-        <v>-140.71</v>
+        <v>-92.02</v>
       </c>
       <c r="L20" t="n">
-        <v>408.67</v>
+        <v>267.27</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>32.87</v>
+        <v>24.51</v>
       </c>
       <c r="K21" t="n">
-        <v>219.91</v>
+        <v>163.99</v>
       </c>
       <c r="L21" t="n">
-        <v>222.36</v>
+        <v>165.81</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>50.89</v>
+        <v>35.73</v>
       </c>
       <c r="K22" t="n">
-        <v>336.07</v>
+        <v>235.95</v>
       </c>
       <c r="L22" t="n">
-        <v>339.9</v>
+        <v>238.64</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-217.14</v>
+        <v>-142.46</v>
       </c>
       <c r="K23" t="n">
-        <v>-299.28</v>
+        <v>-196.35</v>
       </c>
       <c r="L23" t="n">
-        <v>369.75</v>
+        <v>242.59</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-473.74</v>
+        <v>-290.14</v>
       </c>
       <c r="K24" t="n">
-        <v>-302.15</v>
+        <v>-185.05</v>
       </c>
       <c r="L24" t="n">
-        <v>561.89</v>
+        <v>344.13</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-137.38</v>
+        <v>-75.73999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-253.61</v>
+        <v>-139.81</v>
       </c>
       <c r="L25" t="n">
-        <v>288.43</v>
+        <v>159.01</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-206.85</v>
+        <v>-123.95</v>
       </c>
       <c r="K26" t="n">
-        <v>350.65</v>
+        <v>210.11</v>
       </c>
       <c r="L26" t="n">
-        <v>407.11</v>
+        <v>243.95</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-372.64</v>
+        <v>-225.36</v>
       </c>
       <c r="K27" t="n">
-        <v>-263.89</v>
+        <v>-159.59</v>
       </c>
       <c r="L27" t="n">
-        <v>456.62</v>
+        <v>276.14</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>86.91</v>
+        <v>49.87</v>
       </c>
       <c r="K28" t="n">
-        <v>641.9299999999999</v>
+        <v>368.33</v>
       </c>
       <c r="L28" t="n">
-        <v>647.79</v>
+        <v>371.69</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-48.95</v>
+        <v>-40.33</v>
       </c>
       <c r="K29" t="n">
-        <v>-62.38</v>
+        <v>-51.39</v>
       </c>
       <c r="L29" t="n">
-        <v>79.29000000000001</v>
+        <v>65.33</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>8.609999999999999</v>
+        <v>6.61</v>
       </c>
       <c r="K30" t="n">
-        <v>-107.65</v>
+        <v>-82.67</v>
       </c>
       <c r="L30" t="n">
-        <v>108</v>
+        <v>82.94</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>49.26</v>
+        <v>41.08</v>
       </c>
       <c r="K31" t="n">
-        <v>61.14</v>
+        <v>50.98</v>
       </c>
       <c r="L31" t="n">
-        <v>78.52</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>163.61</v>
+        <v>139.09</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.83</v>
+        <v>-5.8</v>
       </c>
       <c r="L32" t="n">
-        <v>163.75</v>
+        <v>139.21</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>73.5</v>
+        <v>53.48</v>
       </c>
       <c r="K33" t="n">
-        <v>-101.04</v>
+        <v>-73.51000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>124.94</v>
+        <v>90.91</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>48.56</v>
+        <v>38.9</v>
       </c>
       <c r="K34" t="n">
-        <v>-91.09</v>
+        <v>-72.97</v>
       </c>
       <c r="L34" t="n">
-        <v>103.23</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-185.58</v>
+        <v>-124.81</v>
       </c>
       <c r="K35" t="n">
-        <v>-263.72</v>
+        <v>-177.37</v>
       </c>
       <c r="L35" t="n">
-        <v>322.47</v>
+        <v>216.88</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-161.64</v>
+        <v>-115.13</v>
       </c>
       <c r="K36" t="n">
-        <v>89.48</v>
+        <v>63.73</v>
       </c>
       <c r="L36" t="n">
-        <v>184.75</v>
+        <v>131.59</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>318.3</v>
+        <v>197.53</v>
       </c>
       <c r="K37" t="n">
-        <v>-55.62</v>
+        <v>-34.51</v>
       </c>
       <c r="L37" t="n">
-        <v>323.12</v>
+        <v>200.52</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-198.65</v>
+        <v>-104.81</v>
       </c>
       <c r="K38" t="n">
-        <v>-294.24</v>
+        <v>-155.25</v>
       </c>
       <c r="L38" t="n">
-        <v>355.02</v>
+        <v>187.31</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>253.21</v>
+        <v>153.51</v>
       </c>
       <c r="K39" t="n">
-        <v>-101.05</v>
+        <v>-61.26</v>
       </c>
       <c r="L39" t="n">
-        <v>272.63</v>
+        <v>165.28</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>193.76</v>
+        <v>125.91</v>
       </c>
       <c r="K40" t="n">
-        <v>-97.58</v>
+        <v>-63.41</v>
       </c>
       <c r="L40" t="n">
-        <v>216.94</v>
+        <v>140.98</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-396.58</v>
+        <v>-210.21</v>
       </c>
       <c r="K41" t="n">
-        <v>-459.24</v>
+        <v>-243.43</v>
       </c>
       <c r="L41" t="n">
-        <v>606.78</v>
+        <v>321.63</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>746.39</v>
+        <v>364.87</v>
       </c>
       <c r="K42" t="n">
-        <v>-203.38</v>
+        <v>-99.42</v>
       </c>
       <c r="L42" t="n">
-        <v>773.6</v>
+        <v>378.17</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>388.26</v>
+        <v>235.88</v>
       </c>
       <c r="K43" t="n">
-        <v>422.09</v>
+        <v>256.44</v>
       </c>
       <c r="L43" t="n">
-        <v>573.5</v>
+        <v>348.43</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>58.41</v>
+        <v>43.62</v>
       </c>
       <c r="K44" t="n">
-        <v>205.71</v>
+        <v>153.61</v>
       </c>
       <c r="L44" t="n">
-        <v>213.84</v>
+        <v>159.68</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>18.42</v>
+        <v>16.61</v>
       </c>
       <c r="K45" t="n">
-        <v>83.79000000000001</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>85.79000000000001</v>
+        <v>77.38</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-153.01</v>
+        <v>-128.38</v>
       </c>
       <c r="K46" t="n">
-        <v>-48.12</v>
+        <v>-40.37</v>
       </c>
       <c r="L46" t="n">
-        <v>160.4</v>
+        <v>134.58</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="K47" t="n">
-        <v>156.68</v>
+        <v>125.74</v>
       </c>
       <c r="L47" t="n">
-        <v>156.72</v>
+        <v>125.77</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>20.5</v>
+        <v>17.42</v>
       </c>
       <c r="K48" t="n">
-        <v>-253.17</v>
+        <v>-215.22</v>
       </c>
       <c r="L48" t="n">
-        <v>254</v>
+        <v>215.93</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-106.15</v>
+        <v>-87.91</v>
       </c>
       <c r="K49" t="n">
-        <v>-65.84999999999999</v>
+        <v>-54.53</v>
       </c>
       <c r="L49" t="n">
-        <v>124.92</v>
+        <v>103.45</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-194.24</v>
+        <v>-120.99</v>
       </c>
       <c r="K50" t="n">
-        <v>334.34</v>
+        <v>208.25</v>
       </c>
       <c r="L50" t="n">
-        <v>386.67</v>
+        <v>240.84</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-24.3</v>
+        <v>-14.33</v>
       </c>
       <c r="K51" t="n">
-        <v>-224.42</v>
+        <v>-132.3</v>
       </c>
       <c r="L51" t="n">
-        <v>225.74</v>
+        <v>133.07</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-167.11</v>
+        <v>-121.1</v>
       </c>
       <c r="K52" t="n">
-        <v>23.04</v>
+        <v>16.7</v>
       </c>
       <c r="L52" t="n">
-        <v>168.69</v>
+        <v>122.24</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>144.68</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-401.52</v>
+        <v>-222.75</v>
       </c>
       <c r="L53" t="n">
-        <v>426.79</v>
+        <v>236.77</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-293.63</v>
+        <v>-170.01</v>
       </c>
       <c r="K54" t="n">
-        <v>55.07</v>
+        <v>31.89</v>
       </c>
       <c r="L54" t="n">
-        <v>298.75</v>
+        <v>172.97</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>363.85</v>
+        <v>217.74</v>
       </c>
       <c r="K55" t="n">
-        <v>164.66</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>399.38</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>401.66</v>
+        <v>239.52</v>
       </c>
       <c r="K56" t="n">
-        <v>232.76</v>
+        <v>138.8</v>
       </c>
       <c r="L56" t="n">
-        <v>464.23</v>
+        <v>276.83</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-28.88</v>
+        <v>-14.63</v>
       </c>
       <c r="K57" t="n">
-        <v>431.31</v>
+        <v>218.44</v>
       </c>
       <c r="L57" t="n">
-        <v>432.27</v>
+        <v>218.93</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-542.0700000000001</v>
+        <v>-264.25</v>
       </c>
       <c r="K58" t="n">
-        <v>-679.5</v>
+        <v>-331.25</v>
       </c>
       <c r="L58" t="n">
-        <v>869.23</v>
+        <v>423.74</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-99.43000000000001</v>
+        <v>-83.69</v>
       </c>
       <c r="K59" t="n">
-        <v>36.36</v>
+        <v>30.6</v>
       </c>
       <c r="L59" t="n">
-        <v>105.87</v>
+        <v>89.11</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>113.83</v>
+        <v>96.19</v>
       </c>
       <c r="K60" t="n">
-        <v>21.82</v>
+        <v>18.44</v>
       </c>
       <c r="L60" t="n">
-        <v>115.9</v>
+        <v>97.94</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-201.17</v>
+        <v>-146.13</v>
       </c>
       <c r="K61" t="n">
-        <v>63.49</v>
+        <v>46.12</v>
       </c>
       <c r="L61" t="n">
-        <v>210.95</v>
+        <v>153.23</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>56.35</v>
+        <v>42.05</v>
       </c>
       <c r="K62" t="n">
-        <v>109.1</v>
+        <v>81.42</v>
       </c>
       <c r="L62" t="n">
-        <v>122.79</v>
+        <v>91.64</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-8.26</v>
+        <v>-5.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-100.57</v>
+        <v>-69.37</v>
       </c>
       <c r="L63" t="n">
-        <v>100.91</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>113.48</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>102.3</v>
+        <v>73.02</v>
       </c>
       <c r="L64" t="n">
-        <v>152.78</v>
+        <v>109.06</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-259.34</v>
+        <v>-154.86</v>
       </c>
       <c r="K65" t="n">
-        <v>-197.63</v>
+        <v>-118.01</v>
       </c>
       <c r="L65" t="n">
-        <v>326.06</v>
+        <v>194.69</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-388.43</v>
+        <v>-228.98</v>
       </c>
       <c r="K66" t="n">
-        <v>-27.93</v>
+        <v>-16.47</v>
       </c>
       <c r="L66" t="n">
-        <v>389.44</v>
+        <v>229.57</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-194.47</v>
+        <v>-116.02</v>
       </c>
       <c r="K67" t="n">
-        <v>91.34</v>
+        <v>54.49</v>
       </c>
       <c r="L67" t="n">
-        <v>214.85</v>
+        <v>128.18</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-55.92</v>
+        <v>-36.18</v>
       </c>
       <c r="K68" t="n">
-        <v>-181.46</v>
+        <v>-117.4</v>
       </c>
       <c r="L68" t="n">
-        <v>189.88</v>
+        <v>122.85</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-54.57</v>
+        <v>-29.7</v>
       </c>
       <c r="K69" t="n">
-        <v>533.62</v>
+        <v>290.48</v>
       </c>
       <c r="L69" t="n">
-        <v>536.4</v>
+        <v>291.99</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>665.9400000000001</v>
+        <v>359.27</v>
       </c>
       <c r="K70" t="n">
-        <v>106.67</v>
+        <v>57.55</v>
       </c>
       <c r="L70" t="n">
-        <v>674.4299999999999</v>
+        <v>363.85</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>278.14</v>
+        <v>132.78</v>
       </c>
       <c r="K71" t="n">
-        <v>502.54</v>
+        <v>239.9</v>
       </c>
       <c r="L71" t="n">
-        <v>574.38</v>
+        <v>274.19</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-690.3200000000001</v>
+        <v>-374.44</v>
       </c>
       <c r="K72" t="n">
-        <v>-120.4</v>
+        <v>-65.3</v>
       </c>
       <c r="L72" t="n">
-        <v>700.74</v>
+        <v>380.09</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-225.13</v>
+        <v>-111.41</v>
       </c>
       <c r="K73" t="n">
-        <v>429.95</v>
+        <v>212.77</v>
       </c>
       <c r="L73" t="n">
-        <v>485.32</v>
+        <v>240.18</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>56.13</v>
+        <v>47.12</v>
       </c>
       <c r="K74" t="n">
-        <v>-164.51</v>
+        <v>-138.11</v>
       </c>
       <c r="L74" t="n">
-        <v>173.82</v>
+        <v>145.93</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>119.93</v>
+        <v>102.16</v>
       </c>
       <c r="K75" t="n">
-        <v>-29.41</v>
+        <v>-25.05</v>
       </c>
       <c r="L75" t="n">
-        <v>123.48</v>
+        <v>105.19</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-61.34</v>
+        <v>-51.96</v>
       </c>
       <c r="K76" t="n">
-        <v>-65.3</v>
+        <v>-55.32</v>
       </c>
       <c r="L76" t="n">
-        <v>89.59</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-82.70999999999999</v>
+        <v>-60.79</v>
       </c>
       <c r="K77" t="n">
-        <v>99.20999999999999</v>
+        <v>72.91</v>
       </c>
       <c r="L77" t="n">
-        <v>129.17</v>
+        <v>94.93000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-80.47</v>
+        <v>-63.34</v>
       </c>
       <c r="K78" t="n">
-        <v>126.5</v>
+        <v>99.58</v>
       </c>
       <c r="L78" t="n">
-        <v>149.93</v>
+        <v>118.02</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>7.24</v>
+        <v>5.84</v>
       </c>
       <c r="K79" t="n">
-        <v>-169.56</v>
+        <v>-136.83</v>
       </c>
       <c r="L79" t="n">
-        <v>169.71</v>
+        <v>136.95</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>109.12</v>
+        <v>69.09</v>
       </c>
       <c r="K80" t="n">
-        <v>73.23999999999999</v>
+        <v>46.37</v>
       </c>
       <c r="L80" t="n">
-        <v>131.42</v>
+        <v>83.20999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-158.45</v>
+        <v>-97.51000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>-281.7</v>
+        <v>-173.36</v>
       </c>
       <c r="L81" t="n">
-        <v>323.21</v>
+        <v>198.9</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-244.44</v>
+        <v>-164.17</v>
       </c>
       <c r="K82" t="n">
-        <v>-245.75</v>
+        <v>-165.05</v>
       </c>
       <c r="L82" t="n">
-        <v>346.62</v>
+        <v>232.8</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-311.65</v>
+        <v>-160.61</v>
       </c>
       <c r="K83" t="n">
-        <v>-372.4</v>
+        <v>-191.92</v>
       </c>
       <c r="L83" t="n">
-        <v>485.6</v>
+        <v>250.26</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-284.18</v>
+        <v>-148.78</v>
       </c>
       <c r="K84" t="n">
-        <v>374.71</v>
+        <v>196.18</v>
       </c>
       <c r="L84" t="n">
-        <v>470.28</v>
+        <v>246.22</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>94.73999999999999</v>
+        <v>56.86</v>
       </c>
       <c r="K85" t="n">
-        <v>351.02</v>
+        <v>210.68</v>
       </c>
       <c r="L85" t="n">
-        <v>363.58</v>
+        <v>218.22</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>330.39</v>
+        <v>161.42</v>
       </c>
       <c r="K86" t="n">
-        <v>-396.77</v>
+        <v>-193.86</v>
       </c>
       <c r="L86" t="n">
-        <v>516.3200000000001</v>
+        <v>252.26</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-380.88</v>
+        <v>-183.48</v>
       </c>
       <c r="K87" t="n">
-        <v>251.08</v>
+        <v>120.95</v>
       </c>
       <c r="L87" t="n">
-        <v>456.2</v>
+        <v>219.76</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-584.62</v>
+        <v>-308.35</v>
       </c>
       <c r="K88" t="n">
-        <v>-167.76</v>
+        <v>-88.48</v>
       </c>
       <c r="L88" t="n">
-        <v>608.22</v>
+        <v>320.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>119.95</v>
+        <v>124.04</v>
       </c>
       <c r="K14" t="n">
-        <v>-35.95</v>
+        <v>-37.17</v>
       </c>
       <c r="L14" t="n">
-        <v>125.22</v>
+        <v>129.49</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-96.7</v>
+        <v>-97.51000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-15.22</v>
+        <v>-15.34</v>
       </c>
       <c r="L15" t="n">
-        <v>97.89</v>
+        <v>98.70999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>194.44</v>
+        <v>197.53</v>
       </c>
       <c r="K16" t="n">
-        <v>-19.03</v>
+        <v>-19.33</v>
       </c>
       <c r="L16" t="n">
-        <v>195.37</v>
+        <v>198.48</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>58.71</v>
+        <v>63.33</v>
       </c>
       <c r="K17" t="n">
-        <v>-98.59999999999999</v>
+        <v>-106.35</v>
       </c>
       <c r="L17" t="n">
-        <v>114.76</v>
+        <v>123.78</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>127.43</v>
+        <v>133.77</v>
       </c>
       <c r="K18" t="n">
-        <v>9.470000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="L18" t="n">
-        <v>127.78</v>
+        <v>134.14</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>57.35</v>
+        <v>59.67</v>
       </c>
       <c r="K19" t="n">
-        <v>96.05</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>111.86</v>
+        <v>116.39</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-250.93</v>
+        <v>-276.11</v>
       </c>
       <c r="K20" t="n">
-        <v>-92.02</v>
+        <v>-101.26</v>
       </c>
       <c r="L20" t="n">
-        <v>267.27</v>
+        <v>294.09</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>24.51</v>
+        <v>26.74</v>
       </c>
       <c r="K21" t="n">
-        <v>163.99</v>
+        <v>178.91</v>
       </c>
       <c r="L21" t="n">
-        <v>165.81</v>
+        <v>180.9</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>35.73</v>
+        <v>38.77</v>
       </c>
       <c r="K22" t="n">
-        <v>235.95</v>
+        <v>256.01</v>
       </c>
       <c r="L22" t="n">
-        <v>238.64</v>
+        <v>258.93</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-142.46</v>
+        <v>-156.07</v>
       </c>
       <c r="K23" t="n">
-        <v>-196.35</v>
+        <v>-215.1</v>
       </c>
       <c r="L23" t="n">
-        <v>242.59</v>
+        <v>265.75</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-290.14</v>
+        <v>-322.13</v>
       </c>
       <c r="K24" t="n">
-        <v>-185.05</v>
+        <v>-205.46</v>
       </c>
       <c r="L24" t="n">
-        <v>344.13</v>
+        <v>382.08</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-75.73999999999999</v>
+        <v>-86.93000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-139.81</v>
+        <v>-160.47</v>
       </c>
       <c r="L25" t="n">
-        <v>159.01</v>
+        <v>182.51</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-123.95</v>
+        <v>-138.6</v>
       </c>
       <c r="K26" t="n">
-        <v>210.11</v>
+        <v>234.95</v>
       </c>
       <c r="L26" t="n">
-        <v>243.95</v>
+        <v>272.79</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-225.36</v>
+        <v>-250.93</v>
       </c>
       <c r="K27" t="n">
-        <v>-159.59</v>
+        <v>-177.7</v>
       </c>
       <c r="L27" t="n">
-        <v>276.14</v>
+        <v>307.48</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>49.87</v>
+        <v>56.07</v>
       </c>
       <c r="K28" t="n">
-        <v>368.33</v>
+        <v>414.13</v>
       </c>
       <c r="L28" t="n">
-        <v>371.69</v>
+        <v>417.91</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-40.33</v>
+        <v>-41.51</v>
       </c>
       <c r="K29" t="n">
-        <v>-51.39</v>
+        <v>-52.9</v>
       </c>
       <c r="L29" t="n">
-        <v>65.33</v>
+        <v>67.25</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>6.61</v>
+        <v>6.85</v>
       </c>
       <c r="K30" t="n">
-        <v>-82.67</v>
+        <v>-85.64</v>
       </c>
       <c r="L30" t="n">
-        <v>82.94</v>
+        <v>85.92</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>41.08</v>
+        <v>41.93</v>
       </c>
       <c r="K31" t="n">
-        <v>50.98</v>
+        <v>52.04</v>
       </c>
       <c r="L31" t="n">
-        <v>65.47</v>
+        <v>66.83</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>139.09</v>
+        <v>146.19</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.8</v>
+        <v>-6.1</v>
       </c>
       <c r="L32" t="n">
-        <v>139.21</v>
+        <v>146.32</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>53.48</v>
+        <v>57.39</v>
       </c>
       <c r="K33" t="n">
-        <v>-73.51000000000001</v>
+        <v>-78.90000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>90.91</v>
+        <v>97.56</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>38.9</v>
+        <v>41.52</v>
       </c>
       <c r="K34" t="n">
-        <v>-72.97</v>
+        <v>-77.89</v>
       </c>
       <c r="L34" t="n">
-        <v>82.7</v>
+        <v>88.26000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-124.81</v>
+        <v>-136.98</v>
       </c>
       <c r="K35" t="n">
-        <v>-177.37</v>
+        <v>-194.66</v>
       </c>
       <c r="L35" t="n">
-        <v>216.88</v>
+        <v>238.02</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-115.13</v>
+        <v>-125.82</v>
       </c>
       <c r="K36" t="n">
-        <v>63.73</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>131.59</v>
+        <v>143.81</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>197.53</v>
+        <v>219.12</v>
       </c>
       <c r="K37" t="n">
-        <v>-34.51</v>
+        <v>-38.29</v>
       </c>
       <c r="L37" t="n">
-        <v>200.52</v>
+        <v>222.44</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-104.81</v>
+        <v>-119.02</v>
       </c>
       <c r="K38" t="n">
-        <v>-155.25</v>
+        <v>-176.29</v>
       </c>
       <c r="L38" t="n">
-        <v>187.31</v>
+        <v>212.7</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>153.51</v>
+        <v>171</v>
       </c>
       <c r="K39" t="n">
-        <v>-61.26</v>
+        <v>-68.25</v>
       </c>
       <c r="L39" t="n">
-        <v>165.28</v>
+        <v>184.12</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>125.91</v>
+        <v>140.2</v>
       </c>
       <c r="K40" t="n">
-        <v>-63.41</v>
+        <v>-70.61</v>
       </c>
       <c r="L40" t="n">
-        <v>140.98</v>
+        <v>156.97</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-210.21</v>
+        <v>-239.87</v>
       </c>
       <c r="K41" t="n">
-        <v>-243.43</v>
+        <v>-277.77</v>
       </c>
       <c r="L41" t="n">
-        <v>321.63</v>
+        <v>367.01</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>364.87</v>
+        <v>419.66</v>
       </c>
       <c r="K42" t="n">
-        <v>-99.42</v>
+        <v>-114.35</v>
       </c>
       <c r="L42" t="n">
-        <v>378.17</v>
+        <v>434.96</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>235.88</v>
+        <v>262.49</v>
       </c>
       <c r="K43" t="n">
-        <v>256.44</v>
+        <v>285.37</v>
       </c>
       <c r="L43" t="n">
-        <v>348.43</v>
+        <v>387.73</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>43.62</v>
+        <v>44.8</v>
       </c>
       <c r="K44" t="n">
-        <v>153.61</v>
+        <v>157.79</v>
       </c>
       <c r="L44" t="n">
-        <v>159.68</v>
+        <v>164.03</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>16.61</v>
+        <v>16.63</v>
       </c>
       <c r="K45" t="n">
-        <v>75.56999999999999</v>
+        <v>75.66</v>
       </c>
       <c r="L45" t="n">
-        <v>77.38</v>
+        <v>77.45999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-128.38</v>
+        <v>-131.52</v>
       </c>
       <c r="K46" t="n">
-        <v>-40.37</v>
+        <v>-41.36</v>
       </c>
       <c r="L46" t="n">
-        <v>134.58</v>
+        <v>137.86</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="K47" t="n">
-        <v>125.74</v>
+        <v>131.89</v>
       </c>
       <c r="L47" t="n">
-        <v>125.77</v>
+        <v>131.92</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>17.42</v>
+        <v>18.17</v>
       </c>
       <c r="K48" t="n">
-        <v>-215.22</v>
+        <v>-224.38</v>
       </c>
       <c r="L48" t="n">
-        <v>215.93</v>
+        <v>225.11</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-87.91</v>
+        <v>-91.41</v>
       </c>
       <c r="K49" t="n">
-        <v>-54.53</v>
+        <v>-56.7</v>
       </c>
       <c r="L49" t="n">
-        <v>103.45</v>
+        <v>107.56</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-120.99</v>
+        <v>-134.14</v>
       </c>
       <c r="K50" t="n">
-        <v>208.25</v>
+        <v>230.89</v>
       </c>
       <c r="L50" t="n">
-        <v>240.84</v>
+        <v>267.03</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.33</v>
+        <v>-15.9</v>
       </c>
       <c r="K51" t="n">
-        <v>-132.3</v>
+        <v>-146.78</v>
       </c>
       <c r="L51" t="n">
-        <v>133.07</v>
+        <v>147.64</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-121.1</v>
+        <v>-131.34</v>
       </c>
       <c r="K52" t="n">
-        <v>16.7</v>
+        <v>18.11</v>
       </c>
       <c r="L52" t="n">
-        <v>122.24</v>
+        <v>132.58</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>80.26000000000001</v>
+        <v>89.81</v>
       </c>
       <c r="K53" t="n">
-        <v>-222.75</v>
+        <v>-249.24</v>
       </c>
       <c r="L53" t="n">
-        <v>236.77</v>
+        <v>264.93</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-170.01</v>
+        <v>-189.17</v>
       </c>
       <c r="K54" t="n">
-        <v>31.89</v>
+        <v>35.48</v>
       </c>
       <c r="L54" t="n">
-        <v>172.97</v>
+        <v>192.47</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>217.74</v>
+        <v>241</v>
       </c>
       <c r="K55" t="n">
-        <v>98.54000000000001</v>
+        <v>109.07</v>
       </c>
       <c r="L55" t="n">
-        <v>239</v>
+        <v>264.54</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>239.52</v>
+        <v>265.38</v>
       </c>
       <c r="K56" t="n">
-        <v>138.8</v>
+        <v>153.78</v>
       </c>
       <c r="L56" t="n">
-        <v>276.83</v>
+        <v>306.72</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-14.63</v>
+        <v>-16.79</v>
       </c>
       <c r="K57" t="n">
-        <v>218.44</v>
+        <v>250.66</v>
       </c>
       <c r="L57" t="n">
-        <v>218.93</v>
+        <v>251.22</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-264.25</v>
+        <v>-301.37</v>
       </c>
       <c r="K58" t="n">
-        <v>-331.25</v>
+        <v>-377.78</v>
       </c>
       <c r="L58" t="n">
-        <v>423.74</v>
+        <v>483.26</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-83.69</v>
+        <v>-84.84999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>30.6</v>
+        <v>31.03</v>
       </c>
       <c r="L59" t="n">
-        <v>89.11</v>
+        <v>90.34</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>96.19</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>18.44</v>
+        <v>18.59</v>
       </c>
       <c r="L60" t="n">
-        <v>97.94</v>
+        <v>98.72</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-146.13</v>
+        <v>-151.09</v>
       </c>
       <c r="K61" t="n">
-        <v>46.12</v>
+        <v>47.68</v>
       </c>
       <c r="L61" t="n">
-        <v>153.23</v>
+        <v>158.43</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>42.05</v>
+        <v>44.34</v>
       </c>
       <c r="K62" t="n">
-        <v>81.42</v>
+        <v>85.86</v>
       </c>
       <c r="L62" t="n">
-        <v>91.64</v>
+        <v>96.63</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.7</v>
+        <v>-6.14</v>
       </c>
       <c r="K63" t="n">
-        <v>-69.37</v>
+        <v>-74.73</v>
       </c>
       <c r="L63" t="n">
-        <v>69.59999999999999</v>
+        <v>74.98</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>81.01000000000001</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>73.02</v>
+        <v>77.52</v>
       </c>
       <c r="L64" t="n">
-        <v>109.06</v>
+        <v>115.77</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-154.86</v>
+        <v>-172.04</v>
       </c>
       <c r="K65" t="n">
-        <v>-118.01</v>
+        <v>-131.1</v>
       </c>
       <c r="L65" t="n">
-        <v>194.69</v>
+        <v>216.3</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-228.98</v>
+        <v>-256.01</v>
       </c>
       <c r="K66" t="n">
-        <v>-16.47</v>
+        <v>-18.41</v>
       </c>
       <c r="L66" t="n">
-        <v>229.57</v>
+        <v>256.67</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-116.02</v>
+        <v>-128.9</v>
       </c>
       <c r="K67" t="n">
-        <v>54.49</v>
+        <v>60.54</v>
       </c>
       <c r="L67" t="n">
-        <v>128.18</v>
+        <v>142.41</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-36.18</v>
+        <v>-39.96</v>
       </c>
       <c r="K68" t="n">
-        <v>-117.4</v>
+        <v>-129.67</v>
       </c>
       <c r="L68" t="n">
-        <v>122.85</v>
+        <v>135.69</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-29.7</v>
+        <v>-33.66</v>
       </c>
       <c r="K69" t="n">
-        <v>290.48</v>
+        <v>329.2</v>
       </c>
       <c r="L69" t="n">
-        <v>291.99</v>
+        <v>330.91</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>359.27</v>
+        <v>406.7</v>
       </c>
       <c r="K70" t="n">
-        <v>57.55</v>
+        <v>65.14</v>
       </c>
       <c r="L70" t="n">
-        <v>363.85</v>
+        <v>411.88</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>132.78</v>
+        <v>153.58</v>
       </c>
       <c r="K71" t="n">
-        <v>239.9</v>
+        <v>277.48</v>
       </c>
       <c r="L71" t="n">
-        <v>274.19</v>
+        <v>317.14</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-374.44</v>
+        <v>-422.46</v>
       </c>
       <c r="K72" t="n">
-        <v>-65.3</v>
+        <v>-73.68000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>380.09</v>
+        <v>428.84</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-111.41</v>
+        <v>-126.55</v>
       </c>
       <c r="K73" t="n">
-        <v>212.77</v>
+        <v>241.68</v>
       </c>
       <c r="L73" t="n">
-        <v>240.18</v>
+        <v>272.81</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>47.12</v>
+        <v>47.98</v>
       </c>
       <c r="K74" t="n">
-        <v>-138.11</v>
+        <v>-140.62</v>
       </c>
       <c r="L74" t="n">
-        <v>145.93</v>
+        <v>148.58</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>102.16</v>
+        <v>103.3</v>
       </c>
       <c r="K75" t="n">
-        <v>-25.05</v>
+        <v>-25.33</v>
       </c>
       <c r="L75" t="n">
-        <v>105.19</v>
+        <v>106.36</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-51.96</v>
+        <v>-52.78</v>
       </c>
       <c r="K76" t="n">
-        <v>-55.32</v>
+        <v>-56.2</v>
       </c>
       <c r="L76" t="n">
-        <v>75.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-60.79</v>
+        <v>-64.43000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>72.91</v>
+        <v>77.28</v>
       </c>
       <c r="L77" t="n">
-        <v>94.93000000000001</v>
+        <v>100.61</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-63.34</v>
+        <v>-66.33</v>
       </c>
       <c r="K78" t="n">
-        <v>99.58</v>
+        <v>104.28</v>
       </c>
       <c r="L78" t="n">
-        <v>118.02</v>
+        <v>123.58</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>5.84</v>
+        <v>6.1</v>
       </c>
       <c r="K79" t="n">
-        <v>-136.83</v>
+        <v>-142.94</v>
       </c>
       <c r="L79" t="n">
-        <v>136.95</v>
+        <v>143.07</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>69.09</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>46.37</v>
+        <v>51.41</v>
       </c>
       <c r="L80" t="n">
-        <v>83.20999999999999</v>
+        <v>92.25</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-97.51000000000001</v>
+        <v>-108.09</v>
       </c>
       <c r="K81" t="n">
-        <v>-173.36</v>
+        <v>-192.18</v>
       </c>
       <c r="L81" t="n">
-        <v>198.9</v>
+        <v>220.5</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-164.17</v>
+        <v>-179.23</v>
       </c>
       <c r="K82" t="n">
-        <v>-165.05</v>
+        <v>-180.2</v>
       </c>
       <c r="L82" t="n">
-        <v>232.8</v>
+        <v>254.16</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-160.61</v>
+        <v>-182.73</v>
       </c>
       <c r="K83" t="n">
-        <v>-191.92</v>
+        <v>-218.35</v>
       </c>
       <c r="L83" t="n">
-        <v>250.26</v>
+        <v>284.72</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-148.78</v>
+        <v>-169.06</v>
       </c>
       <c r="K84" t="n">
-        <v>196.18</v>
+        <v>222.92</v>
       </c>
       <c r="L84" t="n">
-        <v>246.22</v>
+        <v>279.78</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>56.86</v>
+        <v>63.25</v>
       </c>
       <c r="K85" t="n">
-        <v>210.68</v>
+        <v>234.37</v>
       </c>
       <c r="L85" t="n">
-        <v>218.22</v>
+        <v>242.75</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>161.42</v>
+        <v>186.36</v>
       </c>
       <c r="K86" t="n">
-        <v>-193.86</v>
+        <v>-223.8</v>
       </c>
       <c r="L86" t="n">
-        <v>252.26</v>
+        <v>291.24</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-183.48</v>
+        <v>-212.25</v>
       </c>
       <c r="K87" t="n">
-        <v>120.95</v>
+        <v>139.92</v>
       </c>
       <c r="L87" t="n">
-        <v>219.76</v>
+        <v>254.22</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-308.35</v>
+        <v>-354.27</v>
       </c>
       <c r="K88" t="n">
-        <v>-88.48</v>
+        <v>-101.66</v>
       </c>
       <c r="L88" t="n">
-        <v>320.79</v>
+        <v>368.57</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>124.04</v>
+        <v>66.73</v>
       </c>
       <c r="K14" t="n">
-        <v>-37.17</v>
+        <v>-20</v>
       </c>
       <c r="L14" t="n">
-        <v>129.49</v>
+        <v>69.66</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-97.51000000000001</v>
+        <v>-54.24</v>
       </c>
       <c r="K15" t="n">
-        <v>-15.34</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>98.70999999999999</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>197.53</v>
+        <v>106.26</v>
       </c>
       <c r="K16" t="n">
-        <v>-19.33</v>
+        <v>-10.4</v>
       </c>
       <c r="L16" t="n">
-        <v>198.48</v>
+        <v>106.77</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>63.33</v>
+        <v>34.43</v>
       </c>
       <c r="K17" t="n">
-        <v>-106.35</v>
+        <v>-57.82</v>
       </c>
       <c r="L17" t="n">
-        <v>123.78</v>
+        <v>67.29000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>133.77</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>9.94</v>
+        <v>5.65</v>
       </c>
       <c r="L18" t="n">
-        <v>134.14</v>
+        <v>76.25</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>59.67</v>
+        <v>33.18</v>
       </c>
       <c r="K19" t="n">
-        <v>99.93000000000001</v>
+        <v>55.57</v>
       </c>
       <c r="L19" t="n">
-        <v>116.39</v>
+        <v>64.72</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-276.11</v>
+        <v>-152.05</v>
       </c>
       <c r="K20" t="n">
-        <v>-101.26</v>
+        <v>-55.76</v>
       </c>
       <c r="L20" t="n">
-        <v>294.09</v>
+        <v>161.95</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>26.74</v>
+        <v>14.01</v>
       </c>
       <c r="K21" t="n">
-        <v>178.91</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>180.9</v>
+        <v>94.75</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>38.77</v>
+        <v>19.69</v>
       </c>
       <c r="K22" t="n">
-        <v>256.01</v>
+        <v>130.05</v>
       </c>
       <c r="L22" t="n">
-        <v>258.93</v>
+        <v>131.53</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-156.07</v>
+        <v>-89.87</v>
       </c>
       <c r="K23" t="n">
-        <v>-215.1</v>
+        <v>-123.87</v>
       </c>
       <c r="L23" t="n">
-        <v>265.75</v>
+        <v>153.03</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-322.13</v>
+        <v>-167.11</v>
       </c>
       <c r="K24" t="n">
-        <v>-205.46</v>
+        <v>-106.58</v>
       </c>
       <c r="L24" t="n">
-        <v>382.08</v>
+        <v>198.2</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-86.93000000000001</v>
+        <v>-53.98</v>
       </c>
       <c r="K25" t="n">
-        <v>-160.47</v>
+        <v>-99.64</v>
       </c>
       <c r="L25" t="n">
-        <v>182.51</v>
+        <v>113.32</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-138.6</v>
+        <v>-78.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>234.95</v>
+        <v>133.24</v>
       </c>
       <c r="L26" t="n">
-        <v>272.79</v>
+        <v>154.69</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-250.93</v>
+        <v>-146.38</v>
       </c>
       <c r="K27" t="n">
-        <v>-177.7</v>
+        <v>-103.66</v>
       </c>
       <c r="L27" t="n">
-        <v>307.48</v>
+        <v>179.37</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>56.07</v>
+        <v>31.72</v>
       </c>
       <c r="K28" t="n">
-        <v>414.13</v>
+        <v>234.28</v>
       </c>
       <c r="L28" t="n">
-        <v>417.91</v>
+        <v>236.41</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-41.51</v>
+        <v>-24.81</v>
       </c>
       <c r="K29" t="n">
-        <v>-52.9</v>
+        <v>-31.62</v>
       </c>
       <c r="L29" t="n">
-        <v>67.25</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>6.85</v>
+        <v>3.88</v>
       </c>
       <c r="K30" t="n">
-        <v>-85.64</v>
+        <v>-48.51</v>
       </c>
       <c r="L30" t="n">
-        <v>85.92</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>41.93</v>
+        <v>23.06</v>
       </c>
       <c r="K31" t="n">
-        <v>52.04</v>
+        <v>28.62</v>
       </c>
       <c r="L31" t="n">
-        <v>66.83</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>146.19</v>
+        <v>76.97</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.1</v>
+        <v>-3.21</v>
       </c>
       <c r="L32" t="n">
-        <v>146.32</v>
+        <v>77.04000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>57.39</v>
+        <v>34.66</v>
       </c>
       <c r="K33" t="n">
-        <v>-78.90000000000001</v>
+        <v>-47.64</v>
       </c>
       <c r="L33" t="n">
-        <v>97.56</v>
+        <v>58.91</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>41.52</v>
+        <v>23.09</v>
       </c>
       <c r="K34" t="n">
-        <v>-77.89</v>
+        <v>-43.31</v>
       </c>
       <c r="L34" t="n">
-        <v>88.26000000000001</v>
+        <v>49.08</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-136.98</v>
+        <v>-74.3</v>
       </c>
       <c r="K35" t="n">
-        <v>-194.66</v>
+        <v>-105.59</v>
       </c>
       <c r="L35" t="n">
-        <v>238.02</v>
+        <v>129.11</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-125.82</v>
+        <v>-65.13</v>
       </c>
       <c r="K36" t="n">
-        <v>69.65000000000001</v>
+        <v>36.05</v>
       </c>
       <c r="L36" t="n">
-        <v>143.81</v>
+        <v>74.44</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>219.12</v>
+        <v>114.32</v>
       </c>
       <c r="K37" t="n">
-        <v>-38.29</v>
+        <v>-19.97</v>
       </c>
       <c r="L37" t="n">
-        <v>222.44</v>
+        <v>116.05</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-119.02</v>
+        <v>-67.12</v>
       </c>
       <c r="K38" t="n">
-        <v>-176.29</v>
+        <v>-99.43000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>212.7</v>
+        <v>119.96</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>171</v>
+        <v>98.94</v>
       </c>
       <c r="K39" t="n">
-        <v>-68.25</v>
+        <v>-39.48</v>
       </c>
       <c r="L39" t="n">
-        <v>184.12</v>
+        <v>106.52</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>140.2</v>
+        <v>86.08</v>
       </c>
       <c r="K40" t="n">
-        <v>-70.61</v>
+        <v>-43.35</v>
       </c>
       <c r="L40" t="n">
-        <v>156.97</v>
+        <v>96.38</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-239.87</v>
+        <v>-134.9</v>
       </c>
       <c r="K41" t="n">
-        <v>-277.77</v>
+        <v>-156.21</v>
       </c>
       <c r="L41" t="n">
-        <v>367.01</v>
+        <v>206.4</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>419.66</v>
+        <v>244.4</v>
       </c>
       <c r="K42" t="n">
-        <v>-114.35</v>
+        <v>-66.59</v>
       </c>
       <c r="L42" t="n">
-        <v>434.96</v>
+        <v>253.31</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>262.49</v>
+        <v>155.25</v>
       </c>
       <c r="K43" t="n">
-        <v>285.37</v>
+        <v>168.78</v>
       </c>
       <c r="L43" t="n">
-        <v>387.73</v>
+        <v>229.33</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>44.8</v>
+        <v>24.17</v>
       </c>
       <c r="K44" t="n">
-        <v>157.79</v>
+        <v>85.12</v>
       </c>
       <c r="L44" t="n">
-        <v>164.03</v>
+        <v>88.48</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>16.63</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>75.66</v>
+        <v>41.49</v>
       </c>
       <c r="L45" t="n">
-        <v>77.45999999999999</v>
+        <v>42.48</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-131.52</v>
+        <v>-64.87</v>
       </c>
       <c r="K46" t="n">
-        <v>-41.36</v>
+        <v>-20.4</v>
       </c>
       <c r="L46" t="n">
-        <v>137.86</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>2.76</v>
+        <v>1.39</v>
       </c>
       <c r="K47" t="n">
-        <v>131.89</v>
+        <v>66.25</v>
       </c>
       <c r="L47" t="n">
-        <v>131.92</v>
+        <v>66.27</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>18.17</v>
+        <v>9.56</v>
       </c>
       <c r="K48" t="n">
-        <v>-224.38</v>
+        <v>-118.14</v>
       </c>
       <c r="L48" t="n">
-        <v>225.11</v>
+        <v>118.52</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-91.41</v>
+        <v>-44.49</v>
       </c>
       <c r="K49" t="n">
-        <v>-56.7</v>
+        <v>-27.6</v>
       </c>
       <c r="L49" t="n">
-        <v>107.56</v>
+        <v>52.35</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-134.14</v>
+        <v>-70.68000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>230.89</v>
+        <v>121.66</v>
       </c>
       <c r="L50" t="n">
-        <v>267.03</v>
+        <v>140.7</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.9</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-146.78</v>
+        <v>-74.2</v>
       </c>
       <c r="L51" t="n">
-        <v>147.64</v>
+        <v>74.64</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-131.34</v>
+        <v>-78.18000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>18.11</v>
+        <v>10.78</v>
       </c>
       <c r="L52" t="n">
-        <v>132.58</v>
+        <v>78.92</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>89.81</v>
+        <v>48.46</v>
       </c>
       <c r="K53" t="n">
-        <v>-249.24</v>
+        <v>-134.5</v>
       </c>
       <c r="L53" t="n">
-        <v>264.93</v>
+        <v>142.96</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-189.17</v>
+        <v>-114.72</v>
       </c>
       <c r="K54" t="n">
-        <v>35.48</v>
+        <v>21.52</v>
       </c>
       <c r="L54" t="n">
-        <v>192.47</v>
+        <v>116.72</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>241</v>
+        <v>132.91</v>
       </c>
       <c r="K55" t="n">
-        <v>109.07</v>
+        <v>60.15</v>
       </c>
       <c r="L55" t="n">
-        <v>264.54</v>
+        <v>145.89</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>265.38</v>
+        <v>149.51</v>
       </c>
       <c r="K56" t="n">
-        <v>153.78</v>
+        <v>86.64</v>
       </c>
       <c r="L56" t="n">
-        <v>306.72</v>
+        <v>172.79</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-16.79</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>250.66</v>
+        <v>138.73</v>
       </c>
       <c r="L57" t="n">
-        <v>251.22</v>
+        <v>139.04</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-301.37</v>
+        <v>-174.04</v>
       </c>
       <c r="K58" t="n">
-        <v>-377.78</v>
+        <v>-218.16</v>
       </c>
       <c r="L58" t="n">
-        <v>483.26</v>
+        <v>279.07</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-84.84999999999999</v>
+        <v>-42.35</v>
       </c>
       <c r="K59" t="n">
-        <v>31.03</v>
+        <v>15.49</v>
       </c>
       <c r="L59" t="n">
-        <v>90.34</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>96.95999999999999</v>
+        <v>54.41</v>
       </c>
       <c r="K60" t="n">
-        <v>18.59</v>
+        <v>10.43</v>
       </c>
       <c r="L60" t="n">
-        <v>98.72</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-151.09</v>
+        <v>-82.18000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>47.68</v>
+        <v>25.94</v>
       </c>
       <c r="L61" t="n">
-        <v>158.43</v>
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>44.34</v>
+        <v>24.61</v>
       </c>
       <c r="K62" t="n">
-        <v>85.86</v>
+        <v>47.66</v>
       </c>
       <c r="L62" t="n">
-        <v>96.63</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-6.14</v>
+        <v>-1.74</v>
       </c>
       <c r="K63" t="n">
-        <v>-74.73</v>
+        <v>-21.17</v>
       </c>
       <c r="L63" t="n">
-        <v>74.98</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>85.98999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="K64" t="n">
-        <v>77.52</v>
+        <v>37.95</v>
       </c>
       <c r="L64" t="n">
-        <v>115.77</v>
+        <v>56.68</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-172.04</v>
+        <v>-85.19</v>
       </c>
       <c r="K65" t="n">
-        <v>-131.1</v>
+        <v>-64.92</v>
       </c>
       <c r="L65" t="n">
-        <v>216.3</v>
+        <v>107.11</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-256.01</v>
+        <v>-129.41</v>
       </c>
       <c r="K66" t="n">
-        <v>-18.41</v>
+        <v>-9.31</v>
       </c>
       <c r="L66" t="n">
-        <v>256.67</v>
+        <v>129.75</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-128.9</v>
+        <v>-63.76</v>
       </c>
       <c r="K67" t="n">
-        <v>60.54</v>
+        <v>29.95</v>
       </c>
       <c r="L67" t="n">
-        <v>142.41</v>
+        <v>70.45</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-39.96</v>
+        <v>-18.3</v>
       </c>
       <c r="K68" t="n">
-        <v>-129.67</v>
+        <v>-59.38</v>
       </c>
       <c r="L68" t="n">
-        <v>135.69</v>
+        <v>62.14</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-33.66</v>
+        <v>-19.07</v>
       </c>
       <c r="K69" t="n">
-        <v>329.2</v>
+        <v>186.51</v>
       </c>
       <c r="L69" t="n">
-        <v>330.91</v>
+        <v>187.49</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>406.7</v>
+        <v>222.81</v>
       </c>
       <c r="K70" t="n">
-        <v>65.14</v>
+        <v>35.69</v>
       </c>
       <c r="L70" t="n">
-        <v>411.88</v>
+        <v>225.65</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>153.58</v>
+        <v>85.31999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>277.48</v>
+        <v>154.15</v>
       </c>
       <c r="L71" t="n">
-        <v>317.14</v>
+        <v>176.18</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-422.46</v>
+        <v>-233.33</v>
       </c>
       <c r="K72" t="n">
-        <v>-73.68000000000001</v>
+        <v>-40.7</v>
       </c>
       <c r="L72" t="n">
-        <v>428.84</v>
+        <v>236.86</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-126.55</v>
+        <v>-70.88</v>
       </c>
       <c r="K73" t="n">
-        <v>241.68</v>
+        <v>135.37</v>
       </c>
       <c r="L73" t="n">
-        <v>272.81</v>
+        <v>152.81</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>47.98</v>
+        <v>23.72</v>
       </c>
       <c r="K74" t="n">
-        <v>-140.62</v>
+        <v>-69.52</v>
       </c>
       <c r="L74" t="n">
-        <v>148.58</v>
+        <v>73.45999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>103.3</v>
+        <v>53.95</v>
       </c>
       <c r="K75" t="n">
-        <v>-25.33</v>
+        <v>-13.23</v>
       </c>
       <c r="L75" t="n">
-        <v>106.36</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-52.78</v>
+        <v>-27.01</v>
       </c>
       <c r="K76" t="n">
-        <v>-56.2</v>
+        <v>-28.76</v>
       </c>
       <c r="L76" t="n">
-        <v>77.09999999999999</v>
+        <v>39.45</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-64.43000000000001</v>
+        <v>-37.19</v>
       </c>
       <c r="K77" t="n">
-        <v>77.28</v>
+        <v>44.61</v>
       </c>
       <c r="L77" t="n">
-        <v>100.61</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-66.33</v>
+        <v>-31.34</v>
       </c>
       <c r="K78" t="n">
-        <v>104.28</v>
+        <v>49.27</v>
       </c>
       <c r="L78" t="n">
-        <v>123.58</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>6.1</v>
+        <v>3.12</v>
       </c>
       <c r="K79" t="n">
-        <v>-142.94</v>
+        <v>-73</v>
       </c>
       <c r="L79" t="n">
-        <v>143.07</v>
+        <v>73.06999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>76.59999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="K80" t="n">
-        <v>51.41</v>
+        <v>1.48</v>
       </c>
       <c r="L80" t="n">
-        <v>92.25</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-108.09</v>
+        <v>-55.47</v>
       </c>
       <c r="K81" t="n">
-        <v>-192.18</v>
+        <v>-98.63</v>
       </c>
       <c r="L81" t="n">
-        <v>220.5</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-179.23</v>
+        <v>-90.44</v>
       </c>
       <c r="K82" t="n">
-        <v>-180.2</v>
+        <v>-90.93000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>254.16</v>
+        <v>128.25</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-182.73</v>
+        <v>-94.03</v>
       </c>
       <c r="K83" t="n">
-        <v>-218.35</v>
+        <v>-112.36</v>
       </c>
       <c r="L83" t="n">
-        <v>284.72</v>
+        <v>146.52</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-169.06</v>
+        <v>-92.62</v>
       </c>
       <c r="K84" t="n">
-        <v>222.92</v>
+        <v>122.13</v>
       </c>
       <c r="L84" t="n">
-        <v>279.78</v>
+        <v>153.28</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>63.25</v>
+        <v>35.27</v>
       </c>
       <c r="K85" t="n">
-        <v>234.37</v>
+        <v>130.7</v>
       </c>
       <c r="L85" t="n">
-        <v>242.75</v>
+        <v>135.37</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>186.36</v>
+        <v>102.56</v>
       </c>
       <c r="K86" t="n">
-        <v>-223.8</v>
+        <v>-123.17</v>
       </c>
       <c r="L86" t="n">
-        <v>291.24</v>
+        <v>160.28</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-212.25</v>
+        <v>-114.52</v>
       </c>
       <c r="K87" t="n">
-        <v>139.92</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>254.22</v>
+        <v>137.16</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-354.27</v>
+        <v>-197.88</v>
       </c>
       <c r="K88" t="n">
-        <v>-101.66</v>
+        <v>-56.78</v>
       </c>
       <c r="L88" t="n">
-        <v>368.57</v>
+        <v>205.87</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>66.73</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-20</v>
+        <v>-19.9</v>
       </c>
       <c r="L14" t="n">
-        <v>69.66</v>
+        <v>69.31999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-54.24</v>
+        <v>-54.89</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.529999999999999</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>54.91</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>106.26</v>
+        <v>100.73</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.4</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>106.77</v>
+        <v>101.21</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>34.43</v>
+        <v>35.11</v>
       </c>
       <c r="K17" t="n">
-        <v>-57.82</v>
+        <v>-58.97</v>
       </c>
       <c r="L17" t="n">
-        <v>67.29000000000001</v>
+        <v>68.63</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>76.04000000000001</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>5.65</v>
+        <v>5.57</v>
       </c>
       <c r="L18" t="n">
-        <v>76.25</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>33.18</v>
+        <v>33.38</v>
       </c>
       <c r="K19" t="n">
-        <v>55.57</v>
+        <v>55.91</v>
       </c>
       <c r="L19" t="n">
-        <v>64.72</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-152.05</v>
+        <v>-145.09</v>
       </c>
       <c r="K20" t="n">
-        <v>-55.76</v>
+        <v>-53.21</v>
       </c>
       <c r="L20" t="n">
-        <v>161.95</v>
+        <v>154.54</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>14.01</v>
+        <v>14.05</v>
       </c>
       <c r="K21" t="n">
-        <v>93.70999999999999</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>94.75</v>
+        <v>95.03</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>19.69</v>
+        <v>19.11</v>
       </c>
       <c r="K22" t="n">
-        <v>130.05</v>
+        <v>126.22</v>
       </c>
       <c r="L22" t="n">
-        <v>131.53</v>
+        <v>127.66</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-89.87</v>
+        <v>-88.67</v>
       </c>
       <c r="K23" t="n">
-        <v>-123.87</v>
+        <v>-122.21</v>
       </c>
       <c r="L23" t="n">
-        <v>153.03</v>
+        <v>150.99</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-167.11</v>
+        <v>-162.17</v>
       </c>
       <c r="K24" t="n">
-        <v>-106.58</v>
+        <v>-103.43</v>
       </c>
       <c r="L24" t="n">
-        <v>198.2</v>
+        <v>192.35</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-53.98</v>
+        <v>-55.77</v>
       </c>
       <c r="K25" t="n">
-        <v>-99.64</v>
+        <v>-102.94</v>
       </c>
       <c r="L25" t="n">
-        <v>113.32</v>
+        <v>117.08</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-78.59999999999999</v>
+        <v>-80.23</v>
       </c>
       <c r="K26" t="n">
-        <v>133.24</v>
+        <v>136</v>
       </c>
       <c r="L26" t="n">
-        <v>154.69</v>
+        <v>157.9</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-146.38</v>
+        <v>-146.22</v>
       </c>
       <c r="K27" t="n">
-        <v>-103.66</v>
+        <v>-103.55</v>
       </c>
       <c r="L27" t="n">
-        <v>179.37</v>
+        <v>179.17</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>31.72</v>
+        <v>30.96</v>
       </c>
       <c r="K28" t="n">
-        <v>234.28</v>
+        <v>228.66</v>
       </c>
       <c r="L28" t="n">
-        <v>236.41</v>
+        <v>230.74</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-24.81</v>
+        <v>-25.97</v>
       </c>
       <c r="K29" t="n">
-        <v>-31.62</v>
+        <v>-33.09</v>
       </c>
       <c r="L29" t="n">
-        <v>40.2</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>-48.51</v>
+        <v>-50.03</v>
       </c>
       <c r="L30" t="n">
-        <v>48.66</v>
+        <v>50.19</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>23.06</v>
+        <v>24.87</v>
       </c>
       <c r="K31" t="n">
-        <v>28.62</v>
+        <v>30.87</v>
       </c>
       <c r="L31" t="n">
-        <v>36.75</v>
+        <v>39.65</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>76.97</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.21</v>
+        <v>-3.16</v>
       </c>
       <c r="L32" t="n">
-        <v>77.04000000000001</v>
+        <v>75.75</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>34.66</v>
+        <v>35.53</v>
       </c>
       <c r="K33" t="n">
-        <v>-47.64</v>
+        <v>-48.85</v>
       </c>
       <c r="L33" t="n">
-        <v>58.91</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>23.09</v>
+        <v>24.29</v>
       </c>
       <c r="K34" t="n">
-        <v>-43.31</v>
+        <v>-45.55</v>
       </c>
       <c r="L34" t="n">
-        <v>49.08</v>
+        <v>51.62</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-74.3</v>
+        <v>-72.06999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-105.59</v>
+        <v>-102.42</v>
       </c>
       <c r="L35" t="n">
-        <v>129.11</v>
+        <v>125.23</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-65.13</v>
+        <v>-67.48999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>36.05</v>
+        <v>37.36</v>
       </c>
       <c r="L36" t="n">
-        <v>74.44</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>114.32</v>
+        <v>112.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-19.97</v>
+        <v>-19.71</v>
       </c>
       <c r="L37" t="n">
-        <v>116.05</v>
+        <v>114.51</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-67.12</v>
+        <v>-69.3</v>
       </c>
       <c r="K38" t="n">
-        <v>-99.43000000000001</v>
+        <v>-102.65</v>
       </c>
       <c r="L38" t="n">
-        <v>119.96</v>
+        <v>123.85</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>98.94</v>
+        <v>102.58</v>
       </c>
       <c r="K39" t="n">
-        <v>-39.48</v>
+        <v>-40.94</v>
       </c>
       <c r="L39" t="n">
-        <v>106.52</v>
+        <v>110.45</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>86.08</v>
+        <v>89.47</v>
       </c>
       <c r="K40" t="n">
-        <v>-43.35</v>
+        <v>-45.06</v>
       </c>
       <c r="L40" t="n">
-        <v>96.38</v>
+        <v>100.17</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-134.9</v>
+        <v>-134.8</v>
       </c>
       <c r="K41" t="n">
-        <v>-156.21</v>
+        <v>-156.1</v>
       </c>
       <c r="L41" t="n">
-        <v>206.4</v>
+        <v>206.25</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>244.4</v>
+        <v>237.5</v>
       </c>
       <c r="K42" t="n">
-        <v>-66.59</v>
+        <v>-64.72</v>
       </c>
       <c r="L42" t="n">
-        <v>253.31</v>
+        <v>246.16</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>155.25</v>
+        <v>150.43</v>
       </c>
       <c r="K43" t="n">
-        <v>168.78</v>
+        <v>163.54</v>
       </c>
       <c r="L43" t="n">
-        <v>229.33</v>
+        <v>222.21</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>24.17</v>
+        <v>23.37</v>
       </c>
       <c r="K44" t="n">
-        <v>85.12</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>88.48</v>
+        <v>85.58</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>9.119999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>41.49</v>
+        <v>43.44</v>
       </c>
       <c r="L45" t="n">
-        <v>42.48</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-64.87</v>
+        <v>-63.47</v>
       </c>
       <c r="K46" t="n">
-        <v>-20.4</v>
+        <v>-19.96</v>
       </c>
       <c r="L46" t="n">
-        <v>68</v>
+        <v>66.53</v>
       </c>
     </row>
     <row r="47">
@@ -2029,10 +2029,10 @@
         <v>1.39</v>
       </c>
       <c r="K47" t="n">
-        <v>66.25</v>
+        <v>66.36</v>
       </c>
       <c r="L47" t="n">
-        <v>66.27</v>
+        <v>66.37</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>9.56</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-118.14</v>
+        <v>-111.74</v>
       </c>
       <c r="L48" t="n">
-        <v>118.52</v>
+        <v>112.1</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-44.49</v>
+        <v>-45.87</v>
       </c>
       <c r="K49" t="n">
-        <v>-27.6</v>
+        <v>-28.45</v>
       </c>
       <c r="L49" t="n">
-        <v>52.35</v>
+        <v>53.97</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-70.68000000000001</v>
+        <v>-68.48</v>
       </c>
       <c r="K50" t="n">
-        <v>121.66</v>
+        <v>117.87</v>
       </c>
       <c r="L50" t="n">
-        <v>140.7</v>
+        <v>136.32</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.039999999999999</v>
+        <v>-8.52</v>
       </c>
       <c r="K51" t="n">
-        <v>-74.2</v>
+        <v>-78.69</v>
       </c>
       <c r="L51" t="n">
-        <v>74.64</v>
+        <v>79.15000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-78.18000000000001</v>
+        <v>-79.90000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>10.78</v>
+        <v>11.02</v>
       </c>
       <c r="L52" t="n">
-        <v>78.92</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>48.46</v>
+        <v>48.84</v>
       </c>
       <c r="K53" t="n">
-        <v>-134.5</v>
+        <v>-135.53</v>
       </c>
       <c r="L53" t="n">
-        <v>142.96</v>
+        <v>144.06</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-114.72</v>
+        <v>-117.25</v>
       </c>
       <c r="K54" t="n">
-        <v>21.52</v>
+        <v>21.99</v>
       </c>
       <c r="L54" t="n">
-        <v>116.72</v>
+        <v>119.29</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>132.91</v>
+        <v>132.72</v>
       </c>
       <c r="K55" t="n">
-        <v>60.15</v>
+        <v>60.06</v>
       </c>
       <c r="L55" t="n">
-        <v>145.89</v>
+        <v>145.67</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>149.51</v>
+        <v>151.28</v>
       </c>
       <c r="K56" t="n">
-        <v>86.64</v>
+        <v>87.67</v>
       </c>
       <c r="L56" t="n">
-        <v>172.79</v>
+        <v>174.85</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-9.289999999999999</v>
+        <v>-10.09</v>
       </c>
       <c r="K57" t="n">
-        <v>138.73</v>
+        <v>150.75</v>
       </c>
       <c r="L57" t="n">
-        <v>139.04</v>
+        <v>151.09</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-174.04</v>
+        <v>-167.84</v>
       </c>
       <c r="K58" t="n">
-        <v>-218.16</v>
+        <v>-210.39</v>
       </c>
       <c r="L58" t="n">
-        <v>279.07</v>
+        <v>269.14</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-42.35</v>
+        <v>-43.95</v>
       </c>
       <c r="K59" t="n">
-        <v>15.49</v>
+        <v>16.07</v>
       </c>
       <c r="L59" t="n">
-        <v>45.1</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>54.41</v>
+        <v>54.94</v>
       </c>
       <c r="K60" t="n">
-        <v>10.43</v>
+        <v>10.53</v>
       </c>
       <c r="L60" t="n">
-        <v>55.4</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-82.18000000000001</v>
+        <v>-80.04000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>25.94</v>
+        <v>25.26</v>
       </c>
       <c r="L61" t="n">
-        <v>86.18000000000001</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>24.61</v>
+        <v>25.75</v>
       </c>
       <c r="K62" t="n">
-        <v>47.66</v>
+        <v>49.85</v>
       </c>
       <c r="L62" t="n">
-        <v>53.64</v>
+        <v>56.11</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.74</v>
+        <v>-1.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-21.17</v>
+        <v>-20.67</v>
       </c>
       <c r="L63" t="n">
-        <v>21.24</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>42.1</v>
+        <v>43.55</v>
       </c>
       <c r="K64" t="n">
-        <v>37.95</v>
+        <v>39.26</v>
       </c>
       <c r="L64" t="n">
-        <v>56.68</v>
+        <v>58.63</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-85.19</v>
+        <v>-85.93000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-64.92</v>
+        <v>-65.48</v>
       </c>
       <c r="L65" t="n">
-        <v>107.11</v>
+        <v>108.03</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-129.41</v>
+        <v>-127.33</v>
       </c>
       <c r="K66" t="n">
-        <v>-9.31</v>
+        <v>-9.16</v>
       </c>
       <c r="L66" t="n">
-        <v>129.75</v>
+        <v>127.66</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-63.76</v>
+        <v>-68.93000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>29.95</v>
+        <v>32.37</v>
       </c>
       <c r="L67" t="n">
-        <v>70.45</v>
+        <v>76.15000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-18.3</v>
+        <v>-17.9</v>
       </c>
       <c r="K68" t="n">
-        <v>-59.38</v>
+        <v>-58.09</v>
       </c>
       <c r="L68" t="n">
-        <v>62.14</v>
+        <v>60.79</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-19.07</v>
+        <v>-18.66</v>
       </c>
       <c r="K69" t="n">
-        <v>186.51</v>
+        <v>182.51</v>
       </c>
       <c r="L69" t="n">
-        <v>187.49</v>
+        <v>183.46</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>222.81</v>
+        <v>214.64</v>
       </c>
       <c r="K70" t="n">
-        <v>35.69</v>
+        <v>34.38</v>
       </c>
       <c r="L70" t="n">
-        <v>225.65</v>
+        <v>217.37</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>85.31999999999999</v>
+        <v>89.56</v>
       </c>
       <c r="K71" t="n">
-        <v>154.15</v>
+        <v>161.81</v>
       </c>
       <c r="L71" t="n">
-        <v>176.18</v>
+        <v>184.94</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-233.33</v>
+        <v>-235.27</v>
       </c>
       <c r="K72" t="n">
-        <v>-40.7</v>
+        <v>-41.03</v>
       </c>
       <c r="L72" t="n">
-        <v>236.86</v>
+        <v>238.82</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-70.88</v>
+        <v>-74.8</v>
       </c>
       <c r="K73" t="n">
-        <v>135.37</v>
+        <v>142.85</v>
       </c>
       <c r="L73" t="n">
-        <v>152.81</v>
+        <v>161.25</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>23.72</v>
+        <v>23</v>
       </c>
       <c r="K74" t="n">
-        <v>-69.52</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>73.45999999999999</v>
+        <v>71.20999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>53.95</v>
+        <v>54.34</v>
       </c>
       <c r="K75" t="n">
-        <v>-13.23</v>
+        <v>-13.32</v>
       </c>
       <c r="L75" t="n">
-        <v>55.55</v>
+        <v>55.95</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-27.01</v>
+        <v>-28.66</v>
       </c>
       <c r="K76" t="n">
-        <v>-28.76</v>
+        <v>-30.51</v>
       </c>
       <c r="L76" t="n">
-        <v>39.45</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-37.19</v>
+        <v>-38.29</v>
       </c>
       <c r="K77" t="n">
-        <v>44.61</v>
+        <v>45.93</v>
       </c>
       <c r="L77" t="n">
-        <v>58.08</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-31.34</v>
+        <v>-31.79</v>
       </c>
       <c r="K78" t="n">
-        <v>49.27</v>
+        <v>49.98</v>
       </c>
       <c r="L78" t="n">
-        <v>58.4</v>
+        <v>59.24</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="K79" t="n">
-        <v>-73</v>
+        <v>-72.25</v>
       </c>
       <c r="L79" t="n">
-        <v>73.06999999999999</v>
+        <v>72.31999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="K80" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="L80" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-55.47</v>
+        <v>-55.07</v>
       </c>
       <c r="K81" t="n">
-        <v>-98.63</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>113.16</v>
+        <v>112.33</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-90.44</v>
+        <v>-88.14</v>
       </c>
       <c r="K82" t="n">
-        <v>-90.93000000000001</v>
+        <v>-88.61</v>
       </c>
       <c r="L82" t="n">
-        <v>128.25</v>
+        <v>124.98</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-94.03</v>
+        <v>-95.31999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-112.36</v>
+        <v>-113.9</v>
       </c>
       <c r="L83" t="n">
-        <v>146.52</v>
+        <v>148.53</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-92.62</v>
+        <v>-92.90000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>122.13</v>
+        <v>122.5</v>
       </c>
       <c r="L84" t="n">
-        <v>153.28</v>
+        <v>153.74</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>35.27</v>
+        <v>35.53</v>
       </c>
       <c r="K85" t="n">
-        <v>130.7</v>
+        <v>131.65</v>
       </c>
       <c r="L85" t="n">
-        <v>135.37</v>
+        <v>136.37</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>102.56</v>
+        <v>105.99</v>
       </c>
       <c r="K86" t="n">
-        <v>-123.17</v>
+        <v>-127.28</v>
       </c>
       <c r="L86" t="n">
-        <v>160.28</v>
+        <v>165.63</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-114.52</v>
+        <v>-130.13</v>
       </c>
       <c r="K87" t="n">
-        <v>75.48999999999999</v>
+        <v>85.78</v>
       </c>
       <c r="L87" t="n">
-        <v>137.16</v>
+        <v>155.86</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-197.88</v>
+        <v>-200.11</v>
       </c>
       <c r="K88" t="n">
-        <v>-56.78</v>
+        <v>-57.42</v>
       </c>
       <c r="L88" t="n">
-        <v>205.87</v>
+        <v>208.18</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>66.40000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-19.9</v>
+        <v>-19.82</v>
       </c>
       <c r="L14" t="n">
-        <v>69.31999999999999</v>
+        <v>69.06</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-54.89</v>
+        <v>-55.63</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.640000000000001</v>
+        <v>-8.75</v>
       </c>
       <c r="L15" t="n">
-        <v>55.57</v>
+        <v>56.32</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>100.73</v>
+        <v>94.58</v>
       </c>
       <c r="K16" t="n">
-        <v>-9.859999999999999</v>
+        <v>-9.26</v>
       </c>
       <c r="L16" t="n">
-        <v>101.21</v>
+        <v>95.04000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>35.11</v>
+        <v>35.89</v>
       </c>
       <c r="K17" t="n">
-        <v>-58.97</v>
+        <v>-60.28</v>
       </c>
       <c r="L17" t="n">
-        <v>68.63</v>
+        <v>70.16</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>74.98999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>5.57</v>
+        <v>5.48</v>
       </c>
       <c r="L18" t="n">
-        <v>75.2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>33.38</v>
+        <v>33.62</v>
       </c>
       <c r="K19" t="n">
-        <v>55.91</v>
+        <v>56.3</v>
       </c>
       <c r="L19" t="n">
-        <v>65.12</v>
+        <v>65.56999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-145.09</v>
+        <v>-137.14</v>
       </c>
       <c r="K20" t="n">
-        <v>-53.21</v>
+        <v>-50.29</v>
       </c>
       <c r="L20" t="n">
-        <v>154.54</v>
+        <v>146.07</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>14.05</v>
+        <v>14.1</v>
       </c>
       <c r="K21" t="n">
-        <v>93.98999999999999</v>
+        <v>94.31</v>
       </c>
       <c r="L21" t="n">
-        <v>95.03</v>
+        <v>95.36</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>19.11</v>
+        <v>18.51</v>
       </c>
       <c r="K22" t="n">
-        <v>126.22</v>
+        <v>122.23</v>
       </c>
       <c r="L22" t="n">
-        <v>127.66</v>
+        <v>123.62</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-88.67</v>
+        <v>-87.28</v>
       </c>
       <c r="K23" t="n">
-        <v>-122.21</v>
+        <v>-120.3</v>
       </c>
       <c r="L23" t="n">
-        <v>150.99</v>
+        <v>148.63</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-162.17</v>
+        <v>-155.83</v>
       </c>
       <c r="K24" t="n">
-        <v>-103.43</v>
+        <v>-99.39</v>
       </c>
       <c r="L24" t="n">
-        <v>192.35</v>
+        <v>184.83</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-55.77</v>
+        <v>-57.81</v>
       </c>
       <c r="K25" t="n">
-        <v>-102.94</v>
+        <v>-106.72</v>
       </c>
       <c r="L25" t="n">
-        <v>117.08</v>
+        <v>121.37</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-80.23</v>
+        <v>-82.09</v>
       </c>
       <c r="K26" t="n">
-        <v>136</v>
+        <v>139.16</v>
       </c>
       <c r="L26" t="n">
-        <v>157.9</v>
+        <v>161.56</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-146.22</v>
+        <v>-146.03</v>
       </c>
       <c r="K27" t="n">
-        <v>-103.55</v>
+        <v>-103.41</v>
       </c>
       <c r="L27" t="n">
-        <v>179.17</v>
+        <v>178.94</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>30.96</v>
+        <v>30.01</v>
       </c>
       <c r="K28" t="n">
-        <v>228.66</v>
+        <v>221.65</v>
       </c>
       <c r="L28" t="n">
-        <v>230.74</v>
+        <v>223.67</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-25.97</v>
+        <v>-27.29</v>
       </c>
       <c r="K29" t="n">
-        <v>-33.09</v>
+        <v>-34.78</v>
       </c>
       <c r="L29" t="n">
-        <v>42.07</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="K30" t="n">
-        <v>-50.03</v>
+        <v>-51.77</v>
       </c>
       <c r="L30" t="n">
-        <v>50.19</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>24.87</v>
+        <v>26.95</v>
       </c>
       <c r="K31" t="n">
-        <v>30.87</v>
+        <v>33.45</v>
       </c>
       <c r="L31" t="n">
-        <v>39.65</v>
+        <v>42.95</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>75.68000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.16</v>
+        <v>-3.11</v>
       </c>
       <c r="L32" t="n">
-        <v>75.75</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>35.53</v>
+        <v>36.54</v>
       </c>
       <c r="K33" t="n">
-        <v>-48.85</v>
+        <v>-50.23</v>
       </c>
       <c r="L33" t="n">
-        <v>60.41</v>
+        <v>62.11</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>24.29</v>
+        <v>25.65</v>
       </c>
       <c r="K34" t="n">
-        <v>-45.55</v>
+        <v>-48.12</v>
       </c>
       <c r="L34" t="n">
-        <v>51.62</v>
+        <v>54.53</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-72.06999999999999</v>
+        <v>-69.52</v>
       </c>
       <c r="K35" t="n">
-        <v>-102.42</v>
+        <v>-98.8</v>
       </c>
       <c r="L35" t="n">
-        <v>125.23</v>
+        <v>120.81</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-67.48999999999999</v>
+        <v>-70.19</v>
       </c>
       <c r="K36" t="n">
-        <v>37.36</v>
+        <v>38.85</v>
       </c>
       <c r="L36" t="n">
-        <v>77.14</v>
+        <v>80.22</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>112.8</v>
+        <v>111.06</v>
       </c>
       <c r="K37" t="n">
-        <v>-19.71</v>
+        <v>-19.41</v>
       </c>
       <c r="L37" t="n">
-        <v>114.51</v>
+        <v>112.75</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-69.3</v>
+        <v>-71.73</v>
       </c>
       <c r="K38" t="n">
-        <v>-102.65</v>
+        <v>-106.24</v>
       </c>
       <c r="L38" t="n">
-        <v>123.85</v>
+        <v>128.19</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>102.58</v>
+        <v>106.74</v>
       </c>
       <c r="K39" t="n">
-        <v>-40.94</v>
+        <v>-42.6</v>
       </c>
       <c r="L39" t="n">
-        <v>110.45</v>
+        <v>114.93</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>89.47</v>
+        <v>93.34</v>
       </c>
       <c r="K40" t="n">
-        <v>-45.06</v>
+        <v>-47.01</v>
       </c>
       <c r="L40" t="n">
-        <v>100.17</v>
+        <v>104.51</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-134.8</v>
+        <v>-133.52</v>
       </c>
       <c r="K41" t="n">
-        <v>-156.1</v>
+        <v>-154.62</v>
       </c>
       <c r="L41" t="n">
-        <v>206.25</v>
+        <v>204.29</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>237.5</v>
+        <v>229.62</v>
       </c>
       <c r="K42" t="n">
-        <v>-64.72</v>
+        <v>-62.57</v>
       </c>
       <c r="L42" t="n">
-        <v>246.16</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>150.43</v>
+        <v>144.92</v>
       </c>
       <c r="K43" t="n">
-        <v>163.54</v>
+        <v>157.55</v>
       </c>
       <c r="L43" t="n">
-        <v>222.21</v>
+        <v>214.07</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>23.37</v>
+        <v>22.5</v>
       </c>
       <c r="K44" t="n">
-        <v>82.31999999999999</v>
+        <v>79.25</v>
       </c>
       <c r="L44" t="n">
-        <v>85.58</v>
+        <v>82.38</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>9.550000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="K45" t="n">
-        <v>43.44</v>
+        <v>45.68</v>
       </c>
       <c r="L45" t="n">
-        <v>44.48</v>
+        <v>46.77</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-63.47</v>
+        <v>-62.72</v>
       </c>
       <c r="K46" t="n">
-        <v>-19.96</v>
+        <v>-19.72</v>
       </c>
       <c r="L46" t="n">
-        <v>66.53</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="K47" t="n">
-        <v>66.36</v>
+        <v>67.22</v>
       </c>
       <c r="L47" t="n">
-        <v>66.37</v>
+        <v>67.23999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>9.050000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="K48" t="n">
-        <v>-111.74</v>
+        <v>-104.88</v>
       </c>
       <c r="L48" t="n">
-        <v>112.1</v>
+        <v>105.22</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-45.87</v>
+        <v>-48.17</v>
       </c>
       <c r="K49" t="n">
-        <v>-28.45</v>
+        <v>-29.88</v>
       </c>
       <c r="L49" t="n">
-        <v>53.97</v>
+        <v>56.68</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-68.48</v>
+        <v>-65.97</v>
       </c>
       <c r="K50" t="n">
-        <v>117.87</v>
+        <v>113.54</v>
       </c>
       <c r="L50" t="n">
-        <v>136.32</v>
+        <v>131.32</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.52</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-78.69</v>
+        <v>-84.11</v>
       </c>
       <c r="L51" t="n">
-        <v>79.15000000000001</v>
+        <v>84.61</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-79.90000000000001</v>
+        <v>-81.86</v>
       </c>
       <c r="K52" t="n">
-        <v>11.02</v>
+        <v>11.29</v>
       </c>
       <c r="L52" t="n">
-        <v>80.65000000000001</v>
+        <v>82.63</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>48.84</v>
+        <v>49.13</v>
       </c>
       <c r="K53" t="n">
-        <v>-135.53</v>
+        <v>-136.36</v>
       </c>
       <c r="L53" t="n">
-        <v>144.06</v>
+        <v>144.94</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-117.25</v>
+        <v>-120.14</v>
       </c>
       <c r="K54" t="n">
-        <v>21.99</v>
+        <v>22.53</v>
       </c>
       <c r="L54" t="n">
-        <v>119.29</v>
+        <v>122.23</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>132.72</v>
+        <v>132.26</v>
       </c>
       <c r="K55" t="n">
-        <v>60.06</v>
+        <v>59.85</v>
       </c>
       <c r="L55" t="n">
-        <v>145.67</v>
+        <v>145.17</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>151.28</v>
+        <v>152.3</v>
       </c>
       <c r="K56" t="n">
-        <v>87.67</v>
+        <v>88.25</v>
       </c>
       <c r="L56" t="n">
-        <v>174.85</v>
+        <v>176.02</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-10.09</v>
+        <v>-10.78</v>
       </c>
       <c r="K57" t="n">
-        <v>150.75</v>
+        <v>161.01</v>
       </c>
       <c r="L57" t="n">
-        <v>151.09</v>
+        <v>161.37</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-167.84</v>
+        <v>-160.75</v>
       </c>
       <c r="K58" t="n">
-        <v>-210.39</v>
+        <v>-201.51</v>
       </c>
       <c r="L58" t="n">
-        <v>269.14</v>
+        <v>257.78</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-43.95</v>
+        <v>-46.25</v>
       </c>
       <c r="K59" t="n">
-        <v>16.07</v>
+        <v>16.91</v>
       </c>
       <c r="L59" t="n">
-        <v>46.8</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>54.94</v>
+        <v>55.55</v>
       </c>
       <c r="K60" t="n">
-        <v>10.53</v>
+        <v>10.65</v>
       </c>
       <c r="L60" t="n">
-        <v>55.94</v>
+        <v>56.56</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-80.04000000000001</v>
+        <v>-77.63</v>
       </c>
       <c r="K61" t="n">
-        <v>25.26</v>
+        <v>24.5</v>
       </c>
       <c r="L61" t="n">
-        <v>83.94</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>25.75</v>
+        <v>27.04</v>
       </c>
       <c r="K62" t="n">
-        <v>49.85</v>
+        <v>52.36</v>
       </c>
       <c r="L62" t="n">
-        <v>56.11</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.7</v>
+        <v>-1.84</v>
       </c>
       <c r="K63" t="n">
-        <v>-20.67</v>
+        <v>-22.41</v>
       </c>
       <c r="L63" t="n">
-        <v>20.74</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>43.55</v>
+        <v>45.86</v>
       </c>
       <c r="K64" t="n">
-        <v>39.26</v>
+        <v>41.34</v>
       </c>
       <c r="L64" t="n">
-        <v>58.63</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-85.93000000000001</v>
+        <v>-87.45</v>
       </c>
       <c r="K65" t="n">
-        <v>-65.48</v>
+        <v>-66.64</v>
       </c>
       <c r="L65" t="n">
-        <v>108.03</v>
+        <v>109.95</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-127.33</v>
+        <v>-125.45</v>
       </c>
       <c r="K66" t="n">
-        <v>-9.16</v>
+        <v>-9.02</v>
       </c>
       <c r="L66" t="n">
-        <v>127.66</v>
+        <v>125.78</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-68.93000000000001</v>
+        <v>-75.34999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>32.37</v>
+        <v>35.39</v>
       </c>
       <c r="L67" t="n">
-        <v>76.15000000000001</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-17.9</v>
+        <v>-19.62</v>
       </c>
       <c r="K68" t="n">
-        <v>-58.09</v>
+        <v>-63.66</v>
       </c>
       <c r="L68" t="n">
-        <v>60.79</v>
+        <v>66.61</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-18.66</v>
+        <v>-18.18</v>
       </c>
       <c r="K69" t="n">
-        <v>182.51</v>
+        <v>177.79</v>
       </c>
       <c r="L69" t="n">
-        <v>183.46</v>
+        <v>178.71</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>214.64</v>
+        <v>204.84</v>
       </c>
       <c r="K70" t="n">
-        <v>34.38</v>
+        <v>32.81</v>
       </c>
       <c r="L70" t="n">
-        <v>217.37</v>
+        <v>207.45</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>89.56</v>
+        <v>92.58</v>
       </c>
       <c r="K71" t="n">
-        <v>161.81</v>
+        <v>167.27</v>
       </c>
       <c r="L71" t="n">
-        <v>184.94</v>
+        <v>191.19</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-235.27</v>
+        <v>-231.03</v>
       </c>
       <c r="K72" t="n">
-        <v>-41.03</v>
+        <v>-40.29</v>
       </c>
       <c r="L72" t="n">
-        <v>238.82</v>
+        <v>234.52</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-74.8</v>
+        <v>-78.38</v>
       </c>
       <c r="K73" t="n">
-        <v>142.85</v>
+        <v>149.68</v>
       </c>
       <c r="L73" t="n">
-        <v>161.25</v>
+        <v>168.96</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>23</v>
+        <v>22.47</v>
       </c>
       <c r="K74" t="n">
-        <v>-67.40000000000001</v>
+        <v>-65.86</v>
       </c>
       <c r="L74" t="n">
-        <v>71.20999999999999</v>
+        <v>69.59</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>54.34</v>
+        <v>55.07</v>
       </c>
       <c r="K75" t="n">
-        <v>-13.32</v>
+        <v>-13.5</v>
       </c>
       <c r="L75" t="n">
-        <v>55.95</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-28.66</v>
+        <v>-30.76</v>
       </c>
       <c r="K76" t="n">
-        <v>-30.51</v>
+        <v>-32.75</v>
       </c>
       <c r="L76" t="n">
-        <v>41.86</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-38.29</v>
+        <v>-39.56</v>
       </c>
       <c r="K77" t="n">
-        <v>45.93</v>
+        <v>47.44</v>
       </c>
       <c r="L77" t="n">
-        <v>59.8</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-31.79</v>
+        <v>-32.98</v>
       </c>
       <c r="K78" t="n">
-        <v>49.98</v>
+        <v>51.85</v>
       </c>
       <c r="L78" t="n">
-        <v>59.24</v>
+        <v>61.45</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="K79" t="n">
-        <v>-72.25</v>
+        <v>-72.02</v>
       </c>
       <c r="L79" t="n">
-        <v>72.31999999999999</v>
+        <v>72.09</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="K80" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="L80" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-55.07</v>
+        <v>-54.65</v>
       </c>
       <c r="K81" t="n">
-        <v>-97.90000000000001</v>
+        <v>-97.17</v>
       </c>
       <c r="L81" t="n">
-        <v>112.33</v>
+        <v>111.48</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-88.14</v>
+        <v>-85.90000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-88.61</v>
+        <v>-86.36</v>
       </c>
       <c r="L82" t="n">
-        <v>124.98</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-95.31999999999999</v>
+        <v>-96.38</v>
       </c>
       <c r="K83" t="n">
-        <v>-113.9</v>
+        <v>-115.16</v>
       </c>
       <c r="L83" t="n">
-        <v>148.53</v>
+        <v>150.17</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-92.90000000000001</v>
+        <v>-93.04000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>122.5</v>
+        <v>122.68</v>
       </c>
       <c r="L84" t="n">
-        <v>153.74</v>
+        <v>153.97</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>35.53</v>
+        <v>35.78</v>
       </c>
       <c r="K85" t="n">
-        <v>131.65</v>
+        <v>132.57</v>
       </c>
       <c r="L85" t="n">
-        <v>136.37</v>
+        <v>137.32</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>105.99</v>
+        <v>114.76</v>
       </c>
       <c r="K86" t="n">
-        <v>-127.28</v>
+        <v>-137.81</v>
       </c>
       <c r="L86" t="n">
-        <v>165.63</v>
+        <v>179.34</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-130.13</v>
+        <v>-142.03</v>
       </c>
       <c r="K87" t="n">
-        <v>85.78</v>
+        <v>93.63</v>
       </c>
       <c r="L87" t="n">
-        <v>155.86</v>
+        <v>170.12</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-200.11</v>
+        <v>-199.54</v>
       </c>
       <c r="K88" t="n">
-        <v>-57.42</v>
+        <v>-57.26</v>
       </c>
       <c r="L88" t="n">
-        <v>208.18</v>
+        <v>207.59</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -628,25 +628,25 @@
         <v>3.3</v>
       </c>
       <c r="F14" t="n">
-        <v>8.4</v>
+        <v>8.35</v>
       </c>
       <c r="G14" t="n">
-        <v>160.6</v>
+        <v>157.4</v>
       </c>
       <c r="H14" t="n">
-        <v>73.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>66.15000000000001</v>
+        <v>72.67</v>
       </c>
       <c r="K14" t="n">
-        <v>-19.82</v>
+        <v>-22.57</v>
       </c>
       <c r="L14" t="n">
-        <v>69.06</v>
+        <v>76.09</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>3.11</v>
       </c>
       <c r="F15" t="n">
-        <v>8.77</v>
+        <v>6.28</v>
       </c>
       <c r="G15" t="n">
-        <v>179.3</v>
+        <v>164.7</v>
       </c>
       <c r="H15" t="n">
-        <v>70.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-55.63</v>
+        <v>-57.13</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.75</v>
+        <v>-9.94</v>
       </c>
       <c r="L15" t="n">
-        <v>56.32</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>3.3</v>
       </c>
       <c r="F16" t="n">
-        <v>9.359999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="G16" t="n">
-        <v>178</v>
+        <v>176.5</v>
       </c>
       <c r="H16" t="n">
-        <v>75.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>94.58</v>
+        <v>98.23</v>
       </c>
       <c r="K16" t="n">
-        <v>-9.26</v>
+        <v>-10.24</v>
       </c>
       <c r="L16" t="n">
-        <v>95.04000000000001</v>
+        <v>98.76000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>3.21</v>
       </c>
       <c r="F17" t="n">
-        <v>9.76</v>
+        <v>9.91</v>
       </c>
       <c r="G17" t="n">
-        <v>169</v>
+        <v>184.4</v>
       </c>
       <c r="H17" t="n">
-        <v>73.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>35.89</v>
+        <v>36.48</v>
       </c>
       <c r="K17" t="n">
-        <v>-60.28</v>
+        <v>-66.23999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>70.16</v>
+        <v>75.62</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>2.96</v>
       </c>
       <c r="F18" t="n">
-        <v>8.73</v>
+        <v>9.24</v>
       </c>
       <c r="G18" t="n">
-        <v>172.2</v>
+        <v>163.9</v>
       </c>
       <c r="H18" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>73.79000000000001</v>
+        <v>88.94</v>
       </c>
       <c r="K18" t="n">
-        <v>5.48</v>
+        <v>4.53</v>
       </c>
       <c r="L18" t="n">
-        <v>74</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>3.08</v>
       </c>
       <c r="F19" t="n">
-        <v>8.76</v>
+        <v>7.64</v>
       </c>
       <c r="G19" t="n">
-        <v>161.5</v>
+        <v>164.5</v>
       </c>
       <c r="H19" t="n">
-        <v>70.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>33.62</v>
+        <v>42.43</v>
       </c>
       <c r="K19" t="n">
-        <v>56.3</v>
+        <v>67.33</v>
       </c>
       <c r="L19" t="n">
-        <v>65.56999999999999</v>
+        <v>79.58</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>2.93</v>
       </c>
       <c r="F20" t="n">
-        <v>8.56</v>
+        <v>7.31</v>
       </c>
       <c r="G20" t="n">
-        <v>154.2</v>
+        <v>160.4</v>
       </c>
       <c r="H20" t="n">
-        <v>73.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="I20" t="n">
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-137.14</v>
+        <v>-142.39</v>
       </c>
       <c r="K20" t="n">
-        <v>-50.29</v>
+        <v>-59.15</v>
       </c>
       <c r="L20" t="n">
-        <v>146.07</v>
+        <v>154.18</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>3.17</v>
       </c>
       <c r="F21" t="n">
-        <v>9.17</v>
+        <v>7.07</v>
       </c>
       <c r="G21" t="n">
-        <v>168.3</v>
+        <v>172.8</v>
       </c>
       <c r="H21" t="n">
-        <v>82.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>14.1</v>
+        <v>16.82</v>
       </c>
       <c r="K21" t="n">
-        <v>94.31</v>
+        <v>96.7</v>
       </c>
       <c r="L21" t="n">
-        <v>95.36</v>
+        <v>98.16</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>3.48</v>
       </c>
       <c r="F22" t="n">
-        <v>8.630000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>165</v>
+        <v>161.9</v>
       </c>
       <c r="H22" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>18.51</v>
+        <v>24.68</v>
       </c>
       <c r="K22" t="n">
-        <v>122.23</v>
+        <v>131.41</v>
       </c>
       <c r="L22" t="n">
-        <v>123.62</v>
+        <v>133.71</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>3.27</v>
       </c>
       <c r="F23" t="n">
-        <v>9.33</v>
+        <v>6.68</v>
       </c>
       <c r="G23" t="n">
-        <v>159.5</v>
+        <v>175.9</v>
       </c>
       <c r="H23" t="n">
-        <v>71.2</v>
+        <v>71.5</v>
       </c>
       <c r="I23" t="n">
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-87.28</v>
+        <v>-86.73</v>
       </c>
       <c r="K23" t="n">
-        <v>-120.3</v>
+        <v>-138.74</v>
       </c>
       <c r="L23" t="n">
-        <v>148.63</v>
+        <v>163.61</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>3.75</v>
       </c>
       <c r="F24" t="n">
-        <v>8.34</v>
+        <v>9.65</v>
       </c>
       <c r="G24" t="n">
-        <v>169.5</v>
+        <v>156.2</v>
       </c>
       <c r="H24" t="n">
-        <v>73.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-155.83</v>
+        <v>-161.58</v>
       </c>
       <c r="K24" t="n">
-        <v>-99.39</v>
+        <v>-133.66</v>
       </c>
       <c r="L24" t="n">
-        <v>184.83</v>
+        <v>209.7</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>2.77</v>
       </c>
       <c r="F25" t="n">
-        <v>8.52</v>
+        <v>6.05</v>
       </c>
       <c r="G25" t="n">
-        <v>169.3</v>
+        <v>159.8</v>
       </c>
       <c r="H25" t="n">
-        <v>80.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-57.81</v>
+        <v>-40.99</v>
       </c>
       <c r="K25" t="n">
-        <v>-106.72</v>
+        <v>-120.26</v>
       </c>
       <c r="L25" t="n">
-        <v>121.37</v>
+        <v>127.06</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>3.25</v>
       </c>
       <c r="F26" t="n">
-        <v>8.51</v>
+        <v>9.92</v>
       </c>
       <c r="G26" t="n">
         <v>159.6</v>
       </c>
       <c r="H26" t="n">
-        <v>77.3</v>
+        <v>71.5</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>-82.09</v>
+        <v>-99.03</v>
       </c>
       <c r="K26" t="n">
-        <v>139.16</v>
+        <v>146.86</v>
       </c>
       <c r="L26" t="n">
-        <v>161.56</v>
+        <v>177.13</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>3.08</v>
       </c>
       <c r="F27" t="n">
-        <v>9.17</v>
+        <v>7.83</v>
       </c>
       <c r="G27" t="n">
-        <v>177.5</v>
+        <v>172.7</v>
       </c>
       <c r="H27" t="n">
-        <v>73.2</v>
+        <v>80.5</v>
       </c>
       <c r="I27" t="n">
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-146.03</v>
+        <v>-147.13</v>
       </c>
       <c r="K27" t="n">
-        <v>-103.41</v>
+        <v>-145.09</v>
       </c>
       <c r="L27" t="n">
-        <v>178.94</v>
+        <v>206.64</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>3.29</v>
       </c>
       <c r="F28" t="n">
-        <v>9.1</v>
+        <v>9.75</v>
       </c>
       <c r="G28" t="n">
-        <v>152.4</v>
+        <v>171.3</v>
       </c>
       <c r="H28" t="n">
-        <v>76.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>30.01</v>
+        <v>34.01</v>
       </c>
       <c r="K28" t="n">
-        <v>221.65</v>
+        <v>230.2</v>
       </c>
       <c r="L28" t="n">
-        <v>223.67</v>
+        <v>232.69</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>2.68</v>
       </c>
       <c r="F29" t="n">
-        <v>9.52</v>
+        <v>5.56</v>
       </c>
       <c r="G29" t="n">
-        <v>170.2</v>
+        <v>179.7</v>
       </c>
       <c r="H29" t="n">
-        <v>78.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.29</v>
+        <v>-30.57</v>
       </c>
       <c r="K29" t="n">
-        <v>-34.78</v>
+        <v>-39.79</v>
       </c>
       <c r="L29" t="n">
-        <v>44.2</v>
+        <v>50.18</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>2.99</v>
       </c>
       <c r="F30" t="n">
-        <v>8.199999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="G30" t="n">
-        <v>175.5</v>
+        <v>153.3</v>
       </c>
       <c r="H30" t="n">
-        <v>79.8</v>
+        <v>79.5</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>4.14</v>
+        <v>6.28</v>
       </c>
       <c r="K30" t="n">
-        <v>-51.77</v>
+        <v>-64.2</v>
       </c>
       <c r="L30" t="n">
-        <v>51.93</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>3.19</v>
       </c>
       <c r="F31" t="n">
-        <v>8.81</v>
+        <v>10.12</v>
       </c>
       <c r="G31" t="n">
-        <v>159.6</v>
+        <v>165.6</v>
       </c>
       <c r="H31" t="n">
-        <v>79.8</v>
+        <v>71.5</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>26.95</v>
+        <v>36.51</v>
       </c>
       <c r="K31" t="n">
-        <v>33.45</v>
+        <v>42.37</v>
       </c>
       <c r="L31" t="n">
-        <v>42.95</v>
+        <v>55.93</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>3.36</v>
       </c>
       <c r="F32" t="n">
-        <v>8.26</v>
+        <v>10.12</v>
       </c>
       <c r="G32" t="n">
-        <v>158.4</v>
+        <v>154.5</v>
       </c>
       <c r="H32" t="n">
-        <v>77.2</v>
+        <v>71</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>74.5</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.11</v>
+        <v>-6.13</v>
       </c>
       <c r="L32" t="n">
-        <v>74.56999999999999</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>2.66</v>
       </c>
       <c r="F33" t="n">
-        <v>8.81</v>
+        <v>8.08</v>
       </c>
       <c r="G33" t="n">
-        <v>156</v>
+        <v>165.4</v>
       </c>
       <c r="H33" t="n">
-        <v>75.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="I33" t="n">
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>36.54</v>
+        <v>41.84</v>
       </c>
       <c r="K33" t="n">
-        <v>-50.23</v>
+        <v>-59.91</v>
       </c>
       <c r="L33" t="n">
-        <v>62.11</v>
+        <v>73.08</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>3.08</v>
       </c>
       <c r="F34" t="n">
-        <v>8.59</v>
+        <v>10.12</v>
       </c>
       <c r="G34" t="n">
-        <v>172.5</v>
+        <v>161.1</v>
       </c>
       <c r="H34" t="n">
-        <v>81.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>25.65</v>
+        <v>33.61</v>
       </c>
       <c r="K34" t="n">
-        <v>-48.12</v>
+        <v>-62.79</v>
       </c>
       <c r="L34" t="n">
-        <v>54.53</v>
+        <v>71.22</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>9.800000000000001</v>
+        <v>6.55</v>
       </c>
       <c r="G35" t="n">
-        <v>163.2</v>
+        <v>185.3</v>
       </c>
       <c r="H35" t="n">
-        <v>75.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-69.52</v>
+        <v>-77.06</v>
       </c>
       <c r="K35" t="n">
-        <v>-98.8</v>
+        <v>-113.38</v>
       </c>
       <c r="L35" t="n">
-        <v>120.81</v>
+        <v>137.09</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>3.23</v>
       </c>
       <c r="F36" t="n">
-        <v>8.01</v>
+        <v>10.12</v>
       </c>
       <c r="G36" t="n">
-        <v>167.6</v>
+        <v>149.4</v>
       </c>
       <c r="H36" t="n">
-        <v>79.7</v>
+        <v>75.5</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-70.19</v>
+        <v>-91.03</v>
       </c>
       <c r="K36" t="n">
-        <v>38.85</v>
+        <v>42.96</v>
       </c>
       <c r="L36" t="n">
-        <v>80.22</v>
+        <v>100.65</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>3.19</v>
       </c>
       <c r="F37" t="n">
-        <v>8.9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>177</v>
+        <v>167.3</v>
       </c>
       <c r="H37" t="n">
-        <v>75.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>111.06</v>
+        <v>127.22</v>
       </c>
       <c r="K37" t="n">
-        <v>-19.41</v>
+        <v>-31.03</v>
       </c>
       <c r="L37" t="n">
-        <v>112.75</v>
+        <v>130.95</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>3.36</v>
       </c>
       <c r="F38" t="n">
-        <v>8.93</v>
+        <v>9.43</v>
       </c>
       <c r="G38" t="n">
-        <v>158.9</v>
+        <v>167.9</v>
       </c>
       <c r="H38" t="n">
-        <v>74.8</v>
+        <v>71.2</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-71.73</v>
+        <v>-59.18</v>
       </c>
       <c r="K38" t="n">
-        <v>-106.24</v>
+        <v>-125.49</v>
       </c>
       <c r="L38" t="n">
-        <v>128.19</v>
+        <v>138.75</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>3.25</v>
       </c>
       <c r="F39" t="n">
-        <v>8.75</v>
+        <v>6.46</v>
       </c>
       <c r="G39" t="n">
-        <v>164.4</v>
+        <v>164.3</v>
       </c>
       <c r="H39" t="n">
-        <v>75.8</v>
+        <v>74</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>106.74</v>
+        <v>117.66</v>
       </c>
       <c r="K39" t="n">
-        <v>-42.6</v>
+        <v>-76.18000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>114.93</v>
+        <v>140.17</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>2.84</v>
       </c>
       <c r="F40" t="n">
-        <v>8.58</v>
+        <v>8.84</v>
       </c>
       <c r="G40" t="n">
-        <v>166.4</v>
+        <v>160.9</v>
       </c>
       <c r="H40" t="n">
-        <v>76.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>93.34</v>
+        <v>116.09</v>
       </c>
       <c r="K40" t="n">
-        <v>-47.01</v>
+        <v>-81.45</v>
       </c>
       <c r="L40" t="n">
-        <v>104.51</v>
+        <v>141.81</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>3.39</v>
       </c>
       <c r="F41" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="G41" t="n">
-        <v>166.4</v>
+        <v>167.4</v>
       </c>
       <c r="H41" t="n">
-        <v>78.2</v>
+        <v>75</v>
       </c>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-133.52</v>
+        <v>-133.94</v>
       </c>
       <c r="K41" t="n">
-        <v>-154.62</v>
+        <v>-198.11</v>
       </c>
       <c r="L41" t="n">
-        <v>204.29</v>
+        <v>239.14</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>3.09</v>
       </c>
       <c r="F42" t="n">
-        <v>8.529999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="G42" t="n">
-        <v>167.6</v>
+        <v>159.8</v>
       </c>
       <c r="H42" t="n">
-        <v>75</v>
+        <v>75.5</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>229.62</v>
+        <v>229.22</v>
       </c>
       <c r="K42" t="n">
-        <v>-62.57</v>
+        <v>-85.77</v>
       </c>
       <c r="L42" t="n">
-        <v>238</v>
+        <v>244.74</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>8.220000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G43" t="n">
-        <v>151.5</v>
+        <v>153.6</v>
       </c>
       <c r="H43" t="n">
-        <v>72.3</v>
+        <v>67.5</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>144.92</v>
+        <v>190.67</v>
       </c>
       <c r="K43" t="n">
-        <v>157.55</v>
+        <v>162.19</v>
       </c>
       <c r="L43" t="n">
-        <v>214.07</v>
+        <v>250.32</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>3.29</v>
       </c>
       <c r="F44" t="n">
-        <v>8.19</v>
+        <v>8.52</v>
       </c>
       <c r="G44" t="n">
-        <v>153.4</v>
+        <v>153.1</v>
       </c>
       <c r="H44" t="n">
-        <v>72.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>22.5</v>
+        <v>25.13</v>
       </c>
       <c r="K44" t="n">
-        <v>79.25</v>
+        <v>86.48</v>
       </c>
       <c r="L44" t="n">
-        <v>82.38</v>
+        <v>90.06</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>3.21</v>
       </c>
       <c r="F45" t="n">
-        <v>8.94</v>
+        <v>8.83</v>
       </c>
       <c r="G45" t="n">
-        <v>161.4</v>
+        <v>168</v>
       </c>
       <c r="H45" t="n">
-        <v>73.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>10.04</v>
+        <v>12.72</v>
       </c>
       <c r="K45" t="n">
-        <v>45.68</v>
+        <v>55.82</v>
       </c>
       <c r="L45" t="n">
-        <v>46.77</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>3.64</v>
       </c>
       <c r="F46" t="n">
-        <v>8.68</v>
+        <v>10.12</v>
       </c>
       <c r="G46" t="n">
-        <v>161.7</v>
+        <v>162.9</v>
       </c>
       <c r="H46" t="n">
-        <v>78.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I46" t="n">
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-62.72</v>
+        <v>-69.42</v>
       </c>
       <c r="K46" t="n">
-        <v>-19.72</v>
+        <v>-22.9</v>
       </c>
       <c r="L46" t="n">
-        <v>65.75</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>3.58</v>
       </c>
       <c r="F47" t="n">
-        <v>9.23</v>
+        <v>9.65</v>
       </c>
       <c r="G47" t="n">
-        <v>166.2</v>
+        <v>174</v>
       </c>
       <c r="H47" t="n">
-        <v>73.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="K47" t="n">
-        <v>67.22</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>67.23999999999999</v>
+        <v>78.11</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>3.36</v>
       </c>
       <c r="F48" t="n">
-        <v>8.390000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>172.2</v>
+        <v>157.1</v>
       </c>
       <c r="H48" t="n">
-        <v>71.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="I48" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>8.49</v>
+        <v>10.63</v>
       </c>
       <c r="K48" t="n">
-        <v>-104.88</v>
+        <v>-118.82</v>
       </c>
       <c r="L48" t="n">
-        <v>105.22</v>
+        <v>119.29</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>3.74</v>
       </c>
       <c r="F49" t="n">
-        <v>8.44</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>168.8</v>
+        <v>158.2</v>
       </c>
       <c r="H49" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-48.17</v>
+        <v>-56.34</v>
       </c>
       <c r="K49" t="n">
-        <v>-29.88</v>
+        <v>-41.22</v>
       </c>
       <c r="L49" t="n">
-        <v>56.68</v>
+        <v>69.81</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>3.14</v>
       </c>
       <c r="F50" t="n">
-        <v>9.039999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>168.4</v>
+        <v>170.2</v>
       </c>
       <c r="H50" t="n">
-        <v>75.5</v>
+        <v>76</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-65.97</v>
+        <v>-73.45</v>
       </c>
       <c r="K50" t="n">
-        <v>113.54</v>
+        <v>120.12</v>
       </c>
       <c r="L50" t="n">
-        <v>131.32</v>
+        <v>140.8</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>3.56</v>
       </c>
       <c r="F51" t="n">
-        <v>8.31</v>
+        <v>10.12</v>
       </c>
       <c r="G51" t="n">
-        <v>146.5</v>
+        <v>155.5</v>
       </c>
       <c r="H51" t="n">
-        <v>72.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.109999999999999</v>
+        <v>-1.61</v>
       </c>
       <c r="K51" t="n">
-        <v>-84.11</v>
+        <v>-91.73999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>84.61</v>
+        <v>91.75</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>2.6</v>
       </c>
       <c r="F52" t="n">
-        <v>9.140000000000001</v>
+        <v>5.62</v>
       </c>
       <c r="G52" t="n">
-        <v>159.5</v>
+        <v>172.1</v>
       </c>
       <c r="H52" t="n">
-        <v>70.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-81.86</v>
+        <v>-92.97</v>
       </c>
       <c r="K52" t="n">
-        <v>11.29</v>
+        <v>2.76</v>
       </c>
       <c r="L52" t="n">
-        <v>82.63</v>
+        <v>93.01000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>3.56</v>
       </c>
       <c r="F53" t="n">
-        <v>8.18</v>
+        <v>10.12</v>
       </c>
       <c r="G53" t="n">
-        <v>153.7</v>
+        <v>153</v>
       </c>
       <c r="H53" t="n">
-        <v>69.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>49.13</v>
+        <v>64.89</v>
       </c>
       <c r="K53" t="n">
-        <v>-136.36</v>
+        <v>-168.11</v>
       </c>
       <c r="L53" t="n">
-        <v>144.94</v>
+        <v>180.2</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>2.92</v>
       </c>
       <c r="F54" t="n">
-        <v>9.220000000000001</v>
+        <v>4.64</v>
       </c>
       <c r="G54" t="n">
-        <v>171.9</v>
+        <v>173.7</v>
       </c>
       <c r="H54" t="n">
-        <v>65.5</v>
+        <v>77.7</v>
       </c>
       <c r="I54" t="n">
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-120.14</v>
+        <v>-125.8</v>
       </c>
       <c r="K54" t="n">
-        <v>22.53</v>
+        <v>-3.76</v>
       </c>
       <c r="L54" t="n">
-        <v>122.23</v>
+        <v>125.86</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>3.46</v>
       </c>
       <c r="F55" t="n">
-        <v>8.949999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="G55" t="n">
-        <v>160.3</v>
+        <v>168.3</v>
       </c>
       <c r="H55" t="n">
-        <v>69.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I55" t="n">
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>132.26</v>
+        <v>158.77</v>
       </c>
       <c r="K55" t="n">
-        <v>59.85</v>
+        <v>39.89</v>
       </c>
       <c r="L55" t="n">
-        <v>145.17</v>
+        <v>163.71</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>3.36</v>
       </c>
       <c r="F56" t="n">
-        <v>8.48</v>
+        <v>7.25</v>
       </c>
       <c r="G56" t="n">
-        <v>158.6</v>
+        <v>158.9</v>
       </c>
       <c r="H56" t="n">
-        <v>68.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I56" t="n">
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>152.3</v>
+        <v>178.47</v>
       </c>
       <c r="K56" t="n">
-        <v>88.25</v>
+        <v>59.56</v>
       </c>
       <c r="L56" t="n">
-        <v>176.02</v>
+        <v>188.14</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>3.68</v>
       </c>
       <c r="F57" t="n">
-        <v>9.06</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>159.5</v>
+        <v>170.6</v>
       </c>
       <c r="H57" t="n">
-        <v>74.2</v>
+        <v>71.5</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-10.78</v>
+        <v>-17.36</v>
       </c>
       <c r="K57" t="n">
-        <v>161.01</v>
+        <v>156.33</v>
       </c>
       <c r="L57" t="n">
-        <v>161.37</v>
+        <v>157.3</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>3.14</v>
       </c>
       <c r="F58" t="n">
-        <v>8.76</v>
+        <v>6.8</v>
       </c>
       <c r="G58" t="n">
-        <v>167.8</v>
+        <v>164.6</v>
       </c>
       <c r="H58" t="n">
-        <v>69</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I58" t="n">
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-160.75</v>
+        <v>-153.96</v>
       </c>
       <c r="K58" t="n">
-        <v>-201.51</v>
+        <v>-232.66</v>
       </c>
       <c r="L58" t="n">
-        <v>257.78</v>
+        <v>278.98</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>3.59</v>
       </c>
       <c r="F59" t="n">
-        <v>8.92</v>
+        <v>10.12</v>
       </c>
       <c r="G59" t="n">
-        <v>172.6</v>
+        <v>167.7</v>
       </c>
       <c r="H59" t="n">
-        <v>71.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-46.25</v>
+        <v>-53.58</v>
       </c>
       <c r="K59" t="n">
-        <v>16.91</v>
+        <v>18.07</v>
       </c>
       <c r="L59" t="n">
-        <v>49.25</v>
+        <v>56.55</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>3.05</v>
       </c>
       <c r="F60" t="n">
-        <v>8.25</v>
+        <v>7.19</v>
       </c>
       <c r="G60" t="n">
-        <v>160</v>
+        <v>154.4</v>
       </c>
       <c r="H60" t="n">
-        <v>70.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>55.55</v>
+        <v>66.11</v>
       </c>
       <c r="K60" t="n">
-        <v>10.65</v>
+        <v>11.7</v>
       </c>
       <c r="L60" t="n">
-        <v>56.56</v>
+        <v>67.14</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>3.26</v>
       </c>
       <c r="F61" t="n">
-        <v>8.380000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>166.7</v>
+        <v>157</v>
       </c>
       <c r="H61" t="n">
-        <v>74.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-77.63</v>
+        <v>-85.44</v>
       </c>
       <c r="K61" t="n">
-        <v>24.5</v>
+        <v>26.39</v>
       </c>
       <c r="L61" t="n">
-        <v>81.40000000000001</v>
+        <v>89.42</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>3.09</v>
       </c>
       <c r="F62" t="n">
-        <v>8.140000000000001</v>
+        <v>4.92</v>
       </c>
       <c r="G62" t="n">
-        <v>178.7</v>
+        <v>152.2</v>
       </c>
       <c r="H62" t="n">
-        <v>64.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>27.04</v>
+        <v>30.56</v>
       </c>
       <c r="K62" t="n">
-        <v>52.36</v>
+        <v>50.19</v>
       </c>
       <c r="L62" t="n">
-        <v>58.93</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>3.32</v>
       </c>
       <c r="F63" t="n">
-        <v>8.58</v>
+        <v>8.34</v>
       </c>
       <c r="G63" t="n">
-        <v>162.9</v>
+        <v>161</v>
       </c>
       <c r="H63" t="n">
-        <v>72.8</v>
+        <v>73.2</v>
       </c>
       <c r="I63" t="n">
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.84</v>
+        <v>0.44</v>
       </c>
       <c r="K63" t="n">
-        <v>-22.41</v>
+        <v>-36.46</v>
       </c>
       <c r="L63" t="n">
-        <v>22.49</v>
+        <v>36.46</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>3.71</v>
       </c>
       <c r="F64" t="n">
-        <v>8.92</v>
+        <v>9.74</v>
       </c>
       <c r="G64" t="n">
-        <v>174.9</v>
+        <v>167.6</v>
       </c>
       <c r="H64" t="n">
-        <v>71.8</v>
+        <v>79.2</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>45.86</v>
+        <v>57.34</v>
       </c>
       <c r="K64" t="n">
-        <v>41.34</v>
+        <v>44.49</v>
       </c>
       <c r="L64" t="n">
-        <v>61.74</v>
+        <v>72.56999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>3.93</v>
       </c>
       <c r="F65" t="n">
-        <v>8.76</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>160.8</v>
+        <v>164.4</v>
       </c>
       <c r="H65" t="n">
-        <v>77</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-87.45</v>
+        <v>-79.98999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-66.64</v>
+        <v>-78.61</v>
       </c>
       <c r="L65" t="n">
-        <v>109.95</v>
+        <v>112.15</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>3.56</v>
       </c>
       <c r="F66" t="n">
-        <v>8.4</v>
+        <v>10.12</v>
       </c>
       <c r="G66" t="n">
         <v>157.4</v>
       </c>
       <c r="H66" t="n">
-        <v>78.3</v>
+        <v>70.5</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-125.45</v>
+        <v>-131.62</v>
       </c>
       <c r="K66" t="n">
-        <v>-9.02</v>
+        <v>-20.84</v>
       </c>
       <c r="L66" t="n">
-        <v>125.78</v>
+        <v>133.26</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>3.95</v>
       </c>
       <c r="F67" t="n">
-        <v>8.75</v>
+        <v>10.12</v>
       </c>
       <c r="G67" t="n">
-        <v>165.2</v>
+        <v>164.3</v>
       </c>
       <c r="H67" t="n">
-        <v>77</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-75.34999999999999</v>
+        <v>-85.05</v>
       </c>
       <c r="K67" t="n">
-        <v>35.39</v>
+        <v>-0.6</v>
       </c>
       <c r="L67" t="n">
-        <v>83.25</v>
+        <v>85.05</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>3.5</v>
       </c>
       <c r="F68" t="n">
-        <v>9.27</v>
+        <v>10.12</v>
       </c>
       <c r="G68" t="n">
-        <v>170.3</v>
+        <v>174.6</v>
       </c>
       <c r="H68" t="n">
-        <v>75.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-19.62</v>
+        <v>-15.92</v>
       </c>
       <c r="K68" t="n">
-        <v>-63.66</v>
+        <v>-136.84</v>
       </c>
       <c r="L68" t="n">
-        <v>66.61</v>
+        <v>137.76</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>3.34</v>
       </c>
       <c r="F69" t="n">
-        <v>8.859999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="G69" t="n">
-        <v>157.2</v>
+        <v>166.5</v>
       </c>
       <c r="H69" t="n">
-        <v>76.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-18.18</v>
+        <v>-15.95</v>
       </c>
       <c r="K69" t="n">
-        <v>177.79</v>
+        <v>167.43</v>
       </c>
       <c r="L69" t="n">
-        <v>178.71</v>
+        <v>168.19</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>3.49</v>
       </c>
       <c r="F70" t="n">
-        <v>8.01</v>
+        <v>10.12</v>
       </c>
       <c r="G70" t="n">
-        <v>162.8</v>
+        <v>149.5</v>
       </c>
       <c r="H70" t="n">
-        <v>74.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>204.84</v>
+        <v>221.2</v>
       </c>
       <c r="K70" t="n">
-        <v>32.81</v>
+        <v>15.53</v>
       </c>
       <c r="L70" t="n">
-        <v>207.45</v>
+        <v>221.75</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>3.61</v>
       </c>
       <c r="F71" t="n">
-        <v>8.17</v>
+        <v>10.12</v>
       </c>
       <c r="G71" t="n">
-        <v>167.4</v>
+        <v>152.8</v>
       </c>
       <c r="H71" t="n">
-        <v>74.2</v>
+        <v>75.5</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>92.58</v>
+        <v>138.3</v>
       </c>
       <c r="K71" t="n">
-        <v>167.27</v>
+        <v>138.62</v>
       </c>
       <c r="L71" t="n">
-        <v>191.19</v>
+        <v>195.81</v>
       </c>
     </row>
     <row r="72">
@@ -3067,22 +3067,22 @@
         <v>8.5</v>
       </c>
       <c r="G72" t="n">
-        <v>170</v>
+        <v>159.3</v>
       </c>
       <c r="H72" t="n">
-        <v>68.5</v>
+        <v>76.7</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-231.03</v>
+        <v>-256.02</v>
       </c>
       <c r="K72" t="n">
-        <v>-40.29</v>
+        <v>-81.27</v>
       </c>
       <c r="L72" t="n">
-        <v>234.52</v>
+        <v>268.61</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>3.46</v>
       </c>
       <c r="F73" t="n">
-        <v>9.01</v>
+        <v>8.48</v>
       </c>
       <c r="G73" t="n">
-        <v>166.7</v>
+        <v>169.5</v>
       </c>
       <c r="H73" t="n">
-        <v>66.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-78.38</v>
+        <v>-96.29000000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>149.68</v>
+        <v>128.89</v>
       </c>
       <c r="L73" t="n">
-        <v>168.96</v>
+        <v>160.89</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>3.63</v>
       </c>
       <c r="F74" t="n">
-        <v>8.77</v>
+        <v>10.12</v>
       </c>
       <c r="G74" t="n">
-        <v>151.5</v>
+        <v>164.8</v>
       </c>
       <c r="H74" t="n">
-        <v>74.2</v>
+        <v>67.5</v>
       </c>
       <c r="I74" t="n">
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>22.47</v>
+        <v>24.59</v>
       </c>
       <c r="K74" t="n">
-        <v>-65.86</v>
+        <v>-73.15000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>69.59</v>
+        <v>77.17</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>3.41</v>
       </c>
       <c r="F75" t="n">
-        <v>8.369999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="G75" t="n">
-        <v>180.6</v>
+        <v>156.7</v>
       </c>
       <c r="H75" t="n">
-        <v>73.2</v>
+        <v>82</v>
       </c>
       <c r="I75" t="n">
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>55.07</v>
+        <v>64.42</v>
       </c>
       <c r="K75" t="n">
-        <v>-13.5</v>
+        <v>-16.47</v>
       </c>
       <c r="L75" t="n">
-        <v>56.7</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>3.49</v>
       </c>
       <c r="F76" t="n">
-        <v>8.630000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="G76" t="n">
-        <v>160.5</v>
+        <v>161.9</v>
       </c>
       <c r="H76" t="n">
-        <v>75.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="I76" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-30.76</v>
+        <v>-35.91</v>
       </c>
       <c r="K76" t="n">
-        <v>-32.75</v>
+        <v>-41.02</v>
       </c>
       <c r="L76" t="n">
-        <v>44.93</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>2.88</v>
       </c>
       <c r="F77" t="n">
-        <v>8.65</v>
+        <v>7.68</v>
       </c>
       <c r="G77" t="n">
-        <v>162.5</v>
+        <v>162.3</v>
       </c>
       <c r="H77" t="n">
-        <v>66.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-39.56</v>
+        <v>-44.07</v>
       </c>
       <c r="K77" t="n">
-        <v>47.44</v>
+        <v>51.04</v>
       </c>
       <c r="L77" t="n">
-        <v>61.77</v>
+        <v>67.43000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>3.9</v>
       </c>
       <c r="F78" t="n">
-        <v>8.890000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="G78" t="n">
-        <v>179.1</v>
+        <v>167.1</v>
       </c>
       <c r="H78" t="n">
-        <v>74.2</v>
+        <v>81.3</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-32.98</v>
+        <v>-38.56</v>
       </c>
       <c r="K78" t="n">
-        <v>51.85</v>
+        <v>59.22</v>
       </c>
       <c r="L78" t="n">
-        <v>61.45</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>3.5</v>
       </c>
       <c r="F79" t="n">
-        <v>8.43</v>
+        <v>9.83</v>
       </c>
       <c r="G79" t="n">
-        <v>166.2</v>
+        <v>158</v>
       </c>
       <c r="H79" t="n">
-        <v>69.7</v>
+        <v>74.8</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>3.07</v>
+        <v>5.23</v>
       </c>
       <c r="K79" t="n">
-        <v>-72.02</v>
+        <v>-89.68000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>72.09</v>
+        <v>89.84</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>3.38</v>
       </c>
       <c r="F80" t="n">
-        <v>8.359999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="G80" t="n">
-        <v>158.1</v>
+        <v>156.5</v>
       </c>
       <c r="H80" t="n">
-        <v>79</v>
+        <v>70.8</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>2.24</v>
+        <v>14.05</v>
       </c>
       <c r="K80" t="n">
-        <v>1.51</v>
+        <v>-19.06</v>
       </c>
       <c r="L80" t="n">
-        <v>2.7</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>3.32</v>
       </c>
       <c r="F81" t="n">
-        <v>8.81</v>
+        <v>10.12</v>
       </c>
       <c r="G81" t="n">
-        <v>173.8</v>
+        <v>165.5</v>
       </c>
       <c r="H81" t="n">
-        <v>75.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-54.65</v>
+        <v>-55.97</v>
       </c>
       <c r="K81" t="n">
-        <v>-97.17</v>
+        <v>-116.5</v>
       </c>
       <c r="L81" t="n">
-        <v>111.48</v>
+        <v>129.25</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>3.59</v>
       </c>
       <c r="F82" t="n">
-        <v>8.48</v>
+        <v>10.12</v>
       </c>
       <c r="G82" t="n">
-        <v>162.8</v>
+        <v>159</v>
       </c>
       <c r="H82" t="n">
-        <v>75</v>
+        <v>73.2</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-85.90000000000001</v>
+        <v>-91.56999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-86.36</v>
+        <v>-105.9</v>
       </c>
       <c r="L82" t="n">
-        <v>121.8</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>3.79</v>
       </c>
       <c r="F83" t="n">
-        <v>9.09</v>
+        <v>10.12</v>
       </c>
       <c r="G83" t="n">
-        <v>163.9</v>
+        <v>171.1</v>
       </c>
       <c r="H83" t="n">
-        <v>73.2</v>
+        <v>73.7</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-96.38</v>
+        <v>-92.76000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-115.16</v>
+        <v>-149.28</v>
       </c>
       <c r="L83" t="n">
-        <v>150.17</v>
+        <v>175.75</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>3.49</v>
       </c>
       <c r="F84" t="n">
-        <v>8.82</v>
+        <v>10.12</v>
       </c>
       <c r="G84" t="n">
-        <v>164.3</v>
+        <v>165.7</v>
       </c>
       <c r="H84" t="n">
-        <v>74.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-93.04000000000001</v>
+        <v>-102.72</v>
       </c>
       <c r="K84" t="n">
-        <v>122.68</v>
+        <v>112.24</v>
       </c>
       <c r="L84" t="n">
-        <v>153.97</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>3.41</v>
       </c>
       <c r="F85" t="n">
-        <v>8.41</v>
+        <v>6.78</v>
       </c>
       <c r="G85" t="n">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="H85" t="n">
-        <v>73.5</v>
+        <v>70</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>35.78</v>
+        <v>58.21</v>
       </c>
       <c r="K85" t="n">
-        <v>132.57</v>
+        <v>135.51</v>
       </c>
       <c r="L85" t="n">
-        <v>137.32</v>
+        <v>147.48</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>3.79</v>
       </c>
       <c r="F86" t="n">
-        <v>9.140000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="G86" t="n">
-        <v>178.2</v>
+        <v>172.1</v>
       </c>
       <c r="H86" t="n">
-        <v>73.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>114.76</v>
+        <v>110.24</v>
       </c>
       <c r="K86" t="n">
-        <v>-137.81</v>
+        <v>-184.59</v>
       </c>
       <c r="L86" t="n">
-        <v>179.34</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>4.21</v>
       </c>
       <c r="F87" t="n">
-        <v>8.65</v>
+        <v>10.12</v>
       </c>
       <c r="G87" t="n">
-        <v>174.4</v>
+        <v>162.4</v>
       </c>
       <c r="H87" t="n">
-        <v>69.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="I87" t="n">
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-142.03</v>
+        <v>-128.57</v>
       </c>
       <c r="K87" t="n">
-        <v>93.63</v>
+        <v>19.04</v>
       </c>
       <c r="L87" t="n">
-        <v>170.12</v>
+        <v>129.97</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>3.51</v>
       </c>
       <c r="F88" t="n">
-        <v>8.83</v>
+        <v>10.12</v>
       </c>
       <c r="G88" t="n">
-        <v>157.8</v>
+        <v>166</v>
       </c>
       <c r="H88" t="n">
-        <v>81.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I88" t="n">
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-199.54</v>
+        <v>-212.67</v>
       </c>
       <c r="K88" t="n">
-        <v>-57.26</v>
+        <v>-101.69</v>
       </c>
       <c r="L88" t="n">
-        <v>207.59</v>
+        <v>235.73</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>72.67</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-22.57</v>
+        <v>-23.84</v>
       </c>
       <c r="L14" t="n">
-        <v>76.09</v>
+        <v>80.38</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-57.13</v>
+        <v>-53.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.94</v>
+        <v>-9.31</v>
       </c>
       <c r="L15" t="n">
-        <v>57.99</v>
+        <v>54.29</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>98.23</v>
+        <v>91.94</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.24</v>
+        <v>-9.59</v>
       </c>
       <c r="L16" t="n">
-        <v>98.76000000000001</v>
+        <v>92.43000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>36.48</v>
+        <v>34.96</v>
       </c>
       <c r="K17" t="n">
-        <v>-66.23999999999999</v>
+        <v>-63.48</v>
       </c>
       <c r="L17" t="n">
-        <v>75.62</v>
+        <v>72.45999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>88.94</v>
+        <v>87.12</v>
       </c>
       <c r="K18" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="L18" t="n">
-        <v>89.05</v>
+        <v>87.23999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>42.43</v>
+        <v>44.06</v>
       </c>
       <c r="K19" t="n">
-        <v>67.33</v>
+        <v>69.92</v>
       </c>
       <c r="L19" t="n">
-        <v>79.58</v>
+        <v>82.64</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-142.39</v>
+        <v>-145.18</v>
       </c>
       <c r="K20" t="n">
-        <v>-59.15</v>
+        <v>-60.31</v>
       </c>
       <c r="L20" t="n">
-        <v>154.18</v>
+        <v>157.21</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>16.82</v>
+        <v>15.74</v>
       </c>
       <c r="K21" t="n">
-        <v>96.7</v>
+        <v>90.53</v>
       </c>
       <c r="L21" t="n">
-        <v>98.16</v>
+        <v>91.89</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>24.68</v>
+        <v>24.17</v>
       </c>
       <c r="K22" t="n">
-        <v>131.41</v>
+        <v>128.68</v>
       </c>
       <c r="L22" t="n">
-        <v>133.71</v>
+        <v>130.93</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-86.73</v>
+        <v>-81.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-138.74</v>
+        <v>-129.88</v>
       </c>
       <c r="L23" t="n">
-        <v>163.61</v>
+        <v>153.17</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-161.58</v>
+        <v>-161.67</v>
       </c>
       <c r="K24" t="n">
-        <v>-133.66</v>
+        <v>-133.74</v>
       </c>
       <c r="L24" t="n">
-        <v>209.7</v>
+        <v>209.82</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-40.99</v>
+        <v>-40.15</v>
       </c>
       <c r="K25" t="n">
-        <v>-120.26</v>
+        <v>-117.81</v>
       </c>
       <c r="L25" t="n">
-        <v>127.06</v>
+        <v>124.46</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>-99.03</v>
+        <v>-94.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>146.86</v>
+        <v>140.74</v>
       </c>
       <c r="L26" t="n">
-        <v>177.13</v>
+        <v>169.75</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-147.13</v>
+        <v>-137.74</v>
       </c>
       <c r="K27" t="n">
-        <v>-145.09</v>
+        <v>-135.83</v>
       </c>
       <c r="L27" t="n">
-        <v>206.64</v>
+        <v>193.45</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>34.01</v>
+        <v>32.6</v>
       </c>
       <c r="K28" t="n">
-        <v>230.2</v>
+        <v>220.68</v>
       </c>
       <c r="L28" t="n">
-        <v>232.69</v>
+        <v>223.08</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-30.57</v>
+        <v>-32.3</v>
       </c>
       <c r="K29" t="n">
-        <v>-39.79</v>
+        <v>-42.04</v>
       </c>
       <c r="L29" t="n">
-        <v>50.18</v>
+        <v>53.02</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>6.28</v>
+        <v>6.63</v>
       </c>
       <c r="K30" t="n">
-        <v>-64.2</v>
+        <v>-67.83</v>
       </c>
       <c r="L30" t="n">
-        <v>64.5</v>
+        <v>68.15000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>36.51</v>
+        <v>38.57</v>
       </c>
       <c r="K31" t="n">
-        <v>42.37</v>
+        <v>44.77</v>
       </c>
       <c r="L31" t="n">
-        <v>55.93</v>
+        <v>59.09</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>93.65000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.13</v>
+        <v>-6.36</v>
       </c>
       <c r="L32" t="n">
-        <v>93.84999999999999</v>
+        <v>97.41</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>41.84</v>
+        <v>44.21</v>
       </c>
       <c r="K33" t="n">
-        <v>-59.91</v>
+        <v>-63.3</v>
       </c>
       <c r="L33" t="n">
-        <v>73.08</v>
+        <v>77.20999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>33.61</v>
+        <v>34.9</v>
       </c>
       <c r="K34" t="n">
-        <v>-62.79</v>
+        <v>-65.20999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>71.22</v>
+        <v>73.95999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-77.06</v>
+        <v>-81.43000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-113.38</v>
+        <v>-119.79</v>
       </c>
       <c r="L35" t="n">
-        <v>137.09</v>
+        <v>144.85</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-91.03</v>
+        <v>-96.18000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>42.96</v>
+        <v>45.39</v>
       </c>
       <c r="L36" t="n">
-        <v>100.65</v>
+        <v>106.35</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>127.22</v>
+        <v>134.42</v>
       </c>
       <c r="K37" t="n">
-        <v>-31.03</v>
+        <v>-32.79</v>
       </c>
       <c r="L37" t="n">
-        <v>130.95</v>
+        <v>138.36</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-59.18</v>
+        <v>-55.41</v>
       </c>
       <c r="K38" t="n">
-        <v>-125.49</v>
+        <v>-117.5</v>
       </c>
       <c r="L38" t="n">
-        <v>138.75</v>
+        <v>129.91</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>117.66</v>
+        <v>124.32</v>
       </c>
       <c r="K39" t="n">
-        <v>-76.18000000000001</v>
+        <v>-80.48999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>140.17</v>
+        <v>148.11</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>116.09</v>
+        <v>120.56</v>
       </c>
       <c r="K40" t="n">
-        <v>-81.45</v>
+        <v>-84.58</v>
       </c>
       <c r="L40" t="n">
-        <v>141.81</v>
+        <v>147.27</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-133.94</v>
+        <v>-136.73</v>
       </c>
       <c r="K41" t="n">
-        <v>-198.11</v>
+        <v>-202.25</v>
       </c>
       <c r="L41" t="n">
-        <v>239.14</v>
+        <v>244.13</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>229.22</v>
+        <v>214.59</v>
       </c>
       <c r="K42" t="n">
-        <v>-85.77</v>
+        <v>-80.3</v>
       </c>
       <c r="L42" t="n">
-        <v>244.74</v>
+        <v>229.12</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>190.67</v>
+        <v>194.41</v>
       </c>
       <c r="K43" t="n">
-        <v>162.19</v>
+        <v>165.37</v>
       </c>
       <c r="L43" t="n">
-        <v>250.32</v>
+        <v>255.22</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>25.13</v>
+        <v>26.55</v>
       </c>
       <c r="K44" t="n">
-        <v>86.48</v>
+        <v>91.36</v>
       </c>
       <c r="L44" t="n">
-        <v>90.06</v>
+        <v>95.14</v>
       </c>
     </row>
     <row r="45">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-69.42</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-22.9</v>
+        <v>-21.9</v>
       </c>
       <c r="L46" t="n">
-        <v>73.09999999999999</v>
+        <v>69.92</v>
       </c>
     </row>
     <row r="47">
@@ -2029,10 +2029,10 @@
         <v>1.62</v>
       </c>
       <c r="K47" t="n">
-        <v>78.09999999999999</v>
+        <v>77.97</v>
       </c>
       <c r="L47" t="n">
-        <v>78.11</v>
+        <v>77.98999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2071,10 +2071,10 @@
         <v>10.63</v>
       </c>
       <c r="K48" t="n">
-        <v>-118.82</v>
+        <v>-118.75</v>
       </c>
       <c r="L48" t="n">
-        <v>119.29</v>
+        <v>119.23</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-56.34</v>
+        <v>-56.21</v>
       </c>
       <c r="K49" t="n">
-        <v>-41.22</v>
+        <v>-41.12</v>
       </c>
       <c r="L49" t="n">
-        <v>69.81</v>
+        <v>69.64</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-73.45</v>
+        <v>-74.89</v>
       </c>
       <c r="K50" t="n">
-        <v>120.12</v>
+        <v>122.48</v>
       </c>
       <c r="L50" t="n">
-        <v>140.8</v>
+        <v>143.56</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-1.61</v>
+        <v>-1.51</v>
       </c>
       <c r="K51" t="n">
-        <v>-91.73999999999999</v>
+        <v>-85.83</v>
       </c>
       <c r="L51" t="n">
-        <v>91.75</v>
+        <v>85.84999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-92.97</v>
+        <v>-94.79000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="L52" t="n">
-        <v>93.01000000000001</v>
+        <v>94.83</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>64.89</v>
+        <v>67.41</v>
       </c>
       <c r="K53" t="n">
-        <v>-168.11</v>
+        <v>-174.64</v>
       </c>
       <c r="L53" t="n">
-        <v>180.2</v>
+        <v>187.2</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-125.8</v>
+        <v>-128.27</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.76</v>
+        <v>-3.84</v>
       </c>
       <c r="L54" t="n">
-        <v>125.86</v>
+        <v>128.33</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>158.77</v>
+        <v>155.57</v>
       </c>
       <c r="K55" t="n">
-        <v>39.89</v>
+        <v>39.08</v>
       </c>
       <c r="L55" t="n">
-        <v>163.71</v>
+        <v>160.41</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>178.47</v>
+        <v>167.24</v>
       </c>
       <c r="K56" t="n">
-        <v>59.56</v>
+        <v>55.81</v>
       </c>
       <c r="L56" t="n">
-        <v>188.14</v>
+        <v>176.31</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-17.36</v>
+        <v>-16.7</v>
       </c>
       <c r="K57" t="n">
-        <v>156.33</v>
+        <v>150.35</v>
       </c>
       <c r="L57" t="n">
-        <v>157.3</v>
+        <v>151.28</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-153.96</v>
+        <v>-162.67</v>
       </c>
       <c r="K58" t="n">
-        <v>-232.66</v>
+        <v>-245.83</v>
       </c>
       <c r="L58" t="n">
-        <v>278.98</v>
+        <v>294.78</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-53.58</v>
+        <v>-50.08</v>
       </c>
       <c r="K59" t="n">
-        <v>18.07</v>
+        <v>16.89</v>
       </c>
       <c r="L59" t="n">
-        <v>56.55</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>66.11</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>11.7</v>
+        <v>12.36</v>
       </c>
       <c r="L60" t="n">
-        <v>67.14</v>
+        <v>70.94</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-85.44</v>
+        <v>-88.72</v>
       </c>
       <c r="K61" t="n">
-        <v>26.39</v>
+        <v>27.4</v>
       </c>
       <c r="L61" t="n">
-        <v>89.42</v>
+        <v>92.84999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>30.56</v>
+        <v>29.28</v>
       </c>
       <c r="K62" t="n">
-        <v>50.19</v>
+        <v>48.1</v>
       </c>
       <c r="L62" t="n">
-        <v>58.76</v>
+        <v>56.31</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="K63" t="n">
-        <v>-36.46</v>
+        <v>-38.51</v>
       </c>
       <c r="L63" t="n">
-        <v>36.46</v>
+        <v>38.51</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>57.34</v>
+        <v>59.41</v>
       </c>
       <c r="K64" t="n">
-        <v>44.49</v>
+        <v>46.1</v>
       </c>
       <c r="L64" t="n">
-        <v>72.56999999999999</v>
+        <v>75.19</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-79.98999999999999</v>
+        <v>-74.8</v>
       </c>
       <c r="K65" t="n">
-        <v>-78.61</v>
+        <v>-73.5</v>
       </c>
       <c r="L65" t="n">
-        <v>112.15</v>
+        <v>104.87</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-131.62</v>
+        <v>-134.12</v>
       </c>
       <c r="K66" t="n">
-        <v>-20.84</v>
+        <v>-21.24</v>
       </c>
       <c r="L66" t="n">
-        <v>133.26</v>
+        <v>135.79</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-85.05</v>
+        <v>-89.76000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.6</v>
+        <v>-0.63</v>
       </c>
       <c r="L67" t="n">
-        <v>85.05</v>
+        <v>89.76000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-15.92</v>
+        <v>-16.83</v>
       </c>
       <c r="K68" t="n">
-        <v>-136.84</v>
+        <v>-144.63</v>
       </c>
       <c r="L68" t="n">
-        <v>137.76</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-15.95</v>
+        <v>-14.94</v>
       </c>
       <c r="K69" t="n">
-        <v>167.43</v>
+        <v>156.76</v>
       </c>
       <c r="L69" t="n">
-        <v>168.19</v>
+        <v>157.47</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>221.2</v>
+        <v>216.75</v>
       </c>
       <c r="K70" t="n">
-        <v>15.53</v>
+        <v>15.22</v>
       </c>
       <c r="L70" t="n">
-        <v>221.75</v>
+        <v>217.29</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>138.3</v>
+        <v>132.94</v>
       </c>
       <c r="K71" t="n">
-        <v>138.62</v>
+        <v>133.24</v>
       </c>
       <c r="L71" t="n">
-        <v>195.81</v>
+        <v>188.22</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-256.02</v>
+        <v>-271.55</v>
       </c>
       <c r="K72" t="n">
-        <v>-81.27</v>
+        <v>-86.2</v>
       </c>
       <c r="L72" t="n">
-        <v>268.61</v>
+        <v>284.9</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-96.29000000000001</v>
+        <v>-90.31</v>
       </c>
       <c r="K73" t="n">
-        <v>128.89</v>
+        <v>120.88</v>
       </c>
       <c r="L73" t="n">
-        <v>160.89</v>
+        <v>150.89</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>24.59</v>
+        <v>23.52</v>
       </c>
       <c r="K74" t="n">
-        <v>-73.15000000000001</v>
+        <v>-69.97</v>
       </c>
       <c r="L74" t="n">
-        <v>77.17</v>
+        <v>73.81999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>64.42</v>
+        <v>61.69</v>
       </c>
       <c r="K75" t="n">
-        <v>-16.47</v>
+        <v>-15.77</v>
       </c>
       <c r="L75" t="n">
-        <v>66.48999999999999</v>
+        <v>63.67</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-35.91</v>
+        <v>-35.13</v>
       </c>
       <c r="K76" t="n">
-        <v>-41.02</v>
+        <v>-40.14</v>
       </c>
       <c r="L76" t="n">
-        <v>54.52</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="77">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-38.56</v>
+        <v>-37.65</v>
       </c>
       <c r="K78" t="n">
-        <v>59.22</v>
+        <v>57.82</v>
       </c>
       <c r="L78" t="n">
-        <v>70.66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>5.23</v>
+        <v>5.43</v>
       </c>
       <c r="K79" t="n">
-        <v>-89.68000000000001</v>
+        <v>-93.02</v>
       </c>
       <c r="L79" t="n">
-        <v>89.84</v>
+        <v>93.18000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>14.05</v>
+        <v>13.15</v>
       </c>
       <c r="K80" t="n">
-        <v>-19.06</v>
+        <v>-17.84</v>
       </c>
       <c r="L80" t="n">
-        <v>23.68</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-55.97</v>
+        <v>-57.06</v>
       </c>
       <c r="K81" t="n">
-        <v>-116.5</v>
+        <v>-118.77</v>
       </c>
       <c r="L81" t="n">
-        <v>129.25</v>
+        <v>131.77</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-91.56999999999999</v>
+        <v>-91.51000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-105.9</v>
+        <v>-105.83</v>
       </c>
       <c r="L82" t="n">
-        <v>140</v>
+        <v>139.91</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-92.76000000000001</v>
+        <v>-96.39</v>
       </c>
       <c r="K83" t="n">
-        <v>-149.28</v>
+        <v>-155.12</v>
       </c>
       <c r="L83" t="n">
-        <v>175.75</v>
+        <v>182.63</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-102.72</v>
+        <v>-100.65</v>
       </c>
       <c r="K84" t="n">
-        <v>112.24</v>
+        <v>109.98</v>
       </c>
       <c r="L84" t="n">
-        <v>152.15</v>
+        <v>149.08</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>58.21</v>
+        <v>61.52</v>
       </c>
       <c r="K85" t="n">
-        <v>135.51</v>
+        <v>143.21</v>
       </c>
       <c r="L85" t="n">
-        <v>147.48</v>
+        <v>155.86</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>110.24</v>
+        <v>108.46</v>
       </c>
       <c r="K86" t="n">
-        <v>-184.59</v>
+        <v>-181.61</v>
       </c>
       <c r="L86" t="n">
-        <v>215</v>
+        <v>211.53</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-128.57</v>
+        <v>-134.47</v>
       </c>
       <c r="K87" t="n">
-        <v>19.04</v>
+        <v>19.92</v>
       </c>
       <c r="L87" t="n">
-        <v>129.97</v>
+        <v>135.94</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-212.67</v>
+        <v>-213.14</v>
       </c>
       <c r="K88" t="n">
-        <v>-101.69</v>
+        <v>-101.92</v>
       </c>
       <c r="L88" t="n">
-        <v>235.73</v>
+        <v>236.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="F14" t="n">
-        <v>8.35</v>
+        <v>9.59</v>
       </c>
       <c r="G14" t="n">
-        <v>157.4</v>
+        <v>160</v>
       </c>
       <c r="H14" t="n">
-        <v>72.09999999999999</v>
+        <v>54.6</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>76.76000000000001</v>
+        <v>-52.22</v>
       </c>
       <c r="K14" t="n">
-        <v>-23.84</v>
+        <v>-24.64</v>
       </c>
       <c r="L14" t="n">
-        <v>80.38</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:07:01</t>
+          <t>07:06:50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="F15" t="n">
-        <v>6.28</v>
+        <v>6.4</v>
       </c>
       <c r="G15" t="n">
-        <v>164.7</v>
+        <v>171.1</v>
       </c>
       <c r="H15" t="n">
-        <v>81.40000000000001</v>
+        <v>30.9</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>-53.49</v>
+        <v>-39.42</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.31</v>
+        <v>43.52</v>
       </c>
       <c r="L15" t="n">
-        <v>54.29</v>
+        <v>58.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:09:26</t>
+          <t>07:08:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3</v>
+        <v>2.47</v>
       </c>
       <c r="F16" t="n">
-        <v>8.9</v>
+        <v>5.48</v>
       </c>
       <c r="G16" t="n">
-        <v>176.5</v>
+        <v>173.9</v>
       </c>
       <c r="H16" t="n">
-        <v>80.8</v>
+        <v>64</v>
       </c>
       <c r="I16" t="n">
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>91.94</v>
+        <v>45.53</v>
       </c>
       <c r="K16" t="n">
-        <v>-9.59</v>
+        <v>-23.3</v>
       </c>
       <c r="L16" t="n">
-        <v>92.43000000000001</v>
+        <v>51.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:14:38</t>
+          <t>07:14:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="F17" t="n">
-        <v>9.91</v>
+        <v>5.48</v>
       </c>
       <c r="G17" t="n">
-        <v>184.4</v>
+        <v>171.6</v>
       </c>
       <c r="H17" t="n">
-        <v>76.2</v>
+        <v>55.5</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>34.96</v>
+        <v>-7.15</v>
       </c>
       <c r="K17" t="n">
-        <v>-63.48</v>
+        <v>-90.37</v>
       </c>
       <c r="L17" t="n">
-        <v>72.45999999999999</v>
+        <v>90.65000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:16:48</t>
+          <t>07:16:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="F18" t="n">
-        <v>9.24</v>
+        <v>5.86</v>
       </c>
       <c r="G18" t="n">
-        <v>163.9</v>
+        <v>174.8</v>
       </c>
       <c r="H18" t="n">
-        <v>77.8</v>
+        <v>30.1</v>
       </c>
       <c r="I18" t="n">
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>87.12</v>
+        <v>-66.87</v>
       </c>
       <c r="K18" t="n">
-        <v>4.44</v>
+        <v>46.73</v>
       </c>
       <c r="L18" t="n">
-        <v>87.23999999999999</v>
+        <v>81.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:19:12</t>
+          <t>07:18:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="F19" t="n">
-        <v>7.64</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>164.5</v>
+        <v>165.4</v>
       </c>
       <c r="H19" t="n">
-        <v>72.5</v>
+        <v>51.7</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>44.06</v>
+        <v>-5.86</v>
       </c>
       <c r="K19" t="n">
-        <v>69.92</v>
+        <v>-62.82</v>
       </c>
       <c r="L19" t="n">
-        <v>82.64</v>
+        <v>63.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:23:29</t>
+          <t>07:23:14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.93</v>
+        <v>2.68</v>
       </c>
       <c r="F20" t="n">
-        <v>7.31</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>160.4</v>
+        <v>163.9</v>
       </c>
       <c r="H20" t="n">
-        <v>68.8</v>
+        <v>50.9</v>
       </c>
       <c r="I20" t="n">
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-145.18</v>
+        <v>-69.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-60.31</v>
+        <v>-91.20999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>157.21</v>
+        <v>114.62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:24:27</t>
+          <t>07:24:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="F21" t="n">
-        <v>7.07</v>
+        <v>10.12</v>
       </c>
       <c r="G21" t="n">
-        <v>172.8</v>
+        <v>159.6</v>
       </c>
       <c r="H21" t="n">
-        <v>75.90000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>15.74</v>
+        <v>97.42</v>
       </c>
       <c r="K21" t="n">
-        <v>90.53</v>
+        <v>-80.68000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>91.89</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:25:18</t>
+          <t>07:25:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.48</v>
+        <v>2.69</v>
       </c>
       <c r="F22" t="n">
-        <v>9.140000000000001</v>
+        <v>6.27</v>
       </c>
       <c r="G22" t="n">
-        <v>161.9</v>
+        <v>171.9</v>
       </c>
       <c r="H22" t="n">
-        <v>74.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>24.17</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>128.68</v>
+        <v>-73.84</v>
       </c>
       <c r="L22" t="n">
-        <v>130.93</v>
+        <v>98.70999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:30:15</t>
+          <t>07:29:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="F23" t="n">
-        <v>6.68</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>175.9</v>
+        <v>154.8</v>
       </c>
       <c r="H23" t="n">
-        <v>71.5</v>
+        <v>55.3</v>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J23" t="n">
-        <v>-81.2</v>
+        <v>70.33</v>
       </c>
       <c r="K23" t="n">
-        <v>-129.88</v>
+        <v>-105.24</v>
       </c>
       <c r="L23" t="n">
-        <v>153.17</v>
+        <v>126.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:32:58</t>
+          <t>07:30:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="F24" t="n">
-        <v>9.65</v>
+        <v>8.16</v>
       </c>
       <c r="G24" t="n">
-        <v>156.2</v>
+        <v>164</v>
       </c>
       <c r="H24" t="n">
-        <v>76.5</v>
+        <v>30</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-161.67</v>
+        <v>-14.6</v>
       </c>
       <c r="K24" t="n">
-        <v>-133.74</v>
+        <v>184.37</v>
       </c>
       <c r="L24" t="n">
-        <v>209.82</v>
+        <v>184.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:34:07</t>
+          <t>07:32:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="F25" t="n">
-        <v>6.05</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>159.8</v>
+        <v>166</v>
       </c>
       <c r="H25" t="n">
-        <v>76.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>-40.15</v>
+        <v>-75.70999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-117.81</v>
+        <v>-188.39</v>
       </c>
       <c r="L25" t="n">
-        <v>124.46</v>
+        <v>203.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:39:07</t>
+          <t>07:36:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="F26" t="n">
-        <v>9.92</v>
+        <v>7.94</v>
       </c>
       <c r="G26" t="n">
-        <v>159.6</v>
+        <v>169.5</v>
       </c>
       <c r="H26" t="n">
-        <v>71.5</v>
+        <v>39.2</v>
       </c>
       <c r="I26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-94.90000000000001</v>
+        <v>219.17</v>
       </c>
       <c r="K26" t="n">
-        <v>140.74</v>
+        <v>-23.8</v>
       </c>
       <c r="L26" t="n">
-        <v>169.75</v>
+        <v>220.46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:41:00</t>
+          <t>07:37:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="F27" t="n">
-        <v>7.83</v>
+        <v>9.6</v>
       </c>
       <c r="G27" t="n">
-        <v>172.7</v>
+        <v>177.1</v>
       </c>
       <c r="H27" t="n">
-        <v>80.5</v>
+        <v>71.3</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-137.74</v>
+        <v>-255.93</v>
       </c>
       <c r="K27" t="n">
-        <v>-135.83</v>
+        <v>11.96</v>
       </c>
       <c r="L27" t="n">
-        <v>193.45</v>
+        <v>256.21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:43:03</t>
+          <t>07:39:23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.29</v>
+        <v>2.93</v>
       </c>
       <c r="F28" t="n">
-        <v>9.75</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>171.3</v>
+        <v>162.6</v>
       </c>
       <c r="H28" t="n">
-        <v>67.90000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="I28" t="n">
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>32.6</v>
+        <v>232.42</v>
       </c>
       <c r="K28" t="n">
-        <v>220.68</v>
+        <v>2.76</v>
       </c>
       <c r="L28" t="n">
-        <v>223.08</v>
+        <v>232.43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:54:49</t>
+          <t>07:49:01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="F29" t="n">
-        <v>5.56</v>
+        <v>7.94</v>
       </c>
       <c r="G29" t="n">
-        <v>179.7</v>
+        <v>165.8</v>
       </c>
       <c r="H29" t="n">
-        <v>76.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-32.3</v>
+        <v>-39.55</v>
       </c>
       <c r="K29" t="n">
-        <v>-42.04</v>
+        <v>-12.97</v>
       </c>
       <c r="L29" t="n">
-        <v>53.02</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:55:23</t>
+          <t>07:50:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="F30" t="n">
         <v>10.12</v>
       </c>
       <c r="G30" t="n">
-        <v>153.3</v>
+        <v>172.7</v>
       </c>
       <c r="H30" t="n">
-        <v>79.5</v>
+        <v>38.7</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>6.63</v>
+        <v>-25.81</v>
       </c>
       <c r="K30" t="n">
-        <v>-67.83</v>
+        <v>-47.27</v>
       </c>
       <c r="L30" t="n">
-        <v>68.15000000000001</v>
+        <v>53.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:56:40</t>
+          <t>07:52:11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="F31" t="n">
-        <v>10.12</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>165.6</v>
+        <v>161.2</v>
       </c>
       <c r="H31" t="n">
-        <v>71.5</v>
+        <v>45.3</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>38.57</v>
+        <v>40.95</v>
       </c>
       <c r="K31" t="n">
-        <v>44.77</v>
+        <v>-27.51</v>
       </c>
       <c r="L31" t="n">
-        <v>59.09</v>
+        <v>49.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:02:23</t>
+          <t>07:57:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.36</v>
+        <v>2.82</v>
       </c>
       <c r="F32" t="n">
-        <v>10.12</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>154.5</v>
+        <v>165.1</v>
       </c>
       <c r="H32" t="n">
-        <v>71</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>97.2</v>
+        <v>63.05</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.36</v>
+        <v>22.52</v>
       </c>
       <c r="L32" t="n">
-        <v>97.41</v>
+        <v>66.95</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:03:59</t>
+          <t>07:58:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.66</v>
+        <v>3.31</v>
       </c>
       <c r="F33" t="n">
-        <v>8.08</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>165.4</v>
+        <v>149.4</v>
       </c>
       <c r="H33" t="n">
-        <v>69.7</v>
+        <v>40.3</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>44.21</v>
+        <v>70.84</v>
       </c>
       <c r="K33" t="n">
-        <v>-63.3</v>
+        <v>-57.31</v>
       </c>
       <c r="L33" t="n">
-        <v>77.20999999999999</v>
+        <v>91.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:06:32</t>
+          <t>08:00:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="F34" t="n">
-        <v>10.12</v>
+        <v>5.38</v>
       </c>
       <c r="G34" t="n">
-        <v>161.1</v>
+        <v>165.7</v>
       </c>
       <c r="H34" t="n">
-        <v>78</v>
+        <v>36.6</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>34.9</v>
+        <v>-85.34999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-65.20999999999999</v>
+        <v>15.12</v>
       </c>
       <c r="L34" t="n">
-        <v>73.95999999999999</v>
+        <v>86.68000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:10:29</t>
+          <t>08:05:29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="F35" t="n">
-        <v>6.55</v>
+        <v>6.38</v>
       </c>
       <c r="G35" t="n">
-        <v>185.3</v>
+        <v>166.6</v>
       </c>
       <c r="H35" t="n">
-        <v>73.3</v>
+        <v>72.3</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-81.43000000000001</v>
+        <v>36.49</v>
       </c>
       <c r="K35" t="n">
-        <v>-119.79</v>
+        <v>-96.15000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>144.85</v>
+        <v>102.84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:12:23</t>
+          <t>08:07:35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.23</v>
+        <v>3.6</v>
       </c>
       <c r="F36" t="n">
         <v>10.12</v>
       </c>
       <c r="G36" t="n">
-        <v>149.4</v>
+        <v>172.3</v>
       </c>
       <c r="H36" t="n">
-        <v>75.5</v>
+        <v>60.6</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-96.18000000000001</v>
+        <v>-129.04</v>
       </c>
       <c r="K36" t="n">
-        <v>45.39</v>
+        <v>-45.68</v>
       </c>
       <c r="L36" t="n">
-        <v>106.35</v>
+        <v>136.88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:13:29</t>
+          <t>08:09:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="F37" t="n">
-        <v>8.779999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>167.3</v>
+        <v>154.2</v>
       </c>
       <c r="H37" t="n">
-        <v>80.2</v>
+        <v>49.1</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>134.42</v>
+        <v>-111.61</v>
       </c>
       <c r="K37" t="n">
-        <v>-32.79</v>
+        <v>33.86</v>
       </c>
       <c r="L37" t="n">
-        <v>138.36</v>
+        <v>116.63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:18:03</t>
+          <t>08:15:02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.36</v>
+        <v>4.13</v>
       </c>
       <c r="F38" t="n">
-        <v>9.43</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>167.9</v>
+        <v>160.9</v>
       </c>
       <c r="H38" t="n">
-        <v>71.2</v>
+        <v>53.5</v>
       </c>
       <c r="I38" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>-55.41</v>
+        <v>-218.64</v>
       </c>
       <c r="K38" t="n">
-        <v>-117.5</v>
+        <v>-66.31999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>129.91</v>
+        <v>228.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:19:53</t>
+          <t>08:16:26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="F39" t="n">
-        <v>6.46</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>164.3</v>
+        <v>162.8</v>
       </c>
       <c r="H39" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>124.32</v>
+        <v>-61.93</v>
       </c>
       <c r="K39" t="n">
-        <v>-80.48999999999999</v>
+        <v>-126.93</v>
       </c>
       <c r="L39" t="n">
-        <v>148.11</v>
+        <v>141.24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:21:47</t>
+          <t>08:19:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.84</v>
+        <v>3.34</v>
       </c>
       <c r="F40" t="n">
-        <v>8.84</v>
+        <v>8.98</v>
       </c>
       <c r="G40" t="n">
-        <v>160.9</v>
+        <v>159.5</v>
       </c>
       <c r="H40" t="n">
-        <v>74.90000000000001</v>
+        <v>51.1</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>120.56</v>
+        <v>51.77</v>
       </c>
       <c r="K40" t="n">
-        <v>-84.58</v>
+        <v>-264.01</v>
       </c>
       <c r="L40" t="n">
-        <v>147.27</v>
+        <v>269.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:26:53</t>
+          <t>08:23:10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.39</v>
+        <v>3.17</v>
       </c>
       <c r="F41" t="n">
-        <v>8.9</v>
+        <v>10.12</v>
       </c>
       <c r="G41" t="n">
-        <v>167.4</v>
+        <v>160.7</v>
       </c>
       <c r="H41" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J41" t="n">
-        <v>-136.73</v>
+        <v>19.53</v>
       </c>
       <c r="K41" t="n">
-        <v>-202.25</v>
+        <v>-196.82</v>
       </c>
       <c r="L41" t="n">
-        <v>244.13</v>
+        <v>197.79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:28:06</t>
+          <t>08:24:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.09</v>
+        <v>3.41</v>
       </c>
       <c r="F42" t="n">
-        <v>8.85</v>
+        <v>10.12</v>
       </c>
       <c r="G42" t="n">
-        <v>159.8</v>
+        <v>157.2</v>
       </c>
       <c r="H42" t="n">
-        <v>75.5</v>
+        <v>50.2</v>
       </c>
       <c r="I42" t="n">
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>214.59</v>
+        <v>206.24</v>
       </c>
       <c r="K42" t="n">
-        <v>-80.3</v>
+        <v>94.27</v>
       </c>
       <c r="L42" t="n">
-        <v>229.12</v>
+        <v>226.76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:29:42</t>
+          <t>08:26:06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="F43" t="n">
-        <v>8.5</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>153.6</v>
+        <v>172.3</v>
       </c>
       <c r="H43" t="n">
-        <v>67.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>194.41</v>
+        <v>179.28</v>
       </c>
       <c r="K43" t="n">
-        <v>165.37</v>
+        <v>-16.81</v>
       </c>
       <c r="L43" t="n">
-        <v>255.22</v>
+        <v>180.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:42:06</t>
+          <t>08:37:10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.29</v>
+        <v>3.47</v>
       </c>
       <c r="F44" t="n">
-        <v>8.52</v>
+        <v>9.01</v>
       </c>
       <c r="G44" t="n">
-        <v>153.1</v>
+        <v>167.9</v>
       </c>
       <c r="H44" t="n">
-        <v>68.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I44" t="n">
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>26.55</v>
+        <v>-2.53</v>
       </c>
       <c r="K44" t="n">
-        <v>91.36</v>
+        <v>59.23</v>
       </c>
       <c r="L44" t="n">
-        <v>95.14</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:44:25</t>
+          <t>08:39:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="F45" t="n">
-        <v>8.83</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>168</v>
+        <v>156.2</v>
       </c>
       <c r="H45" t="n">
-        <v>72.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>12.72</v>
+        <v>-58.47</v>
       </c>
       <c r="K45" t="n">
-        <v>55.82</v>
+        <v>13.67</v>
       </c>
       <c r="L45" t="n">
-        <v>57.25</v>
+        <v>60.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:45:31</t>
+          <t>08:41:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="F46" t="n">
         <v>10.12</v>
       </c>
       <c r="G46" t="n">
-        <v>162.9</v>
+        <v>165.8</v>
       </c>
       <c r="H46" t="n">
-        <v>72.59999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>-66.40000000000001</v>
+        <v>41.53</v>
       </c>
       <c r="K46" t="n">
-        <v>-21.9</v>
+        <v>-16.99</v>
       </c>
       <c r="L46" t="n">
-        <v>69.92</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:51:12</t>
+          <t>08:47:06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.58</v>
+        <v>3.19</v>
       </c>
       <c r="F47" t="n">
-        <v>9.65</v>
+        <v>10.12</v>
       </c>
       <c r="G47" t="n">
-        <v>174</v>
+        <v>163.7</v>
       </c>
       <c r="H47" t="n">
-        <v>74.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>1.62</v>
+        <v>35.5</v>
       </c>
       <c r="K47" t="n">
-        <v>77.97</v>
+        <v>-76.87</v>
       </c>
       <c r="L47" t="n">
-        <v>77.98999999999999</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:53:20</t>
+          <t>08:48:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.36</v>
+        <v>3.54</v>
       </c>
       <c r="F48" t="n">
-        <v>8.140000000000001</v>
+        <v>8.02</v>
       </c>
       <c r="G48" t="n">
-        <v>157.1</v>
+        <v>167.7</v>
       </c>
       <c r="H48" t="n">
-        <v>77.8</v>
+        <v>52</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>10.63</v>
+        <v>38.94</v>
       </c>
       <c r="K48" t="n">
-        <v>-118.75</v>
+        <v>-108.68</v>
       </c>
       <c r="L48" t="n">
-        <v>119.23</v>
+        <v>115.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:55:42</t>
+          <t>08:50:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.74</v>
+        <v>3.43</v>
       </c>
       <c r="F49" t="n">
-        <v>9.949999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="G49" t="n">
-        <v>158.2</v>
+        <v>167.3</v>
       </c>
       <c r="H49" t="n">
-        <v>76.2</v>
+        <v>62.7</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-56.21</v>
+        <v>-86.16</v>
       </c>
       <c r="K49" t="n">
-        <v>-41.12</v>
+        <v>-43.38</v>
       </c>
       <c r="L49" t="n">
-        <v>69.64</v>
+        <v>96.47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:00:41</t>
+          <t>08:53:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.14</v>
+        <v>3.76</v>
       </c>
       <c r="F50" t="n">
-        <v>9.390000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>170.2</v>
+        <v>165.9</v>
       </c>
       <c r="H50" t="n">
-        <v>76</v>
+        <v>61.5</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-74.89</v>
+        <v>109.16</v>
       </c>
       <c r="K50" t="n">
-        <v>122.48</v>
+        <v>-89.41</v>
       </c>
       <c r="L50" t="n">
-        <v>143.56</v>
+        <v>141.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:01:57</t>
+          <t>08:54:32</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.56</v>
+        <v>3.08</v>
       </c>
       <c r="F51" t="n">
-        <v>10.12</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>155.5</v>
+        <v>167.3</v>
       </c>
       <c r="H51" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-1.51</v>
+        <v>12.12</v>
       </c>
       <c r="K51" t="n">
-        <v>-85.83</v>
+        <v>-100.5</v>
       </c>
       <c r="L51" t="n">
-        <v>85.84999999999999</v>
+        <v>101.23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:04:17</t>
+          <t>08:55:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.6</v>
+        <v>3.18</v>
       </c>
       <c r="F52" t="n">
-        <v>5.62</v>
+        <v>8.16</v>
       </c>
       <c r="G52" t="n">
-        <v>172.1</v>
+        <v>151.8</v>
       </c>
       <c r="H52" t="n">
-        <v>71.5</v>
+        <v>69.5</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-94.79000000000001</v>
+        <v>121.36</v>
       </c>
       <c r="K52" t="n">
-        <v>2.82</v>
+        <v>32.45</v>
       </c>
       <c r="L52" t="n">
-        <v>94.83</v>
+        <v>125.62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:07:41</t>
+          <t>09:00:02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="F53" t="n">
         <v>10.12</v>
       </c>
       <c r="G53" t="n">
-        <v>153</v>
+        <v>185.1</v>
       </c>
       <c r="H53" t="n">
-        <v>68.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>67.41</v>
+        <v>-101.83</v>
       </c>
       <c r="K53" t="n">
-        <v>-174.64</v>
+        <v>-291.46</v>
       </c>
       <c r="L53" t="n">
-        <v>187.2</v>
+        <v>308.73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:09:46</t>
+          <t>09:01:08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="F54" t="n">
-        <v>4.64</v>
+        <v>7.05</v>
       </c>
       <c r="G54" t="n">
-        <v>173.7</v>
+        <v>167.6</v>
       </c>
       <c r="H54" t="n">
-        <v>77.7</v>
+        <v>65.2</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-128.27</v>
+        <v>134.7</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.84</v>
+        <v>-159.98</v>
       </c>
       <c r="L54" t="n">
-        <v>128.33</v>
+        <v>209.13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:11:20</t>
+          <t>09:02:39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.46</v>
+        <v>3.06</v>
       </c>
       <c r="F55" t="n">
-        <v>10.12</v>
+        <v>9.73</v>
       </c>
       <c r="G55" t="n">
-        <v>168.3</v>
+        <v>169.2</v>
       </c>
       <c r="H55" t="n">
-        <v>71.90000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J55" t="n">
-        <v>155.57</v>
+        <v>171.9</v>
       </c>
       <c r="K55" t="n">
-        <v>39.08</v>
+        <v>-34.37</v>
       </c>
       <c r="L55" t="n">
-        <v>160.41</v>
+        <v>175.31</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:16:11</t>
+          <t>09:07:06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.36</v>
+        <v>3.77</v>
       </c>
       <c r="F56" t="n">
-        <v>7.25</v>
+        <v>10.04</v>
       </c>
       <c r="G56" t="n">
-        <v>158.9</v>
+        <v>173.8</v>
       </c>
       <c r="H56" t="n">
-        <v>71.09999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>167.24</v>
+        <v>60.97</v>
       </c>
       <c r="K56" t="n">
-        <v>55.81</v>
+        <v>-308.47</v>
       </c>
       <c r="L56" t="n">
-        <v>176.31</v>
+        <v>314.44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:18:24</t>
+          <t>09:09:18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.68</v>
+        <v>3.39</v>
       </c>
       <c r="F57" t="n">
-        <v>8.949999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="G57" t="n">
-        <v>170.6</v>
+        <v>164</v>
       </c>
       <c r="H57" t="n">
-        <v>71.5</v>
+        <v>55.2</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-16.7</v>
+        <v>272.41</v>
       </c>
       <c r="K57" t="n">
-        <v>150.35</v>
+        <v>6.94</v>
       </c>
       <c r="L57" t="n">
-        <v>151.28</v>
+        <v>272.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:20:07</t>
+          <t>09:11:40</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="F58" t="n">
-        <v>6.8</v>
+        <v>7.85</v>
       </c>
       <c r="G58" t="n">
-        <v>164.6</v>
+        <v>162</v>
       </c>
       <c r="H58" t="n">
-        <v>75.59999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-162.67</v>
+        <v>-193.62</v>
       </c>
       <c r="K58" t="n">
-        <v>-245.83</v>
+        <v>104.55</v>
       </c>
       <c r="L58" t="n">
-        <v>294.78</v>
+        <v>220.05</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:28:45</t>
+          <t>09:20:41</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.59</v>
+        <v>2.86</v>
       </c>
       <c r="F59" t="n">
-        <v>10.12</v>
+        <v>9.43</v>
       </c>
       <c r="G59" t="n">
-        <v>167.7</v>
+        <v>163.9</v>
       </c>
       <c r="H59" t="n">
-        <v>78.09999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="I59" t="n">
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-50.08</v>
+        <v>-31.35</v>
       </c>
       <c r="K59" t="n">
-        <v>16.89</v>
+        <v>11.04</v>
       </c>
       <c r="L59" t="n">
-        <v>52.85</v>
+        <v>33.24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:30:14</t>
+          <t>09:23:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="F60" t="n">
-        <v>7.19</v>
+        <v>10.12</v>
       </c>
       <c r="G60" t="n">
-        <v>154.4</v>
+        <v>158</v>
       </c>
       <c r="H60" t="n">
-        <v>71.8</v>
+        <v>45.8</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>69.84999999999999</v>
+        <v>31.32</v>
       </c>
       <c r="K60" t="n">
-        <v>12.36</v>
+        <v>-34.37</v>
       </c>
       <c r="L60" t="n">
-        <v>70.94</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:31:09</t>
+          <t>09:25:21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.26</v>
+        <v>3.78</v>
       </c>
       <c r="F61" t="n">
-        <v>9.630000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="G61" t="n">
-        <v>157</v>
+        <v>169.5</v>
       </c>
       <c r="H61" t="n">
-        <v>75.09999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-88.72</v>
+        <v>28.52</v>
       </c>
       <c r="K61" t="n">
-        <v>27.4</v>
+        <v>45.54</v>
       </c>
       <c r="L61" t="n">
-        <v>92.84999999999999</v>
+        <v>53.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:37:19</t>
+          <t>09:29:49</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.09</v>
+        <v>3.36</v>
       </c>
       <c r="F62" t="n">
-        <v>4.92</v>
+        <v>9.44</v>
       </c>
       <c r="G62" t="n">
-        <v>152.2</v>
+        <v>159.7</v>
       </c>
       <c r="H62" t="n">
-        <v>81.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J62" t="n">
-        <v>29.28</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>48.1</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>56.31</v>
+        <v>73.45999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:38:05</t>
+          <t>09:31:23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.32</v>
+        <v>3.53</v>
       </c>
       <c r="F63" t="n">
-        <v>8.34</v>
+        <v>10.12</v>
       </c>
       <c r="G63" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H63" t="n">
-        <v>73.2</v>
+        <v>52.5</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J63" t="n">
-        <v>0.47</v>
+        <v>35.26</v>
       </c>
       <c r="K63" t="n">
-        <v>-38.51</v>
+        <v>-12.87</v>
       </c>
       <c r="L63" t="n">
-        <v>38.51</v>
+        <v>37.54</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:39:22</t>
+          <t>09:33:01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="F64" t="n">
-        <v>9.74</v>
+        <v>7.72</v>
       </c>
       <c r="G64" t="n">
-        <v>167.6</v>
+        <v>157.1</v>
       </c>
       <c r="H64" t="n">
-        <v>79.2</v>
+        <v>48.5</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>59.41</v>
+        <v>55.33</v>
       </c>
       <c r="K64" t="n">
-        <v>46.1</v>
+        <v>-93.09999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>75.19</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:44:08</t>
+          <t>09:38:28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.93</v>
+        <v>3.11</v>
       </c>
       <c r="F65" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="G65" t="n">
-        <v>164.4</v>
+        <v>169</v>
       </c>
       <c r="H65" t="n">
-        <v>72.09999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="I65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-74.8</v>
+        <v>85.36</v>
       </c>
       <c r="K65" t="n">
-        <v>-73.5</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>104.87</v>
+        <v>109.28</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:46:05</t>
+          <t>09:40:20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="F66" t="n">
-        <v>10.12</v>
+        <v>9.06</v>
       </c>
       <c r="G66" t="n">
-        <v>157.4</v>
+        <v>170</v>
       </c>
       <c r="H66" t="n">
-        <v>70.5</v>
+        <v>32.3</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>-134.12</v>
+        <v>32.77</v>
       </c>
       <c r="K66" t="n">
-        <v>-21.24</v>
+        <v>-51.54</v>
       </c>
       <c r="L66" t="n">
-        <v>135.79</v>
+        <v>61.07</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:47:32</t>
+          <t>09:41:47</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.95</v>
+        <v>3.41</v>
       </c>
       <c r="F67" t="n">
         <v>10.12</v>
       </c>
       <c r="G67" t="n">
-        <v>164.3</v>
+        <v>174.6</v>
       </c>
       <c r="H67" t="n">
-        <v>74.40000000000001</v>
+        <v>54.4</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-89.76000000000001</v>
+        <v>107.11</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.63</v>
+        <v>54.27</v>
       </c>
       <c r="L67" t="n">
-        <v>89.76000000000001</v>
+        <v>120.08</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:50:20</t>
+          <t>09:47:31</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.5</v>
+        <v>4.34</v>
       </c>
       <c r="F68" t="n">
         <v>10.12</v>
       </c>
       <c r="G68" t="n">
-        <v>174.6</v>
+        <v>170.6</v>
       </c>
       <c r="H68" t="n">
-        <v>76.90000000000001</v>
+        <v>55.9</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J68" t="n">
-        <v>-16.83</v>
+        <v>133.84</v>
       </c>
       <c r="K68" t="n">
-        <v>-144.63</v>
+        <v>-292.42</v>
       </c>
       <c r="L68" t="n">
-        <v>145.6</v>
+        <v>321.59</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:52:23</t>
+          <t>09:49:23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.34</v>
+        <v>2.98</v>
       </c>
       <c r="F69" t="n">
-        <v>9.51</v>
+        <v>8.18</v>
       </c>
       <c r="G69" t="n">
-        <v>166.5</v>
+        <v>163.3</v>
       </c>
       <c r="H69" t="n">
-        <v>70.40000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-14.94</v>
+        <v>53.16</v>
       </c>
       <c r="K69" t="n">
-        <v>156.76</v>
+        <v>345.13</v>
       </c>
       <c r="L69" t="n">
-        <v>157.47</v>
+        <v>349.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:54:00</t>
+          <t>09:50:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="F70" t="n">
         <v>10.12</v>
       </c>
       <c r="G70" t="n">
-        <v>149.5</v>
+        <v>167.7</v>
       </c>
       <c r="H70" t="n">
-        <v>73.2</v>
+        <v>70.8</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>216.75</v>
+        <v>80.42</v>
       </c>
       <c r="K70" t="n">
-        <v>15.22</v>
+        <v>211.54</v>
       </c>
       <c r="L70" t="n">
-        <v>217.29</v>
+        <v>226.31</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:58:19</t>
+          <t>09:56:45</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.61</v>
+        <v>3.27</v>
       </c>
       <c r="F71" t="n">
         <v>10.12</v>
       </c>
       <c r="G71" t="n">
-        <v>152.8</v>
+        <v>156.7</v>
       </c>
       <c r="H71" t="n">
-        <v>75.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>132.94</v>
+        <v>-70.25</v>
       </c>
       <c r="K71" t="n">
-        <v>133.24</v>
+        <v>-134.64</v>
       </c>
       <c r="L71" t="n">
-        <v>188.22</v>
+        <v>151.87</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:00:39</t>
+          <t>09:58:12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="F72" t="n">
-        <v>8.5</v>
+        <v>10.12</v>
       </c>
       <c r="G72" t="n">
-        <v>159.3</v>
+        <v>179</v>
       </c>
       <c r="H72" t="n">
-        <v>76.7</v>
+        <v>85.8</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-271.55</v>
+        <v>-128.98</v>
       </c>
       <c r="K72" t="n">
-        <v>-86.2</v>
+        <v>227.38</v>
       </c>
       <c r="L72" t="n">
-        <v>284.9</v>
+        <v>261.41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:02:14</t>
+          <t>09:59:18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.46</v>
+        <v>4.01</v>
       </c>
       <c r="F73" t="n">
-        <v>8.48</v>
+        <v>10.12</v>
       </c>
       <c r="G73" t="n">
-        <v>169.5</v>
+        <v>162.9</v>
       </c>
       <c r="H73" t="n">
-        <v>75.09999999999999</v>
+        <v>39.4</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-90.31</v>
+        <v>-300.18</v>
       </c>
       <c r="K73" t="n">
-        <v>120.88</v>
+        <v>41.29</v>
       </c>
       <c r="L73" t="n">
-        <v>150.89</v>
+        <v>303</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:13:26</t>
+          <t>10:12:52</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.63</v>
+        <v>3.39</v>
       </c>
       <c r="F74" t="n">
         <v>10.12</v>
       </c>
       <c r="G74" t="n">
-        <v>164.8</v>
+        <v>167.6</v>
       </c>
       <c r="H74" t="n">
-        <v>67.5</v>
+        <v>17.6</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>23.52</v>
+        <v>45.75</v>
       </c>
       <c r="K74" t="n">
-        <v>-69.97</v>
+        <v>-2.16</v>
       </c>
       <c r="L74" t="n">
-        <v>73.81999999999999</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:14:38</t>
+          <t>10:14:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.41</v>
+        <v>3.16</v>
       </c>
       <c r="F75" t="n">
-        <v>9.94</v>
+        <v>10.12</v>
       </c>
       <c r="G75" t="n">
-        <v>156.7</v>
+        <v>148.8</v>
       </c>
       <c r="H75" t="n">
-        <v>82</v>
+        <v>56.1</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>61.69</v>
+        <v>13.16</v>
       </c>
       <c r="K75" t="n">
-        <v>-15.77</v>
+        <v>-61.4</v>
       </c>
       <c r="L75" t="n">
-        <v>63.67</v>
+        <v>62.79</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:16:29</t>
+          <t>10:16:19</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.49</v>
+        <v>3.14</v>
       </c>
       <c r="F76" t="n">
-        <v>10.12</v>
+        <v>7.23</v>
       </c>
       <c r="G76" t="n">
-        <v>161.9</v>
+        <v>157.9</v>
       </c>
       <c r="H76" t="n">
-        <v>72</v>
+        <v>62.7</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-35.13</v>
+        <v>-22.61</v>
       </c>
       <c r="K76" t="n">
-        <v>-40.14</v>
+        <v>47.22</v>
       </c>
       <c r="L76" t="n">
-        <v>53.34</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:20:51</t>
+          <t>10:20:37</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.88</v>
+        <v>3.37</v>
       </c>
       <c r="F77" t="n">
-        <v>7.68</v>
+        <v>10.12</v>
       </c>
       <c r="G77" t="n">
-        <v>162.3</v>
+        <v>161.4</v>
       </c>
       <c r="H77" t="n">
-        <v>73</v>
+        <v>67.8</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-44.07</v>
+        <v>36.04</v>
       </c>
       <c r="K77" t="n">
-        <v>51.04</v>
+        <v>33.58</v>
       </c>
       <c r="L77" t="n">
-        <v>67.43000000000001</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:23:15</t>
+          <t>10:23:07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="F78" t="n">
-        <v>10.12</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>167.1</v>
+        <v>154.9</v>
       </c>
       <c r="H78" t="n">
-        <v>81.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J78" t="n">
-        <v>-37.65</v>
+        <v>53.37</v>
       </c>
       <c r="K78" t="n">
-        <v>57.82</v>
+        <v>-30.65</v>
       </c>
       <c r="L78" t="n">
-        <v>69</v>
+        <v>61.54</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:24:17</t>
+          <t>10:24:07</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.5</v>
+        <v>3.91</v>
       </c>
       <c r="F79" t="n">
-        <v>9.83</v>
+        <v>10.12</v>
       </c>
       <c r="G79" t="n">
-        <v>158</v>
+        <v>160.1</v>
       </c>
       <c r="H79" t="n">
-        <v>74.8</v>
+        <v>34.3</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>5.43</v>
+        <v>18.1</v>
       </c>
       <c r="K79" t="n">
-        <v>-93.02</v>
+        <v>-97.52</v>
       </c>
       <c r="L79" t="n">
-        <v>93.18000000000001</v>
+        <v>99.18000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:28:33</t>
+          <t>10:27:34</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.38</v>
+        <v>3.06</v>
       </c>
       <c r="F80" t="n">
-        <v>10.12</v>
+        <v>6.59</v>
       </c>
       <c r="G80" t="n">
-        <v>156.5</v>
+        <v>160.5</v>
       </c>
       <c r="H80" t="n">
-        <v>70.8</v>
+        <v>18.9</v>
       </c>
       <c r="I80" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>13.15</v>
+        <v>-41.81</v>
       </c>
       <c r="K80" t="n">
-        <v>-17.84</v>
+        <v>-125.74</v>
       </c>
       <c r="L80" t="n">
-        <v>22.16</v>
+        <v>132.51</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:30:04</t>
+          <t>10:28:53</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="F81" t="n">
         <v>10.12</v>
       </c>
       <c r="G81" t="n">
-        <v>165.5</v>
+        <v>166.8</v>
       </c>
       <c r="H81" t="n">
-        <v>78.7</v>
+        <v>81</v>
       </c>
       <c r="I81" t="n">
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-57.06</v>
+        <v>55.49</v>
       </c>
       <c r="K81" t="n">
-        <v>-118.77</v>
+        <v>-144.63</v>
       </c>
       <c r="L81" t="n">
-        <v>131.77</v>
+        <v>154.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:31:36</t>
+          <t>10:31:16</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="F82" t="n">
-        <v>10.12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>159</v>
+        <v>175.6</v>
       </c>
       <c r="H82" t="n">
-        <v>73.2</v>
+        <v>30.6</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-91.51000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="K82" t="n">
-        <v>-105.83</v>
+        <v>-17</v>
       </c>
       <c r="L82" t="n">
-        <v>139.91</v>
+        <v>95.64</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:35:44</t>
+          <t>10:36:20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.79</v>
+        <v>3.14</v>
       </c>
       <c r="F83" t="n">
         <v>10.12</v>
       </c>
       <c r="G83" t="n">
-        <v>171.1</v>
+        <v>168</v>
       </c>
       <c r="H83" t="n">
-        <v>73.7</v>
+        <v>58.5</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>-96.39</v>
+        <v>96.8</v>
       </c>
       <c r="K83" t="n">
-        <v>-155.12</v>
+        <v>-82.93000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>182.63</v>
+        <v>127.47</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:37:27</t>
+          <t>10:37:50</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.49</v>
+        <v>2.88</v>
       </c>
       <c r="F84" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
       <c r="G84" t="n">
-        <v>165.7</v>
+        <v>169.7</v>
       </c>
       <c r="H84" t="n">
-        <v>73.90000000000001</v>
+        <v>53.5</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-100.65</v>
+        <v>-80.98</v>
       </c>
       <c r="K84" t="n">
-        <v>109.98</v>
+        <v>-135.08</v>
       </c>
       <c r="L84" t="n">
-        <v>149.08</v>
+        <v>157.49</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:38:21</t>
+          <t>10:38:58</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="F85" t="n">
-        <v>6.78</v>
+        <v>10.12</v>
       </c>
       <c r="G85" t="n">
-        <v>157.5</v>
+        <v>184.2</v>
       </c>
       <c r="H85" t="n">
-        <v>70</v>
+        <v>51.3</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>61.52</v>
+        <v>-146.45</v>
       </c>
       <c r="K85" t="n">
-        <v>143.21</v>
+        <v>-49.66</v>
       </c>
       <c r="L85" t="n">
-        <v>155.86</v>
+        <v>154.64</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:42:43</t>
+          <t>10:44:15</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.79</v>
+        <v>3.25</v>
       </c>
       <c r="F86" t="n">
-        <v>10.12</v>
+        <v>6.95</v>
       </c>
       <c r="G86" t="n">
-        <v>172.1</v>
+        <v>164.6</v>
       </c>
       <c r="H86" t="n">
-        <v>80.8</v>
+        <v>37.9</v>
       </c>
       <c r="I86" t="n">
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>108.46</v>
+        <v>180.41</v>
       </c>
       <c r="K86" t="n">
-        <v>-181.61</v>
+        <v>-140.8</v>
       </c>
       <c r="L86" t="n">
-        <v>211.53</v>
+        <v>228.85</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:45:22</t>
+          <t>10:46:04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.21</v>
+        <v>3.65</v>
       </c>
       <c r="F87" t="n">
         <v>10.12</v>
       </c>
       <c r="G87" t="n">
-        <v>162.4</v>
+        <v>161.4</v>
       </c>
       <c r="H87" t="n">
-        <v>79</v>
+        <v>59.7</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>-134.47</v>
+        <v>-187.67</v>
       </c>
       <c r="K87" t="n">
-        <v>19.92</v>
+        <v>149.28</v>
       </c>
       <c r="L87" t="n">
-        <v>135.94</v>
+        <v>239.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:46:01</t>
+          <t>10:48:18</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.51</v>
+        <v>3.82</v>
       </c>
       <c r="F88" t="n">
         <v>10.12</v>
       </c>
       <c r="G88" t="n">
-        <v>166</v>
+        <v>153.3</v>
       </c>
       <c r="H88" t="n">
-        <v>70.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>-213.14</v>
+        <v>251.09</v>
       </c>
       <c r="K88" t="n">
-        <v>-101.92</v>
+        <v>-15.84</v>
       </c>
       <c r="L88" t="n">
-        <v>236.26</v>
+        <v>251.59</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="F14" t="n">
-        <v>9.59</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>160</v>
+        <v>186.1</v>
       </c>
       <c r="H14" t="n">
-        <v>54.6</v>
+        <v>34.3</v>
       </c>
       <c r="I14" t="n">
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-52.22</v>
+        <v>56.06</v>
       </c>
       <c r="K14" t="n">
-        <v>-24.64</v>
+        <v>5.94</v>
       </c>
       <c r="L14" t="n">
-        <v>57.74</v>
+        <v>56.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:06:50</t>
+          <t>07:07:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.83</v>
+        <v>3.06</v>
       </c>
       <c r="F15" t="n">
-        <v>6.4</v>
+        <v>8.82</v>
       </c>
       <c r="G15" t="n">
-        <v>171.1</v>
+        <v>150.5</v>
       </c>
       <c r="H15" t="n">
-        <v>30.9</v>
+        <v>47.8</v>
       </c>
       <c r="I15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>-39.42</v>
+        <v>32.53</v>
       </c>
       <c r="K15" t="n">
-        <v>43.52</v>
+        <v>25.24</v>
       </c>
       <c r="L15" t="n">
-        <v>58.72</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:08:51</t>
+          <t>07:09:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.47</v>
+        <v>2.94</v>
       </c>
       <c r="F16" t="n">
-        <v>5.48</v>
+        <v>9.32</v>
       </c>
       <c r="G16" t="n">
-        <v>173.9</v>
+        <v>178</v>
       </c>
       <c r="H16" t="n">
-        <v>64</v>
+        <v>66.8</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>45.53</v>
+        <v>-35.42</v>
       </c>
       <c r="K16" t="n">
-        <v>-23.3</v>
+        <v>-40.79</v>
       </c>
       <c r="L16" t="n">
-        <v>51.14</v>
+        <v>54.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:14:41</t>
+          <t>07:15:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.19</v>
+        <v>2.68</v>
       </c>
       <c r="F17" t="n">
-        <v>5.48</v>
+        <v>6.81</v>
       </c>
       <c r="G17" t="n">
-        <v>171.6</v>
+        <v>158.5</v>
       </c>
       <c r="H17" t="n">
-        <v>55.5</v>
+        <v>53.5</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>-7.15</v>
+        <v>-30.73</v>
       </c>
       <c r="K17" t="n">
-        <v>-90.37</v>
+        <v>-57.38</v>
       </c>
       <c r="L17" t="n">
-        <v>90.65000000000001</v>
+        <v>65.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:16:43</t>
+          <t>07:16:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.02</v>
+        <v>2.71</v>
       </c>
       <c r="F18" t="n">
-        <v>5.86</v>
+        <v>5.48</v>
       </c>
       <c r="G18" t="n">
-        <v>174.8</v>
+        <v>152.9</v>
       </c>
       <c r="H18" t="n">
-        <v>30.1</v>
+        <v>13.8</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-66.87</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>46.73</v>
+        <v>-70.12</v>
       </c>
       <c r="L18" t="n">
-        <v>81.58</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:18:44</t>
+          <t>07:17:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="F19" t="n">
-        <v>9.039999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="G19" t="n">
-        <v>165.4</v>
+        <v>162.1</v>
       </c>
       <c r="H19" t="n">
-        <v>51.7</v>
+        <v>95</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.86</v>
+        <v>-24.23</v>
       </c>
       <c r="K19" t="n">
-        <v>-62.82</v>
+        <v>-58.45</v>
       </c>
       <c r="L19" t="n">
-        <v>63.09</v>
+        <v>63.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:23:14</t>
+          <t>07:23:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="F20" t="n">
-        <v>8.470000000000001</v>
+        <v>6.45</v>
       </c>
       <c r="G20" t="n">
-        <v>163.9</v>
+        <v>178.8</v>
       </c>
       <c r="H20" t="n">
-        <v>50.9</v>
+        <v>35.7</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-69.40000000000001</v>
+        <v>57.36</v>
       </c>
       <c r="K20" t="n">
-        <v>-91.20999999999999</v>
+        <v>-76.81</v>
       </c>
       <c r="L20" t="n">
-        <v>114.62</v>
+        <v>95.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:24:22</t>
+          <t>07:24:59</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.28</v>
+        <v>3.01</v>
       </c>
       <c r="F21" t="n">
-        <v>10.12</v>
+        <v>9.74</v>
       </c>
       <c r="G21" t="n">
-        <v>159.6</v>
+        <v>158.1</v>
       </c>
       <c r="H21" t="n">
-        <v>57.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>97.42</v>
+        <v>40.62</v>
       </c>
       <c r="K21" t="n">
-        <v>-80.68000000000001</v>
+        <v>-76.39</v>
       </c>
       <c r="L21" t="n">
-        <v>126.49</v>
+        <v>86.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:25:33</t>
+          <t>07:26:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="F22" t="n">
-        <v>6.27</v>
+        <v>8.09</v>
       </c>
       <c r="G22" t="n">
-        <v>171.9</v>
+        <v>157.2</v>
       </c>
       <c r="H22" t="n">
-        <v>78.90000000000001</v>
+        <v>39.5</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>65.51000000000001</v>
+        <v>112.18</v>
       </c>
       <c r="K22" t="n">
-        <v>-73.84</v>
+        <v>-45.64</v>
       </c>
       <c r="L22" t="n">
-        <v>98.70999999999999</v>
+        <v>121.11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:29:42</t>
+          <t>07:31:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="F23" t="n">
-        <v>8.640000000000001</v>
+        <v>6.95</v>
       </c>
       <c r="G23" t="n">
-        <v>154.8</v>
+        <v>146.3</v>
       </c>
       <c r="H23" t="n">
-        <v>55.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>32</v>
       </c>
       <c r="J23" t="n">
-        <v>70.33</v>
+        <v>-94.64</v>
       </c>
       <c r="K23" t="n">
-        <v>-105.24</v>
+        <v>22.13</v>
       </c>
       <c r="L23" t="n">
-        <v>126.58</v>
+        <v>97.19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:30:53</t>
+          <t>07:33:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.16</v>
+        <v>2.65</v>
       </c>
       <c r="F24" t="n">
-        <v>8.16</v>
+        <v>2.95</v>
       </c>
       <c r="G24" t="n">
-        <v>164</v>
+        <v>167.1</v>
       </c>
       <c r="H24" t="n">
-        <v>30</v>
+        <v>49.6</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J24" t="n">
-        <v>-14.6</v>
+        <v>-140.69</v>
       </c>
       <c r="K24" t="n">
-        <v>184.37</v>
+        <v>18.69</v>
       </c>
       <c r="L24" t="n">
-        <v>184.95</v>
+        <v>141.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:32:38</t>
+          <t>07:35:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.96</v>
+        <v>3.34</v>
       </c>
       <c r="F25" t="n">
-        <v>9.109999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="G25" t="n">
-        <v>166</v>
+        <v>178.7</v>
       </c>
       <c r="H25" t="n">
-        <v>82.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="I25" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>-75.70999999999999</v>
+        <v>-158.7</v>
       </c>
       <c r="K25" t="n">
-        <v>-188.39</v>
+        <v>-121.41</v>
       </c>
       <c r="L25" t="n">
-        <v>203.03</v>
+        <v>199.82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:36:03</t>
+          <t>07:40:58</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.13</v>
+        <v>2.81</v>
       </c>
       <c r="F26" t="n">
-        <v>7.94</v>
+        <v>10.12</v>
       </c>
       <c r="G26" t="n">
-        <v>169.5</v>
+        <v>154.4</v>
       </c>
       <c r="H26" t="n">
-        <v>39.2</v>
+        <v>49.5</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>219.17</v>
+        <v>-121</v>
       </c>
       <c r="K26" t="n">
-        <v>-23.8</v>
+        <v>-158.31</v>
       </c>
       <c r="L26" t="n">
-        <v>220.46</v>
+        <v>199.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:37:56</t>
+          <t>07:41:53</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="F27" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>177.1</v>
+        <v>178.3</v>
       </c>
       <c r="H27" t="n">
-        <v>71.3</v>
+        <v>35</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-255.93</v>
+        <v>184.72</v>
       </c>
       <c r="K27" t="n">
-        <v>11.96</v>
+        <v>-118.44</v>
       </c>
       <c r="L27" t="n">
-        <v>256.21</v>
+        <v>219.43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:39:23</t>
+          <t>07:44:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="F28" t="n">
-        <v>8.720000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="G28" t="n">
-        <v>162.6</v>
+        <v>153.3</v>
       </c>
       <c r="H28" t="n">
-        <v>35.6</v>
+        <v>79.7</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>232.42</v>
+        <v>-166.35</v>
       </c>
       <c r="K28" t="n">
-        <v>2.76</v>
+        <v>121.06</v>
       </c>
       <c r="L28" t="n">
-        <v>232.43</v>
+        <v>205.74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:49:01</t>
+          <t>07:54:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="F29" t="n">
-        <v>7.94</v>
+        <v>8.85</v>
       </c>
       <c r="G29" t="n">
-        <v>165.8</v>
+        <v>176.1</v>
       </c>
       <c r="H29" t="n">
-        <v>70.90000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="I29" t="n">
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-39.55</v>
+        <v>-10</v>
       </c>
       <c r="K29" t="n">
-        <v>-12.97</v>
+        <v>65.06</v>
       </c>
       <c r="L29" t="n">
-        <v>41.62</v>
+        <v>65.81999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:50:31</t>
+          <t>07:55:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.21</v>
+        <v>3.31</v>
       </c>
       <c r="F30" t="n">
-        <v>10.12</v>
+        <v>7.88</v>
       </c>
       <c r="G30" t="n">
-        <v>172.7</v>
+        <v>145.8</v>
       </c>
       <c r="H30" t="n">
-        <v>38.7</v>
+        <v>33.7</v>
       </c>
       <c r="I30" t="n">
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-25.81</v>
+        <v>41.95</v>
       </c>
       <c r="K30" t="n">
-        <v>-47.27</v>
+        <v>41.29</v>
       </c>
       <c r="L30" t="n">
-        <v>53.86</v>
+        <v>58.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:52:11</t>
+          <t>07:58:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.45</v>
+        <v>2.91</v>
       </c>
       <c r="F31" t="n">
-        <v>9.460000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="G31" t="n">
-        <v>161.2</v>
+        <v>160.5</v>
       </c>
       <c r="H31" t="n">
-        <v>45.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>40.95</v>
+        <v>-19.66</v>
       </c>
       <c r="K31" t="n">
-        <v>-27.51</v>
+        <v>-36.48</v>
       </c>
       <c r="L31" t="n">
-        <v>49.33</v>
+        <v>41.44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:57:09</t>
+          <t>08:04:03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.82</v>
+        <v>3.39</v>
       </c>
       <c r="F32" t="n">
-        <v>9.890000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="G32" t="n">
-        <v>165.1</v>
+        <v>167.6</v>
       </c>
       <c r="H32" t="n">
-        <v>74.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="I32" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>63.05</v>
+        <v>40.14</v>
       </c>
       <c r="K32" t="n">
-        <v>22.52</v>
+        <v>98.58</v>
       </c>
       <c r="L32" t="n">
-        <v>66.95</v>
+        <v>106.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:58:40</t>
+          <t>08:06:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.31</v>
+        <v>3.09</v>
       </c>
       <c r="F33" t="n">
-        <v>9.619999999999999</v>
+        <v>6.62</v>
       </c>
       <c r="G33" t="n">
-        <v>149.4</v>
+        <v>161</v>
       </c>
       <c r="H33" t="n">
-        <v>40.3</v>
+        <v>65.2</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>70.84</v>
+        <v>-51.01</v>
       </c>
       <c r="K33" t="n">
-        <v>-57.31</v>
+        <v>-73.97</v>
       </c>
       <c r="L33" t="n">
-        <v>91.12</v>
+        <v>89.84999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:00:54</t>
+          <t>08:08:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.01</v>
+        <v>3.44</v>
       </c>
       <c r="F34" t="n">
-        <v>5.38</v>
+        <v>10.12</v>
       </c>
       <c r="G34" t="n">
-        <v>165.7</v>
+        <v>162</v>
       </c>
       <c r="H34" t="n">
-        <v>36.6</v>
+        <v>57.2</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J34" t="n">
-        <v>-85.34999999999999</v>
+        <v>89.72</v>
       </c>
       <c r="K34" t="n">
-        <v>15.12</v>
+        <v>35.85</v>
       </c>
       <c r="L34" t="n">
-        <v>86.68000000000001</v>
+        <v>96.62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:05:29</t>
+          <t>08:13:41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="F35" t="n">
-        <v>6.38</v>
+        <v>9.34</v>
       </c>
       <c r="G35" t="n">
-        <v>166.6</v>
+        <v>171.1</v>
       </c>
       <c r="H35" t="n">
-        <v>72.3</v>
+        <v>85.5</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>36.49</v>
+        <v>96.03</v>
       </c>
       <c r="K35" t="n">
-        <v>-96.15000000000001</v>
+        <v>-141.01</v>
       </c>
       <c r="L35" t="n">
-        <v>102.84</v>
+        <v>170.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:07:35</t>
+          <t>08:16:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="F36" t="n">
-        <v>10.12</v>
+        <v>6.57</v>
       </c>
       <c r="G36" t="n">
-        <v>172.3</v>
+        <v>168.5</v>
       </c>
       <c r="H36" t="n">
-        <v>60.6</v>
+        <v>67.8</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-129.04</v>
+        <v>78.11</v>
       </c>
       <c r="K36" t="n">
-        <v>-45.68</v>
+        <v>-114.6</v>
       </c>
       <c r="L36" t="n">
-        <v>136.88</v>
+        <v>138.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:09:00</t>
+          <t>08:17:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.89</v>
+        <v>3.16</v>
       </c>
       <c r="F37" t="n">
-        <v>9.460000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>154.2</v>
+        <v>165.4</v>
       </c>
       <c r="H37" t="n">
-        <v>49.1</v>
+        <v>63.5</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J37" t="n">
-        <v>-111.61</v>
+        <v>-99.31</v>
       </c>
       <c r="K37" t="n">
-        <v>33.86</v>
+        <v>-28.86</v>
       </c>
       <c r="L37" t="n">
-        <v>116.63</v>
+        <v>103.42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:15:02</t>
+          <t>08:22:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.13</v>
+        <v>3.39</v>
       </c>
       <c r="F38" t="n">
-        <v>9.779999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="G38" t="n">
-        <v>160.9</v>
+        <v>164.1</v>
       </c>
       <c r="H38" t="n">
-        <v>53.5</v>
+        <v>47.4</v>
       </c>
       <c r="I38" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>-218.64</v>
+        <v>106.2</v>
       </c>
       <c r="K38" t="n">
-        <v>-66.31999999999999</v>
+        <v>-227.06</v>
       </c>
       <c r="L38" t="n">
-        <v>228.47</v>
+        <v>250.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:16:26</t>
+          <t>08:23:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="F39" t="n">
-        <v>8.289999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="G39" t="n">
-        <v>162.8</v>
+        <v>154.9</v>
       </c>
       <c r="H39" t="n">
-        <v>71</v>
+        <v>15.2</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J39" t="n">
-        <v>-61.93</v>
+        <v>58.49</v>
       </c>
       <c r="K39" t="n">
-        <v>-126.93</v>
+        <v>-131.69</v>
       </c>
       <c r="L39" t="n">
-        <v>141.24</v>
+        <v>144.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:19:12</t>
+          <t>08:25:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="F40" t="n">
-        <v>8.98</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>159.5</v>
+        <v>164</v>
       </c>
       <c r="H40" t="n">
-        <v>51.1</v>
+        <v>30</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J40" t="n">
-        <v>51.77</v>
+        <v>-26.6</v>
       </c>
       <c r="K40" t="n">
-        <v>-264.01</v>
+        <v>220.93</v>
       </c>
       <c r="L40" t="n">
-        <v>269.04</v>
+        <v>222.52</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:23:10</t>
+          <t>08:29:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="F41" t="n">
-        <v>10.12</v>
+        <v>10.09</v>
       </c>
       <c r="G41" t="n">
-        <v>160.7</v>
+        <v>166</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J41" t="n">
-        <v>19.53</v>
+        <v>-148.15</v>
       </c>
       <c r="K41" t="n">
-        <v>-196.82</v>
+        <v>-258.09</v>
       </c>
       <c r="L41" t="n">
-        <v>197.79</v>
+        <v>297.58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:24:26</t>
+          <t>08:30:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="F42" t="n">
-        <v>10.12</v>
+        <v>8.9</v>
       </c>
       <c r="G42" t="n">
-        <v>157.2</v>
+        <v>169.5</v>
       </c>
       <c r="H42" t="n">
-        <v>50.2</v>
+        <v>39.2</v>
       </c>
       <c r="I42" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>206.24</v>
+        <v>250.02</v>
       </c>
       <c r="K42" t="n">
-        <v>94.27</v>
+        <v>28.89</v>
       </c>
       <c r="L42" t="n">
-        <v>226.76</v>
+        <v>251.69</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:26:06</t>
+          <t>08:33:06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="F43" t="n">
-        <v>9.039999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="G43" t="n">
-        <v>172.3</v>
+        <v>177.1</v>
       </c>
       <c r="H43" t="n">
-        <v>68.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="I43" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>179.28</v>
+        <v>-279.5</v>
       </c>
       <c r="K43" t="n">
-        <v>-16.81</v>
+        <v>74.44</v>
       </c>
       <c r="L43" t="n">
-        <v>180.07</v>
+        <v>289.24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:37:10</t>
+          <t>08:43:38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.47</v>
+        <v>3.16</v>
       </c>
       <c r="F44" t="n">
-        <v>9.01</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>167.9</v>
+        <v>162.6</v>
       </c>
       <c r="H44" t="n">
-        <v>67.90000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.53</v>
+        <v>57.05</v>
       </c>
       <c r="K44" t="n">
-        <v>59.23</v>
+        <v>12.93</v>
       </c>
       <c r="L44" t="n">
-        <v>59.29</v>
+        <v>58.49</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:39:28</t>
+          <t>08:45:42</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="F45" t="n">
-        <v>8.640000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>156.2</v>
+        <v>165.8</v>
       </c>
       <c r="H45" t="n">
-        <v>91.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-58.47</v>
+        <v>-44.81</v>
       </c>
       <c r="K45" t="n">
-        <v>13.67</v>
+        <v>-4.57</v>
       </c>
       <c r="L45" t="n">
-        <v>60.05</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:41:48</t>
+          <t>08:47:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="F46" t="n">
         <v>10.12</v>
       </c>
       <c r="G46" t="n">
-        <v>165.8</v>
+        <v>172.7</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4</v>
+        <v>38.7</v>
       </c>
       <c r="I46" t="n">
         <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>41.53</v>
+        <v>-34.46</v>
       </c>
       <c r="K46" t="n">
-        <v>-16.99</v>
+        <v>-45.41</v>
       </c>
       <c r="L46" t="n">
-        <v>44.87</v>
+        <v>57.01</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:47:06</t>
+          <t>08:50:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.19</v>
+        <v>3.66</v>
       </c>
       <c r="F47" t="n">
         <v>10.12</v>
       </c>
       <c r="G47" t="n">
-        <v>163.7</v>
+        <v>161.2</v>
       </c>
       <c r="H47" t="n">
-        <v>69.40000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>35.5</v>
+        <v>53.38</v>
       </c>
       <c r="K47" t="n">
-        <v>-76.87</v>
+        <v>-20.08</v>
       </c>
       <c r="L47" t="n">
-        <v>84.67</v>
+        <v>57.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:48:58</t>
+          <t>08:52:24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="F48" t="n">
-        <v>8.02</v>
+        <v>10.12</v>
       </c>
       <c r="G48" t="n">
-        <v>167.7</v>
+        <v>165.1</v>
       </c>
       <c r="H48" t="n">
-        <v>52</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I48" t="n">
         <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>38.94</v>
+        <v>59.93</v>
       </c>
       <c r="K48" t="n">
-        <v>-108.68</v>
+        <v>36.71</v>
       </c>
       <c r="L48" t="n">
-        <v>115.45</v>
+        <v>70.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:50:19</t>
+          <t>08:53:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.43</v>
+        <v>3.51</v>
       </c>
       <c r="F49" t="n">
         <v>10.12</v>
       </c>
       <c r="G49" t="n">
-        <v>167.3</v>
+        <v>149.4</v>
       </c>
       <c r="H49" t="n">
-        <v>62.7</v>
+        <v>40.3</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-86.16</v>
+        <v>78.37</v>
       </c>
       <c r="K49" t="n">
-        <v>-43.38</v>
+        <v>-52.19</v>
       </c>
       <c r="L49" t="n">
-        <v>96.47</v>
+        <v>94.16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:53:27</t>
+          <t>08:57:18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.76</v>
+        <v>3.21</v>
       </c>
       <c r="F50" t="n">
-        <v>9.369999999999999</v>
+        <v>6.29</v>
       </c>
       <c r="G50" t="n">
-        <v>165.9</v>
+        <v>165.7</v>
       </c>
       <c r="H50" t="n">
-        <v>61.5</v>
+        <v>36.6</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>109.16</v>
+        <v>-116.12</v>
       </c>
       <c r="K50" t="n">
-        <v>-89.41</v>
+        <v>44.63</v>
       </c>
       <c r="L50" t="n">
-        <v>141.1</v>
+        <v>124.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:54:32</t>
+          <t>08:59:07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.08</v>
+        <v>3.79</v>
       </c>
       <c r="F51" t="n">
-        <v>9.630000000000001</v>
+        <v>7.31</v>
       </c>
       <c r="G51" t="n">
-        <v>167.3</v>
+        <v>166.6</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>72.3</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>12.12</v>
+        <v>42.01</v>
       </c>
       <c r="K51" t="n">
-        <v>-100.5</v>
+        <v>-99.5</v>
       </c>
       <c r="L51" t="n">
-        <v>101.23</v>
+        <v>108.01</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:55:59</t>
+          <t>09:00:57</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.18</v>
+        <v>3.79</v>
       </c>
       <c r="F52" t="n">
-        <v>8.16</v>
+        <v>10.12</v>
       </c>
       <c r="G52" t="n">
-        <v>151.8</v>
+        <v>172.3</v>
       </c>
       <c r="H52" t="n">
-        <v>69.5</v>
+        <v>60.6</v>
       </c>
       <c r="I52" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>121.36</v>
+        <v>-142.94</v>
       </c>
       <c r="K52" t="n">
-        <v>32.45</v>
+        <v>-12.82</v>
       </c>
       <c r="L52" t="n">
-        <v>125.62</v>
+        <v>143.51</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:00:02</t>
+          <t>09:06:12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.61</v>
+        <v>3.09</v>
       </c>
       <c r="F53" t="n">
         <v>10.12</v>
       </c>
       <c r="G53" t="n">
-        <v>185.1</v>
+        <v>154.2</v>
       </c>
       <c r="H53" t="n">
-        <v>93.2</v>
+        <v>49.1</v>
       </c>
       <c r="I53" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J53" t="n">
-        <v>-101.83</v>
+        <v>-174.92</v>
       </c>
       <c r="K53" t="n">
-        <v>-291.46</v>
+        <v>82.53</v>
       </c>
       <c r="L53" t="n">
-        <v>308.73</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:01:08</t>
+          <t>09:07:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.42</v>
+        <v>4.31</v>
       </c>
       <c r="F54" t="n">
-        <v>7.05</v>
+        <v>10.12</v>
       </c>
       <c r="G54" t="n">
-        <v>167.6</v>
+        <v>160.9</v>
       </c>
       <c r="H54" t="n">
-        <v>65.2</v>
+        <v>53.5</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J54" t="n">
-        <v>134.7</v>
+        <v>-253.26</v>
       </c>
       <c r="K54" t="n">
-        <v>-159.98</v>
+        <v>-5.94</v>
       </c>
       <c r="L54" t="n">
-        <v>209.13</v>
+        <v>253.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:02:39</t>
+          <t>09:08:48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.06</v>
+        <v>3.36</v>
       </c>
       <c r="F55" t="n">
-        <v>9.73</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>169.2</v>
+        <v>162.8</v>
       </c>
       <c r="H55" t="n">
-        <v>60.2</v>
+        <v>71</v>
       </c>
       <c r="I55" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>171.9</v>
+        <v>-95.28</v>
       </c>
       <c r="K55" t="n">
-        <v>-34.37</v>
+        <v>-131.54</v>
       </c>
       <c r="L55" t="n">
-        <v>175.31</v>
+        <v>162.42</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:07:06</t>
+          <t>09:13:47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.77</v>
+        <v>3.52</v>
       </c>
       <c r="F56" t="n">
-        <v>10.04</v>
+        <v>9.85</v>
       </c>
       <c r="G56" t="n">
-        <v>173.8</v>
+        <v>159.5</v>
       </c>
       <c r="H56" t="n">
-        <v>61.9</v>
+        <v>51.1</v>
       </c>
       <c r="I56" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>60.97</v>
+        <v>52.49</v>
       </c>
       <c r="K56" t="n">
-        <v>-308.47</v>
+        <v>-317.38</v>
       </c>
       <c r="L56" t="n">
-        <v>314.44</v>
+        <v>321.69</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:09:18</t>
+          <t>09:16:15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="F57" t="n">
         <v>10.12</v>
       </c>
       <c r="G57" t="n">
-        <v>164</v>
+        <v>160.7</v>
       </c>
       <c r="H57" t="n">
-        <v>55.2</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J57" t="n">
-        <v>272.41</v>
+        <v>8.25</v>
       </c>
       <c r="K57" t="n">
-        <v>6.94</v>
+        <v>-218.03</v>
       </c>
       <c r="L57" t="n">
-        <v>272.5</v>
+        <v>218.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:11:40</t>
+          <t>09:18:47</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.18</v>
+        <v>3.59</v>
       </c>
       <c r="F58" t="n">
-        <v>7.85</v>
+        <v>10.12</v>
       </c>
       <c r="G58" t="n">
-        <v>162</v>
+        <v>157.2</v>
       </c>
       <c r="H58" t="n">
-        <v>64.09999999999999</v>
+        <v>50.2</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>-193.62</v>
+        <v>196.36</v>
       </c>
       <c r="K58" t="n">
-        <v>104.55</v>
+        <v>155.23</v>
       </c>
       <c r="L58" t="n">
-        <v>220.05</v>
+        <v>250.31</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:20:41</t>
+          <t>09:28:56</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.86</v>
+        <v>3.38</v>
       </c>
       <c r="F59" t="n">
-        <v>9.43</v>
+        <v>10.02</v>
       </c>
       <c r="G59" t="n">
-        <v>163.9</v>
+        <v>172.3</v>
       </c>
       <c r="H59" t="n">
-        <v>17.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J59" t="n">
-        <v>-31.35</v>
+        <v>52.52</v>
       </c>
       <c r="K59" t="n">
-        <v>11.04</v>
+        <v>7.08</v>
       </c>
       <c r="L59" t="n">
-        <v>33.24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:23:00</t>
+          <t>09:30:43</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.29</v>
+        <v>3.64</v>
       </c>
       <c r="F60" t="n">
-        <v>10.12</v>
+        <v>9.85</v>
       </c>
       <c r="G60" t="n">
-        <v>158</v>
+        <v>167.9</v>
       </c>
       <c r="H60" t="n">
-        <v>45.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>31.32</v>
+        <v>-61.04</v>
       </c>
       <c r="K60" t="n">
-        <v>-34.37</v>
+        <v>-0.05</v>
       </c>
       <c r="L60" t="n">
-        <v>46.5</v>
+        <v>61.04</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:25:21</t>
+          <t>09:32:02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.78</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>10.12</v>
+        <v>8.84</v>
       </c>
       <c r="G61" t="n">
-        <v>169.5</v>
+        <v>162.9</v>
       </c>
       <c r="H61" t="n">
-        <v>59.9</v>
+        <v>50.7</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>28.52</v>
+        <v>-10.99</v>
       </c>
       <c r="K61" t="n">
-        <v>45.54</v>
+        <v>-41.91</v>
       </c>
       <c r="L61" t="n">
-        <v>53.73</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:29:49</t>
+          <t>09:37:07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.36</v>
+        <v>3.57</v>
       </c>
       <c r="F62" t="n">
-        <v>9.44</v>
+        <v>10.12</v>
       </c>
       <c r="G62" t="n">
-        <v>159.7</v>
+        <v>178.4</v>
       </c>
       <c r="H62" t="n">
-        <v>76.5</v>
+        <v>48.2</v>
       </c>
       <c r="I62" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>72.95999999999999</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-8.539999999999999</v>
+        <v>18.89</v>
       </c>
       <c r="L62" t="n">
-        <v>73.45999999999999</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:31:23</t>
+          <t>09:38:52</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.53</v>
+        <v>3.02</v>
       </c>
       <c r="F63" t="n">
-        <v>10.12</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H63" t="n">
-        <v>52.5</v>
+        <v>80.2</v>
       </c>
       <c r="I63" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J63" t="n">
-        <v>35.26</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-12.87</v>
+        <v>-58.57</v>
       </c>
       <c r="L63" t="n">
-        <v>37.54</v>
+        <v>87.66</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:33:01</t>
+          <t>09:40:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.61</v>
+        <v>3.07</v>
       </c>
       <c r="F64" t="n">
-        <v>7.72</v>
+        <v>10.12</v>
       </c>
       <c r="G64" t="n">
-        <v>157.1</v>
+        <v>155.8</v>
       </c>
       <c r="H64" t="n">
-        <v>48.5</v>
+        <v>74.7</v>
       </c>
       <c r="I64" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>55.33</v>
+        <v>34.05</v>
       </c>
       <c r="K64" t="n">
-        <v>-93.09999999999999</v>
+        <v>-3.69</v>
       </c>
       <c r="L64" t="n">
-        <v>108.3</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:38:28</t>
+          <t>09:45:26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.11</v>
+        <v>3.82</v>
       </c>
       <c r="F65" t="n">
-        <v>9.5</v>
+        <v>10.12</v>
       </c>
       <c r="G65" t="n">
-        <v>169</v>
+        <v>169.7</v>
       </c>
       <c r="H65" t="n">
-        <v>54.8</v>
+        <v>68.5</v>
       </c>
       <c r="I65" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>85.36</v>
+        <v>0.05</v>
       </c>
       <c r="K65" t="n">
-        <v>68.23999999999999</v>
+        <v>-214.63</v>
       </c>
       <c r="L65" t="n">
-        <v>109.28</v>
+        <v>214.63</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:40:20</t>
+          <t>09:46:39</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="F66" t="n">
-        <v>9.06</v>
+        <v>10.12</v>
       </c>
       <c r="G66" t="n">
-        <v>170</v>
+        <v>166.9</v>
       </c>
       <c r="H66" t="n">
-        <v>32.3</v>
+        <v>16.8</v>
       </c>
       <c r="I66" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>32.77</v>
+        <v>48.3</v>
       </c>
       <c r="K66" t="n">
-        <v>-51.54</v>
+        <v>108.63</v>
       </c>
       <c r="L66" t="n">
-        <v>61.07</v>
+        <v>118.88</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:41:47</t>
+          <t>09:47:48</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="F67" t="n">
-        <v>10.12</v>
+        <v>9.66</v>
       </c>
       <c r="G67" t="n">
-        <v>174.6</v>
+        <v>171.2</v>
       </c>
       <c r="H67" t="n">
-        <v>54.4</v>
+        <v>51.8</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>107.11</v>
+        <v>-132.09</v>
       </c>
       <c r="K67" t="n">
-        <v>54.27</v>
+        <v>-23.3</v>
       </c>
       <c r="L67" t="n">
-        <v>120.08</v>
+        <v>134.13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:47:31</t>
+          <t>09:51:49</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.34</v>
+        <v>3.09</v>
       </c>
       <c r="F68" t="n">
-        <v>10.12</v>
+        <v>7.5</v>
       </c>
       <c r="G68" t="n">
-        <v>170.6</v>
+        <v>169.6</v>
       </c>
       <c r="H68" t="n">
-        <v>55.9</v>
+        <v>39.6</v>
       </c>
       <c r="I68" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>133.84</v>
+        <v>210.21</v>
       </c>
       <c r="K68" t="n">
-        <v>-292.42</v>
+        <v>-48.9</v>
       </c>
       <c r="L68" t="n">
-        <v>321.59</v>
+        <v>215.83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:49:23</t>
+          <t>09:53:56</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="F69" t="n">
-        <v>8.18</v>
+        <v>10.12</v>
       </c>
       <c r="G69" t="n">
-        <v>163.3</v>
+        <v>152.2</v>
       </c>
       <c r="H69" t="n">
-        <v>56.7</v>
+        <v>97.5</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>53.16</v>
+        <v>-108.18</v>
       </c>
       <c r="K69" t="n">
-        <v>345.13</v>
+        <v>-182.66</v>
       </c>
       <c r="L69" t="n">
-        <v>349.2</v>
+        <v>212.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:50:51</t>
+          <t>09:55:47</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.43</v>
+        <v>3.71</v>
       </c>
       <c r="F70" t="n">
-        <v>10.12</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>167.7</v>
+        <v>167.3</v>
       </c>
       <c r="H70" t="n">
-        <v>70.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J70" t="n">
-        <v>80.42</v>
+        <v>199.6</v>
       </c>
       <c r="K70" t="n">
-        <v>211.54</v>
+        <v>-138.65</v>
       </c>
       <c r="L70" t="n">
-        <v>226.31</v>
+        <v>243.03</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:56:45</t>
+          <t>09:59:24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.27</v>
+        <v>3.91</v>
       </c>
       <c r="F71" t="n">
         <v>10.12</v>
       </c>
       <c r="G71" t="n">
-        <v>156.7</v>
+        <v>170.2</v>
       </c>
       <c r="H71" t="n">
-        <v>85.59999999999999</v>
+        <v>47.8</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-70.25</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>-134.64</v>
+        <v>309.35</v>
       </c>
       <c r="L71" t="n">
-        <v>151.87</v>
+        <v>324.37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:58:12</t>
+          <t>10:01:13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.78</v>
+        <v>3.29</v>
       </c>
       <c r="F72" t="n">
-        <v>10.12</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>179</v>
+        <v>173.5</v>
       </c>
       <c r="H72" t="n">
-        <v>85.8</v>
+        <v>82.2</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J72" t="n">
-        <v>-128.98</v>
+        <v>-80.20999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>227.38</v>
+        <v>-123.3</v>
       </c>
       <c r="L72" t="n">
-        <v>261.41</v>
+        <v>147.09</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:59:18</t>
+          <t>10:02:45</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.01</v>
+        <v>3.55</v>
       </c>
       <c r="F73" t="n">
         <v>10.12</v>
       </c>
       <c r="G73" t="n">
-        <v>162.9</v>
+        <v>169.6</v>
       </c>
       <c r="H73" t="n">
-        <v>39.4</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J73" t="n">
-        <v>-300.18</v>
+        <v>254.88</v>
       </c>
       <c r="K73" t="n">
-        <v>41.29</v>
+        <v>-110.61</v>
       </c>
       <c r="L73" t="n">
-        <v>303</v>
+        <v>277.85</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:12:52</t>
+          <t>10:14:16</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.39</v>
+        <v>3.48</v>
       </c>
       <c r="F74" t="n">
-        <v>10.12</v>
+        <v>8.42</v>
       </c>
       <c r="G74" t="n">
-        <v>167.6</v>
+        <v>170.8</v>
       </c>
       <c r="H74" t="n">
-        <v>17.6</v>
+        <v>56.5</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>45.75</v>
+        <v>9.41</v>
       </c>
       <c r="K74" t="n">
-        <v>-2.16</v>
+        <v>61</v>
       </c>
       <c r="L74" t="n">
-        <v>45.8</v>
+        <v>61.72</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:14:00</t>
+          <t>10:15:50</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.16</v>
+        <v>3.61</v>
       </c>
       <c r="F75" t="n">
         <v>10.12</v>
       </c>
       <c r="G75" t="n">
-        <v>148.8</v>
+        <v>161.1</v>
       </c>
       <c r="H75" t="n">
-        <v>56.1</v>
+        <v>50.7</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>13.16</v>
+        <v>-6.85</v>
       </c>
       <c r="K75" t="n">
-        <v>-61.4</v>
+        <v>45.03</v>
       </c>
       <c r="L75" t="n">
-        <v>62.79</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:16:19</t>
+          <t>10:18:33</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.14</v>
+        <v>2.96</v>
       </c>
       <c r="F76" t="n">
-        <v>7.23</v>
+        <v>7.81</v>
       </c>
       <c r="G76" t="n">
-        <v>157.9</v>
+        <v>148</v>
       </c>
       <c r="H76" t="n">
-        <v>62.7</v>
+        <v>54.9</v>
       </c>
       <c r="I76" t="n">
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-22.61</v>
+        <v>18.3</v>
       </c>
       <c r="K76" t="n">
-        <v>47.22</v>
+        <v>-43.39</v>
       </c>
       <c r="L76" t="n">
-        <v>52.36</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:20:37</t>
+          <t>10:22:24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3274,31 +3274,31 @@
         <v>3.37</v>
       </c>
       <c r="F77" t="n">
-        <v>10.12</v>
+        <v>7.15</v>
       </c>
       <c r="G77" t="n">
-        <v>161.4</v>
+        <v>173</v>
       </c>
       <c r="H77" t="n">
-        <v>67.8</v>
+        <v>28.1</v>
       </c>
       <c r="I77" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J77" t="n">
-        <v>36.04</v>
+        <v>-23.24</v>
       </c>
       <c r="K77" t="n">
-        <v>33.58</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>49.26</v>
+        <v>99.52</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:23:07</t>
+          <t>10:24:11</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.15</v>
+        <v>3.57</v>
       </c>
       <c r="F78" t="n">
-        <v>8.960000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="G78" t="n">
-        <v>154.9</v>
+        <v>168.6</v>
       </c>
       <c r="H78" t="n">
-        <v>75.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="I78" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J78" t="n">
-        <v>53.37</v>
+        <v>-50.55</v>
       </c>
       <c r="K78" t="n">
-        <v>-30.65</v>
+        <v>-77.87</v>
       </c>
       <c r="L78" t="n">
-        <v>61.54</v>
+        <v>92.84</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:24:07</t>
+          <t>10:25:31</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.91</v>
+        <v>3.04</v>
       </c>
       <c r="F79" t="n">
-        <v>10.12</v>
+        <v>7.36</v>
       </c>
       <c r="G79" t="n">
-        <v>160.1</v>
+        <v>173</v>
       </c>
       <c r="H79" t="n">
-        <v>34.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I79" t="n">
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>18.1</v>
+        <v>-51.29</v>
       </c>
       <c r="K79" t="n">
-        <v>-97.52</v>
+        <v>-63.17</v>
       </c>
       <c r="L79" t="n">
-        <v>99.18000000000001</v>
+        <v>81.37</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:27:34</t>
+          <t>10:30:16</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.06</v>
+        <v>3.48</v>
       </c>
       <c r="F80" t="n">
-        <v>6.59</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>160.5</v>
+        <v>167.9</v>
       </c>
       <c r="H80" t="n">
-        <v>18.9</v>
+        <v>42.2</v>
       </c>
       <c r="I80" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J80" t="n">
-        <v>-41.81</v>
+        <v>-65.19</v>
       </c>
       <c r="K80" t="n">
-        <v>-125.74</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>132.51</v>
+        <v>93.31</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:28:53</t>
+          <t>10:31:10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="F81" t="n">
         <v>10.12</v>
       </c>
       <c r="G81" t="n">
-        <v>166.8</v>
+        <v>169.5</v>
       </c>
       <c r="H81" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>55.49</v>
+        <v>-127.81</v>
       </c>
       <c r="K81" t="n">
-        <v>-144.63</v>
+        <v>6.4</v>
       </c>
       <c r="L81" t="n">
-        <v>154.9</v>
+        <v>127.97</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:31:16</t>
+          <t>10:33:24</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="F82" t="n">
-        <v>9.699999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="G82" t="n">
-        <v>175.6</v>
+        <v>170</v>
       </c>
       <c r="H82" t="n">
-        <v>30.6</v>
+        <v>58.4</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>94.12</v>
+        <v>-62.37</v>
       </c>
       <c r="K82" t="n">
-        <v>-17</v>
+        <v>-98.29000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>95.64</v>
+        <v>116.41</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:36:20</t>
+          <t>10:39:18</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.14</v>
+        <v>4.29</v>
       </c>
       <c r="F83" t="n">
         <v>10.12</v>
       </c>
       <c r="G83" t="n">
-        <v>168</v>
+        <v>167.5</v>
       </c>
       <c r="H83" t="n">
-        <v>58.5</v>
+        <v>38</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>96.8</v>
+        <v>-61.92</v>
       </c>
       <c r="K83" t="n">
-        <v>-82.93000000000001</v>
+        <v>-290.45</v>
       </c>
       <c r="L83" t="n">
-        <v>127.47</v>
+        <v>296.98</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:37:50</t>
+          <t>10:40:36</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="F84" t="n">
-        <v>10.11</v>
+        <v>10.12</v>
       </c>
       <c r="G84" t="n">
-        <v>169.7</v>
+        <v>167</v>
       </c>
       <c r="H84" t="n">
-        <v>53.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-80.98</v>
+        <v>235.86</v>
       </c>
       <c r="K84" t="n">
-        <v>-135.08</v>
+        <v>-36.84</v>
       </c>
       <c r="L84" t="n">
-        <v>157.49</v>
+        <v>238.72</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:38:58</t>
+          <t>10:43:11</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.21</v>
+        <v>4.05</v>
       </c>
       <c r="F85" t="n">
         <v>10.12</v>
       </c>
       <c r="G85" t="n">
-        <v>184.2</v>
+        <v>154.8</v>
       </c>
       <c r="H85" t="n">
-        <v>51.3</v>
+        <v>23.9</v>
       </c>
       <c r="I85" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>-146.45</v>
+        <v>171.84</v>
       </c>
       <c r="K85" t="n">
-        <v>-49.66</v>
+        <v>-169.23</v>
       </c>
       <c r="L85" t="n">
-        <v>154.64</v>
+        <v>241.18</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:44:15</t>
+          <t>10:48:40</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="F86" t="n">
-        <v>6.95</v>
+        <v>10.12</v>
       </c>
       <c r="G86" t="n">
-        <v>164.6</v>
+        <v>169.1</v>
       </c>
       <c r="H86" t="n">
-        <v>37.9</v>
+        <v>42.2</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>180.41</v>
+        <v>-256.22</v>
       </c>
       <c r="K86" t="n">
-        <v>-140.8</v>
+        <v>-46.31</v>
       </c>
       <c r="L86" t="n">
-        <v>228.85</v>
+        <v>260.37</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:46:04</t>
+          <t>10:49:42</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="F87" t="n">
-        <v>10.12</v>
+        <v>9.08</v>
       </c>
       <c r="G87" t="n">
-        <v>161.4</v>
+        <v>186.7</v>
       </c>
       <c r="H87" t="n">
-        <v>59.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J87" t="n">
-        <v>-187.67</v>
+        <v>107.48</v>
       </c>
       <c r="K87" t="n">
-        <v>149.28</v>
+        <v>-184.01</v>
       </c>
       <c r="L87" t="n">
-        <v>239.8</v>
+        <v>213.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:48:18</t>
+          <t>10:51:48</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.82</v>
+        <v>3.23</v>
       </c>
       <c r="F88" t="n">
         <v>10.12</v>
       </c>
       <c r="G88" t="n">
-        <v>153.3</v>
+        <v>162.7</v>
       </c>
       <c r="H88" t="n">
-        <v>75.5</v>
+        <v>50.7</v>
       </c>
       <c r="I88" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J88" t="n">
-        <v>251.09</v>
+        <v>-185.76</v>
       </c>
       <c r="K88" t="n">
-        <v>-15.84</v>
+        <v>23.51</v>
       </c>
       <c r="L88" t="n">
-        <v>251.59</v>
+        <v>187.24</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>66.15000000000001</v>
+        <v>72.86</v>
       </c>
       <c r="K14" t="n">
-        <v>-19.82</v>
+        <v>-21.84</v>
       </c>
       <c r="L14" t="n">
-        <v>69.06</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-55.63</v>
+        <v>-61.54</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.75</v>
+        <v>-9.68</v>
       </c>
       <c r="L15" t="n">
-        <v>56.32</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>94.58</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-9.26</v>
+        <v>-9.35</v>
       </c>
       <c r="L16" t="n">
-        <v>95.04000000000001</v>
+        <v>96.03</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>35.89</v>
+        <v>41.22</v>
       </c>
       <c r="K17" t="n">
-        <v>-60.28</v>
+        <v>-69.22</v>
       </c>
       <c r="L17" t="n">
-        <v>70.16</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>73.79000000000001</v>
+        <v>79.84</v>
       </c>
       <c r="K18" t="n">
-        <v>5.48</v>
+        <v>5.93</v>
       </c>
       <c r="L18" t="n">
-        <v>74</v>
+        <v>80.06</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>33.62</v>
+        <v>37.21</v>
       </c>
       <c r="K19" t="n">
-        <v>56.3</v>
+        <v>62.33</v>
       </c>
       <c r="L19" t="n">
-        <v>65.56999999999999</v>
+        <v>72.59</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-137.14</v>
+        <v>-146.86</v>
       </c>
       <c r="K20" t="n">
-        <v>-50.29</v>
+        <v>-53.86</v>
       </c>
       <c r="L20" t="n">
-        <v>146.07</v>
+        <v>156.43</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>14.1</v>
+        <v>16.44</v>
       </c>
       <c r="K21" t="n">
-        <v>94.31</v>
+        <v>109.95</v>
       </c>
       <c r="L21" t="n">
-        <v>95.36</v>
+        <v>111.17</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>18.51</v>
+        <v>20.63</v>
       </c>
       <c r="K22" t="n">
-        <v>122.23</v>
+        <v>136.23</v>
       </c>
       <c r="L22" t="n">
-        <v>123.62</v>
+        <v>137.79</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-87.28</v>
+        <v>-102.02</v>
       </c>
       <c r="K23" t="n">
-        <v>-120.3</v>
+        <v>-140.62</v>
       </c>
       <c r="L23" t="n">
-        <v>148.63</v>
+        <v>173.73</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-155.83</v>
+        <v>-178.65</v>
       </c>
       <c r="K24" t="n">
-        <v>-99.39</v>
+        <v>-113.94</v>
       </c>
       <c r="L24" t="n">
-        <v>184.83</v>
+        <v>211.9</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-57.81</v>
+        <v>-72.48</v>
       </c>
       <c r="K25" t="n">
-        <v>-106.72</v>
+        <v>-133.8</v>
       </c>
       <c r="L25" t="n">
-        <v>121.37</v>
+        <v>152.17</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-82.09</v>
+        <v>-104.54</v>
       </c>
       <c r="K26" t="n">
-        <v>139.16</v>
+        <v>177.22</v>
       </c>
       <c r="L26" t="n">
-        <v>161.56</v>
+        <v>205.75</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-146.03</v>
+        <v>-179.25</v>
       </c>
       <c r="K27" t="n">
-        <v>-103.41</v>
+        <v>-126.94</v>
       </c>
       <c r="L27" t="n">
-        <v>178.94</v>
+        <v>219.65</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>30.01</v>
+        <v>35.79</v>
       </c>
       <c r="K28" t="n">
-        <v>221.65</v>
+        <v>264.37</v>
       </c>
       <c r="L28" t="n">
-        <v>223.67</v>
+        <v>266.79</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.29</v>
+        <v>-31.31</v>
       </c>
       <c r="K29" t="n">
-        <v>-34.78</v>
+        <v>-39.9</v>
       </c>
       <c r="L29" t="n">
-        <v>44.2</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>4.14</v>
+        <v>4.74</v>
       </c>
       <c r="K30" t="n">
-        <v>-51.77</v>
+        <v>-59.35</v>
       </c>
       <c r="L30" t="n">
-        <v>51.93</v>
+        <v>59.54</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>26.95</v>
+        <v>32.56</v>
       </c>
       <c r="K31" t="n">
-        <v>33.45</v>
+        <v>40.41</v>
       </c>
       <c r="L31" t="n">
-        <v>42.95</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>74.5</v>
+        <v>81.2</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.11</v>
+        <v>-3.39</v>
       </c>
       <c r="L32" t="n">
-        <v>74.56999999999999</v>
+        <v>81.27</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>36.54</v>
+        <v>41.84</v>
       </c>
       <c r="K33" t="n">
-        <v>-50.23</v>
+        <v>-57.52</v>
       </c>
       <c r="L33" t="n">
-        <v>62.11</v>
+        <v>71.12</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>25.65</v>
+        <v>30.53</v>
       </c>
       <c r="K34" t="n">
-        <v>-48.12</v>
+        <v>-57.26</v>
       </c>
       <c r="L34" t="n">
-        <v>54.53</v>
+        <v>64.89</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-69.52</v>
+        <v>-76.68000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-98.8</v>
+        <v>-108.96</v>
       </c>
       <c r="L35" t="n">
-        <v>120.81</v>
+        <v>133.24</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-70.19</v>
+        <v>-85.40000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>38.85</v>
+        <v>47.28</v>
       </c>
       <c r="L36" t="n">
-        <v>80.22</v>
+        <v>97.62</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>111.06</v>
+        <v>126.85</v>
       </c>
       <c r="K37" t="n">
-        <v>-19.41</v>
+        <v>-22.16</v>
       </c>
       <c r="L37" t="n">
-        <v>112.75</v>
+        <v>128.77</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-71.73</v>
+        <v>-90.73</v>
       </c>
       <c r="K38" t="n">
-        <v>-106.24</v>
+        <v>-134.39</v>
       </c>
       <c r="L38" t="n">
-        <v>128.19</v>
+        <v>162.15</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>106.74</v>
+        <v>134.72</v>
       </c>
       <c r="K39" t="n">
-        <v>-42.6</v>
+        <v>-53.77</v>
       </c>
       <c r="L39" t="n">
-        <v>114.93</v>
+        <v>145.05</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>93.34</v>
+        <v>116.52</v>
       </c>
       <c r="K40" t="n">
-        <v>-47.01</v>
+        <v>-58.69</v>
       </c>
       <c r="L40" t="n">
-        <v>104.51</v>
+        <v>130.47</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-133.52</v>
+        <v>-165.35</v>
       </c>
       <c r="K41" t="n">
-        <v>-154.62</v>
+        <v>-191.48</v>
       </c>
       <c r="L41" t="n">
-        <v>204.29</v>
+        <v>253</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>229.62</v>
+        <v>274.06</v>
       </c>
       <c r="K42" t="n">
-        <v>-62.57</v>
+        <v>-74.68000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>238</v>
+        <v>284.05</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>144.92</v>
+        <v>169.31</v>
       </c>
       <c r="K43" t="n">
-        <v>157.55</v>
+        <v>184.07</v>
       </c>
       <c r="L43" t="n">
-        <v>214.07</v>
+        <v>250.1</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>22.5</v>
+        <v>23.62</v>
       </c>
       <c r="K44" t="n">
-        <v>79.25</v>
+        <v>83.17</v>
       </c>
       <c r="L44" t="n">
-        <v>82.38</v>
+        <v>86.45999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>10.04</v>
+        <v>11.62</v>
       </c>
       <c r="K45" t="n">
-        <v>45.68</v>
+        <v>52.85</v>
       </c>
       <c r="L45" t="n">
-        <v>46.77</v>
+        <v>54.11</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-62.72</v>
+        <v>-68.34999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>-19.72</v>
+        <v>-21.49</v>
       </c>
       <c r="L46" t="n">
-        <v>65.75</v>
+        <v>71.65000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="K47" t="n">
-        <v>67.22</v>
+        <v>76.06</v>
       </c>
       <c r="L47" t="n">
-        <v>67.23999999999999</v>
+        <v>76.08</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>8.49</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-104.88</v>
+        <v>-106.38</v>
       </c>
       <c r="L48" t="n">
-        <v>105.22</v>
+        <v>106.73</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-48.17</v>
+        <v>-56.76</v>
       </c>
       <c r="K49" t="n">
-        <v>-29.88</v>
+        <v>-35.21</v>
       </c>
       <c r="L49" t="n">
-        <v>56.68</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-65.97</v>
+        <v>-73.09</v>
       </c>
       <c r="K50" t="n">
-        <v>113.54</v>
+        <v>125.8</v>
       </c>
       <c r="L50" t="n">
-        <v>131.32</v>
+        <v>145.49</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.109999999999999</v>
+        <v>-11.55</v>
       </c>
       <c r="K51" t="n">
-        <v>-84.11</v>
+        <v>-106.67</v>
       </c>
       <c r="L51" t="n">
-        <v>84.61</v>
+        <v>107.29</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-81.86</v>
+        <v>-96.05</v>
       </c>
       <c r="K52" t="n">
-        <v>11.29</v>
+        <v>13.24</v>
       </c>
       <c r="L52" t="n">
-        <v>82.63</v>
+        <v>96.95999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>49.13</v>
+        <v>59.7</v>
       </c>
       <c r="K53" t="n">
-        <v>-136.36</v>
+        <v>-165.67</v>
       </c>
       <c r="L53" t="n">
-        <v>144.94</v>
+        <v>176.1</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-120.14</v>
+        <v>-146.31</v>
       </c>
       <c r="K54" t="n">
-        <v>22.53</v>
+        <v>27.44</v>
       </c>
       <c r="L54" t="n">
-        <v>122.23</v>
+        <v>148.86</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>132.26</v>
+        <v>157.91</v>
       </c>
       <c r="K55" t="n">
-        <v>59.85</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>145.17</v>
+        <v>173.33</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>152.3</v>
+        <v>189.05</v>
       </c>
       <c r="K56" t="n">
-        <v>88.25</v>
+        <v>109.55</v>
       </c>
       <c r="L56" t="n">
-        <v>176.02</v>
+        <v>218.49</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-10.78</v>
+        <v>-14.69</v>
       </c>
       <c r="K57" t="n">
-        <v>161.01</v>
+        <v>219.4</v>
       </c>
       <c r="L57" t="n">
-        <v>161.37</v>
+        <v>219.89</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-160.75</v>
+        <v>-188.31</v>
       </c>
       <c r="K58" t="n">
-        <v>-201.51</v>
+        <v>-236.06</v>
       </c>
       <c r="L58" t="n">
-        <v>257.78</v>
+        <v>301.97</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-46.25</v>
+        <v>-53.9</v>
       </c>
       <c r="K59" t="n">
-        <v>16.91</v>
+        <v>19.71</v>
       </c>
       <c r="L59" t="n">
-        <v>49.25</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>55.55</v>
+        <v>61.1</v>
       </c>
       <c r="K60" t="n">
-        <v>10.65</v>
+        <v>11.71</v>
       </c>
       <c r="L60" t="n">
-        <v>56.56</v>
+        <v>62.21</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-77.63</v>
+        <v>-82.61</v>
       </c>
       <c r="K61" t="n">
-        <v>24.5</v>
+        <v>26.07</v>
       </c>
       <c r="L61" t="n">
-        <v>81.40000000000001</v>
+        <v>86.62</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>27.04</v>
+        <v>31.53</v>
       </c>
       <c r="K62" t="n">
-        <v>52.36</v>
+        <v>61.05</v>
       </c>
       <c r="L62" t="n">
-        <v>58.93</v>
+        <v>68.72</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.84</v>
+        <v>-2.26</v>
       </c>
       <c r="K63" t="n">
-        <v>-22.41</v>
+        <v>-27.52</v>
       </c>
       <c r="L63" t="n">
-        <v>22.49</v>
+        <v>27.61</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>45.86</v>
+        <v>54.62</v>
       </c>
       <c r="K64" t="n">
-        <v>41.34</v>
+        <v>49.24</v>
       </c>
       <c r="L64" t="n">
-        <v>61.74</v>
+        <v>73.54000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-87.45</v>
+        <v>-106.15</v>
       </c>
       <c r="K65" t="n">
-        <v>-66.64</v>
+        <v>-80.89</v>
       </c>
       <c r="L65" t="n">
-        <v>109.95</v>
+        <v>133.46</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-125.45</v>
+        <v>-145.4</v>
       </c>
       <c r="K66" t="n">
-        <v>-9.02</v>
+        <v>-10.46</v>
       </c>
       <c r="L66" t="n">
-        <v>125.78</v>
+        <v>145.77</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-75.34999999999999</v>
+        <v>-99.08</v>
       </c>
       <c r="K67" t="n">
-        <v>35.39</v>
+        <v>46.54</v>
       </c>
       <c r="L67" t="n">
-        <v>83.25</v>
+        <v>109.46</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>-19.62</v>
+        <v>-26.18</v>
       </c>
       <c r="K68" t="n">
-        <v>-63.66</v>
+        <v>-84.94</v>
       </c>
       <c r="L68" t="n">
-        <v>66.61</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-18.18</v>
+        <v>-21.34</v>
       </c>
       <c r="K69" t="n">
-        <v>177.79</v>
+        <v>208.64</v>
       </c>
       <c r="L69" t="n">
-        <v>178.71</v>
+        <v>209.73</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>204.84</v>
+        <v>233.85</v>
       </c>
       <c r="K70" t="n">
-        <v>32.81</v>
+        <v>37.46</v>
       </c>
       <c r="L70" t="n">
-        <v>207.45</v>
+        <v>236.83</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>92.58</v>
+        <v>121.8</v>
       </c>
       <c r="K71" t="n">
-        <v>167.27</v>
+        <v>220.06</v>
       </c>
       <c r="L71" t="n">
-        <v>191.19</v>
+        <v>251.51</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-231.03</v>
+        <v>-282.16</v>
       </c>
       <c r="K72" t="n">
-        <v>-40.29</v>
+        <v>-49.21</v>
       </c>
       <c r="L72" t="n">
-        <v>234.52</v>
+        <v>286.42</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-78.38</v>
+        <v>-103.14</v>
       </c>
       <c r="K73" t="n">
-        <v>149.68</v>
+        <v>196.97</v>
       </c>
       <c r="L73" t="n">
-        <v>168.96</v>
+        <v>222.34</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>22.47</v>
+        <v>24.01</v>
       </c>
       <c r="K74" t="n">
-        <v>-65.86</v>
+        <v>-70.38</v>
       </c>
       <c r="L74" t="n">
-        <v>69.59</v>
+        <v>74.36</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>55.07</v>
+        <v>61.39</v>
       </c>
       <c r="K75" t="n">
-        <v>-13.5</v>
+        <v>-15.05</v>
       </c>
       <c r="L75" t="n">
-        <v>56.7</v>
+        <v>63.21</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-30.76</v>
+        <v>-36.71</v>
       </c>
       <c r="K76" t="n">
-        <v>-32.75</v>
+        <v>-39.09</v>
       </c>
       <c r="L76" t="n">
-        <v>44.93</v>
+        <v>53.62</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-39.56</v>
+        <v>-45.26</v>
       </c>
       <c r="K77" t="n">
-        <v>47.44</v>
+        <v>54.29</v>
       </c>
       <c r="L77" t="n">
-        <v>61.77</v>
+        <v>70.68000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-32.98</v>
+        <v>-38.6</v>
       </c>
       <c r="K78" t="n">
-        <v>51.85</v>
+        <v>60.68</v>
       </c>
       <c r="L78" t="n">
-        <v>61.45</v>
+        <v>71.92</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>3.07</v>
+        <v>3.39</v>
       </c>
       <c r="K79" t="n">
-        <v>-72.02</v>
+        <v>-79.45999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>72.09</v>
+        <v>79.53</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>2.24</v>
+        <v>2.71</v>
       </c>
       <c r="K80" t="n">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="L80" t="n">
-        <v>2.7</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-54.65</v>
+        <v>-63.21</v>
       </c>
       <c r="K81" t="n">
-        <v>-97.17</v>
+        <v>-112.38</v>
       </c>
       <c r="L81" t="n">
-        <v>111.48</v>
+        <v>128.93</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-85.90000000000001</v>
+        <v>-97.11</v>
       </c>
       <c r="K82" t="n">
-        <v>-86.36</v>
+        <v>-97.63</v>
       </c>
       <c r="L82" t="n">
-        <v>121.8</v>
+        <v>137.71</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-96.38</v>
+        <v>-119.19</v>
       </c>
       <c r="K83" t="n">
-        <v>-115.16</v>
+        <v>-142.42</v>
       </c>
       <c r="L83" t="n">
-        <v>150.17</v>
+        <v>185.71</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-93.04000000000001</v>
+        <v>-113.3</v>
       </c>
       <c r="K84" t="n">
-        <v>122.68</v>
+        <v>149.4</v>
       </c>
       <c r="L84" t="n">
-        <v>153.97</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>35.78</v>
+        <v>43.44</v>
       </c>
       <c r="K85" t="n">
-        <v>132.57</v>
+        <v>160.96</v>
       </c>
       <c r="L85" t="n">
-        <v>137.32</v>
+        <v>166.71</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>114.76</v>
+        <v>159.41</v>
       </c>
       <c r="K86" t="n">
-        <v>-137.81</v>
+        <v>-191.43</v>
       </c>
       <c r="L86" t="n">
-        <v>179.34</v>
+        <v>249.11</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-142.03</v>
+        <v>-202.08</v>
       </c>
       <c r="K87" t="n">
-        <v>93.63</v>
+        <v>133.22</v>
       </c>
       <c r="L87" t="n">
-        <v>170.12</v>
+        <v>242.04</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-199.54</v>
+        <v>-251.03</v>
       </c>
       <c r="K88" t="n">
-        <v>-57.26</v>
+        <v>-72.03</v>
       </c>
       <c r="L88" t="n">
-        <v>207.59</v>
+        <v>261.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-24.xlsx
+++ b/output/2024-09-24.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>72.86</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-21.84</v>
+        <v>-22.9</v>
       </c>
       <c r="L14" t="n">
-        <v>76.06</v>
+        <v>79.76000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-61.54</v>
+        <v>-62.44</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.68</v>
+        <v>-9.82</v>
       </c>
       <c r="L15" t="n">
-        <v>62.3</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>95.56999999999999</v>
+        <v>100.21</v>
       </c>
       <c r="K16" t="n">
-        <v>-9.35</v>
+        <v>-9.81</v>
       </c>
       <c r="L16" t="n">
-        <v>96.03</v>
+        <v>100.69</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>41.22</v>
+        <v>42.15</v>
       </c>
       <c r="K17" t="n">
-        <v>-69.22</v>
+        <v>-70.78</v>
       </c>
       <c r="L17" t="n">
-        <v>80.56</v>
+        <v>82.38</v>
       </c>
     </row>
     <row r="18">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>37.21</v>
+        <v>37.48</v>
       </c>
       <c r="K19" t="n">
-        <v>62.33</v>
+        <v>62.77</v>
       </c>
       <c r="L19" t="n">
-        <v>72.59</v>
+        <v>73.11</v>
       </c>
     </row>
     <row r="20">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>32.56</v>
+        <v>33.47</v>
       </c>
       <c r="K31" t="n">
-        <v>40.41</v>
+        <v>41.54</v>
       </c>
       <c r="L31" t="n">
-        <v>51.89</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>81.2</v>
+        <v>84.7</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.39</v>
+        <v>-3.53</v>
       </c>
       <c r="L32" t="n">
-        <v>81.27</v>
+        <v>84.78</v>
       </c>
     </row>
     <row r="33">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>30.53</v>
+        <v>30.74</v>
       </c>
       <c r="K34" t="n">
-        <v>-57.26</v>
+        <v>-57.67</v>
       </c>
       <c r="L34" t="n">
-        <v>64.89</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>23.62</v>
+        <v>24.72</v>
       </c>
       <c r="K44" t="n">
-        <v>83.17</v>
+        <v>87.05</v>
       </c>
       <c r="L44" t="n">
-        <v>86.45999999999999</v>
+        <v>90.48999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>11.62</v>
+        <v>11.98</v>
       </c>
       <c r="K45" t="n">
-        <v>52.85</v>
+        <v>54.52</v>
       </c>
       <c r="L45" t="n">
-        <v>54.11</v>
+        <v>55.82</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-68.34999999999999</v>
+        <v>-76.59</v>
       </c>
       <c r="K46" t="n">
-        <v>-21.49</v>
+        <v>-24.08</v>
       </c>
       <c r="L46" t="n">
-        <v>71.65000000000001</v>
+        <v>80.29000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="K47" t="n">
-        <v>76.06</v>
+        <v>81.88</v>
       </c>
       <c r="L47" t="n">
-        <v>76.08</v>
+        <v>81.89</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>8.609999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="K48" t="n">
-        <v>-106.38</v>
+        <v>-110.97</v>
       </c>
       <c r="L48" t="n">
-        <v>106.73</v>
+        <v>111.33</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-56.76</v>
+        <v>-62.58</v>
       </c>
       <c r="K49" t="n">
-        <v>-35.21</v>
+        <v>-38.82</v>
       </c>
       <c r="L49" t="n">
-        <v>66.8</v>
+        <v>73.64</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-53.9</v>
+        <v>-59.79</v>
       </c>
       <c r="K59" t="n">
-        <v>19.71</v>
+        <v>21.87</v>
       </c>
       <c r="L59" t="n">
-        <v>57.4</v>
+        <v>63.67</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>61.1</v>
+        <v>61.44</v>
       </c>
       <c r="K60" t="n">
-        <v>11.71</v>
+        <v>11.78</v>
       </c>
       <c r="L60" t="n">
-        <v>62.21</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-82.61</v>
+        <v>-85.98</v>
       </c>
       <c r="K61" t="n">
-        <v>26.07</v>
+        <v>27.14</v>
       </c>
       <c r="L61" t="n">
-        <v>86.62</v>
+        <v>90.16</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>31.53</v>
+        <v>31.79</v>
       </c>
       <c r="K62" t="n">
-        <v>61.05</v>
+        <v>61.55</v>
       </c>
       <c r="L62" t="n">
-        <v>68.72</v>
+        <v>69.28</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.26</v>
+        <v>-2.34</v>
       </c>
       <c r="K63" t="n">
-        <v>-27.52</v>
+        <v>-28.55</v>
       </c>
       <c r="L63" t="n">
-        <v>27.61</v>
+        <v>28.64</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>54.62</v>
+        <v>59.95</v>
       </c>
       <c r="K64" t="n">
-        <v>49.24</v>
+        <v>54.04</v>
       </c>
       <c r="L64" t="n">
-        <v>73.54000000000001</v>
+        <v>80.70999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>24.01</v>
+        <v>26.85</v>
       </c>
       <c r="K74" t="n">
-        <v>-70.38</v>
+        <v>-78.7</v>
       </c>
       <c r="L74" t="n">
-        <v>74.36</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>61.39</v>
+        <v>65.73</v>
       </c>
       <c r="K75" t="n">
-        <v>-15.05</v>
+        <v>-16.12</v>
       </c>
       <c r="L75" t="n">
-        <v>63.21</v>
+        <v>67.67</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-36.71</v>
+        <v>-39.92</v>
       </c>
       <c r="K76" t="n">
-        <v>-39.09</v>
+        <v>-42.5</v>
       </c>
       <c r="L76" t="n">
-        <v>53.62</v>
+        <v>58.31</v>
       </c>
     </row>
     <row r="77">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-38.6</v>
+        <v>-43.6</v>
       </c>
       <c r="K78" t="n">
-        <v>60.68</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>71.92</v>
+        <v>81.23999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="K79" t="n">
-        <v>-79.45999999999999</v>
+        <v>-84.54000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>79.53</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="80">
